--- a/IV_3.5K_T1.xlsx
+++ b/IV_3.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Queries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1758,7 +1758,7 @@
         <v>12.5</v>
       </c>
       <c r="AP13">
-        <v>1.6789999999999999E-2</v>
+        <v>1.669E-2</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -1886,7 +1886,7 @@
         <v>14.0625</v>
       </c>
       <c r="AP14">
-        <v>1.8540000000000001E-2</v>
+        <v>1.864E-2</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2014,7 +2014,7 @@
         <v>15.625</v>
       </c>
       <c r="AP15">
-        <v>2.0299999999999999E-2</v>
+        <v>2.0400000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2124,7 +2124,7 @@
         <v>17.1875</v>
       </c>
       <c r="AJ16">
-        <v>2.3199999999999998E-2</v>
+        <v>2.3099999999999999E-2</v>
       </c>
       <c r="AK16">
         <v>17.1875</v>
@@ -2142,7 +2142,7 @@
         <v>17.1875</v>
       </c>
       <c r="AP16">
-        <v>2.3179999999999999E-2</v>
+        <v>2.3279999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
@@ -2270,7 +2270,7 @@
         <v>18.75</v>
       </c>
       <c r="AP17">
-        <v>2.529E-2</v>
+        <v>2.5489999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
@@ -2380,7 +2380,7 @@
         <v>20.3125</v>
       </c>
       <c r="AJ18">
-        <v>2.741E-2</v>
+        <v>2.7480000000000001E-2</v>
       </c>
       <c r="AK18">
         <v>20.3125</v>
@@ -2508,7 +2508,7 @@
         <v>21.875</v>
       </c>
       <c r="AJ19">
-        <v>2.9520000000000001E-2</v>
+        <v>2.9530000000000001E-2</v>
       </c>
       <c r="AK19">
         <v>21.875</v>
@@ -2526,7 +2526,7 @@
         <v>21.875</v>
       </c>
       <c r="AP19">
-        <v>2.9510000000000002E-2</v>
+        <v>2.9309999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
@@ -2636,7 +2636,7 @@
         <v>23.4375</v>
       </c>
       <c r="AJ20">
-        <v>3.1620000000000002E-2</v>
+        <v>3.1609999999999999E-2</v>
       </c>
       <c r="AK20">
         <v>23.4375</v>
@@ -2654,7 +2654,7 @@
         <v>23.4375</v>
       </c>
       <c r="AP20">
-        <v>3.1609999999999999E-2</v>
+        <v>3.1510000000000003E-2</v>
       </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
@@ -2764,7 +2764,7 @@
         <v>25</v>
       </c>
       <c r="AJ21">
-        <v>3.372E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="AK21">
         <v>25</v>
@@ -2782,7 +2782,7 @@
         <v>25</v>
       </c>
       <c r="AP21">
-        <v>3.3709999999999997E-2</v>
+        <v>3.3509999999999998E-2</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
@@ -2892,7 +2892,7 @@
         <v>26.5625</v>
       </c>
       <c r="AJ22">
-        <v>3.5810000000000002E-2</v>
+        <v>3.5770000000000003E-2</v>
       </c>
       <c r="AK22">
         <v>26.5625</v>
@@ -3020,7 +3020,7 @@
         <v>28.125</v>
       </c>
       <c r="AJ23">
-        <v>3.7920000000000002E-2</v>
+        <v>3.7870000000000001E-2</v>
       </c>
       <c r="AK23">
         <v>28.125</v>
@@ -3038,7 +3038,7 @@
         <v>28.125</v>
       </c>
       <c r="AP23">
-        <v>3.7920000000000002E-2</v>
+        <v>3.8120000000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
@@ -3148,7 +3148,7 @@
         <v>29.6875</v>
       </c>
       <c r="AJ24">
-        <v>4.002E-2</v>
+        <v>4.0079999999999998E-2</v>
       </c>
       <c r="AK24">
         <v>29.6875</v>
@@ -3166,7 +3166,7 @@
         <v>29.6875</v>
       </c>
       <c r="AP24">
-        <v>4.002E-2</v>
+        <v>4.0219999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.25">
@@ -3404,7 +3404,7 @@
         <v>32.8125</v>
       </c>
       <c r="AJ26">
-        <v>4.4220000000000002E-2</v>
+        <v>4.4229999999999998E-2</v>
       </c>
       <c r="AK26">
         <v>32.8125</v>
@@ -3422,7 +3422,7 @@
         <v>32.8125</v>
       </c>
       <c r="AP26">
-        <v>4.4209999999999999E-2</v>
+        <v>4.4409999999999998E-2</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
@@ -3532,7 +3532,7 @@
         <v>34.375</v>
       </c>
       <c r="AJ27">
-        <v>4.6330000000000003E-2</v>
+        <v>4.632E-2</v>
       </c>
       <c r="AK27">
         <v>34.375</v>
@@ -3550,7 +3550,7 @@
         <v>34.375</v>
       </c>
       <c r="AP27">
-        <v>4.6330000000000003E-2</v>
+        <v>4.6129999999999997E-2</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
@@ -3660,7 +3660,7 @@
         <v>35.9375</v>
       </c>
       <c r="AJ28">
-        <v>4.8430000000000001E-2</v>
+        <v>4.8419999999999998E-2</v>
       </c>
       <c r="AK28">
         <v>35.9375</v>
@@ -3678,7 +3678,7 @@
         <v>35.9375</v>
       </c>
       <c r="AP28">
-        <v>4.8430000000000001E-2</v>
+        <v>4.863E-2</v>
       </c>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
@@ -3788,7 +3788,7 @@
         <v>37.5</v>
       </c>
       <c r="AJ29">
-        <v>5.0540000000000002E-2</v>
+        <v>5.0520000000000002E-2</v>
       </c>
       <c r="AK29">
         <v>37.5</v>
@@ -3806,7 +3806,7 @@
         <v>37.5</v>
       </c>
       <c r="AP29">
-        <v>5.0540000000000002E-2</v>
+        <v>5.074E-2</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
@@ -3916,7 +3916,7 @@
         <v>39.0625</v>
       </c>
       <c r="AJ30">
-        <v>5.2650000000000002E-2</v>
+        <v>5.2659999999999998E-2</v>
       </c>
       <c r="AK30">
         <v>39.0625</v>
@@ -3934,7 +3934,7 @@
         <v>39.0625</v>
       </c>
       <c r="AP30">
-        <v>5.2639999999999999E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
@@ -4044,7 +4044,7 @@
         <v>40.625</v>
       </c>
       <c r="AJ31">
-        <v>5.4760000000000003E-2</v>
+        <v>5.4769999999999999E-2</v>
       </c>
       <c r="AK31">
         <v>40.625</v>
@@ -4062,7 +4062,7 @@
         <v>40.625</v>
       </c>
       <c r="AP31">
-        <v>5.4760000000000003E-2</v>
+        <v>5.4859999999999999E-2</v>
       </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.25">
@@ -4172,7 +4172,7 @@
         <v>42.1875</v>
       </c>
       <c r="AJ32">
-        <v>5.6849999999999998E-2</v>
+        <v>5.6840000000000002E-2</v>
       </c>
       <c r="AK32">
         <v>42.1875</v>
@@ -4190,7 +4190,7 @@
         <v>42.1875</v>
       </c>
       <c r="AP32">
-        <v>5.6849999999999998E-2</v>
+        <v>5.6950000000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.25">
@@ -4300,7 +4300,7 @@
         <v>43.75</v>
       </c>
       <c r="AJ33">
-        <v>5.8959999999999999E-2</v>
+        <v>5.8950000000000002E-2</v>
       </c>
       <c r="AK33">
         <v>43.75</v>
@@ -4318,7 +4318,7 @@
         <v>43.75</v>
       </c>
       <c r="AP33">
-        <v>5.8950000000000002E-2</v>
+        <v>5.8749999999999997E-2</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
@@ -4428,7 +4428,7 @@
         <v>45.3125</v>
       </c>
       <c r="AJ34">
-        <v>6.1060000000000003E-2</v>
+        <v>6.105E-2</v>
       </c>
       <c r="AK34">
         <v>45.3125</v>
@@ -4446,7 +4446,7 @@
         <v>45.3125</v>
       </c>
       <c r="AP34">
-        <v>6.105E-2</v>
+        <v>6.0850000000000001E-2</v>
       </c>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.25">
@@ -4556,7 +4556,7 @@
         <v>46.875</v>
       </c>
       <c r="AJ35">
-        <v>6.3170000000000004E-2</v>
+        <v>6.318E-2</v>
       </c>
       <c r="AK35">
         <v>46.875</v>
@@ -4574,7 +4574,7 @@
         <v>46.875</v>
       </c>
       <c r="AP35">
-        <v>6.3159999999999994E-2</v>
+        <v>6.336E-2</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>48.4375</v>
       </c>
       <c r="AJ36">
-        <v>6.5269999999999995E-2</v>
+        <v>6.5259999999999999E-2</v>
       </c>
       <c r="AK36">
         <v>48.4375</v>
@@ -4702,7 +4702,7 @@
         <v>48.4375</v>
       </c>
       <c r="AP36">
-        <v>6.5259999999999999E-2</v>
+        <v>6.5060000000000007E-2</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.25">
@@ -4812,7 +4812,7 @@
         <v>50</v>
       </c>
       <c r="AJ37">
-        <v>6.7449999999999996E-2</v>
+        <v>6.7460000000000006E-2</v>
       </c>
       <c r="AK37">
         <v>50</v>
@@ -4940,7 +4940,7 @@
         <v>51.5625</v>
       </c>
       <c r="AJ38">
-        <v>6.9550000000000001E-2</v>
+        <v>6.9519999999999998E-2</v>
       </c>
       <c r="AK38">
         <v>51.5625</v>
@@ -4958,7 +4958,7 @@
         <v>51.5625</v>
       </c>
       <c r="AP38">
-        <v>6.9540000000000005E-2</v>
+        <v>6.9739999999999996E-2</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.25">
@@ -5068,7 +5068,7 @@
         <v>53.125</v>
       </c>
       <c r="AJ39">
-        <v>7.1669999999999998E-2</v>
+        <v>7.1660000000000001E-2</v>
       </c>
       <c r="AK39">
         <v>53.125</v>
@@ -5086,7 +5086,7 @@
         <v>53.125</v>
       </c>
       <c r="AP39">
-        <v>7.1669999999999998E-2</v>
+        <v>7.1569999999999995E-2</v>
       </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.25">
@@ -5196,7 +5196,7 @@
         <v>54.6875</v>
       </c>
       <c r="AJ40">
-        <v>7.3770000000000002E-2</v>
+        <v>7.3760000000000006E-2</v>
       </c>
       <c r="AK40">
         <v>54.6875</v>
@@ -5214,7 +5214,7 @@
         <v>54.6875</v>
       </c>
       <c r="AP40">
-        <v>7.3779999999999998E-2</v>
+        <v>7.3580000000000007E-2</v>
       </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.25">
@@ -5324,7 +5324,7 @@
         <v>56.25</v>
       </c>
       <c r="AJ41">
-        <v>7.5880000000000003E-2</v>
+        <v>7.5870000000000007E-2</v>
       </c>
       <c r="AK41">
         <v>56.25</v>
@@ -5342,7 +5342,7 @@
         <v>56.25</v>
       </c>
       <c r="AP41">
-        <v>7.5889999999999999E-2</v>
+        <v>7.5990000000000002E-2</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.25">
@@ -5362,7 +5362,7 @@
         <v>57.8125</v>
       </c>
       <c r="F42">
-        <v>7.8020000000000006E-2</v>
+        <v>7.7920000000000003E-2</v>
       </c>
       <c r="G42">
         <v>57.8125</v>
@@ -5452,7 +5452,7 @@
         <v>57.8125</v>
       </c>
       <c r="AJ42">
-        <v>7.8E-2</v>
+        <v>7.7899999999999997E-2</v>
       </c>
       <c r="AK42">
         <v>57.8125</v>
@@ -5470,7 +5470,7 @@
         <v>57.8125</v>
       </c>
       <c r="AP42">
-        <v>7.8E-2</v>
+        <v>7.8100000000000003E-2</v>
       </c>
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.25">
@@ -5490,7 +5490,7 @@
         <v>59.375</v>
       </c>
       <c r="F43">
-        <v>8.0130000000000007E-2</v>
+        <v>8.0030000000000004E-2</v>
       </c>
       <c r="G43">
         <v>59.375</v>
@@ -5580,7 +5580,7 @@
         <v>59.375</v>
       </c>
       <c r="AJ43">
-        <v>8.0119999999999997E-2</v>
+        <v>8.0110000000000001E-2</v>
       </c>
       <c r="AK43">
         <v>59.375</v>
@@ -5618,7 +5618,7 @@
         <v>60.9375</v>
       </c>
       <c r="F44">
-        <v>8.2250000000000004E-2</v>
+        <v>8.2449999999999996E-2</v>
       </c>
       <c r="G44">
         <v>60.9375</v>
@@ -5708,7 +5708,7 @@
         <v>60.9375</v>
       </c>
       <c r="AJ44">
-        <v>8.2229999999999998E-2</v>
+        <v>8.2239999999999994E-2</v>
       </c>
       <c r="AK44">
         <v>60.9375</v>
@@ -5746,7 +5746,7 @@
         <v>62.5</v>
       </c>
       <c r="F45" s="1">
-        <v>8.4379999999999997E-2</v>
+        <v>8.4180000000000005E-2</v>
       </c>
       <c r="G45">
         <v>62.5</v>
@@ -5836,7 +5836,7 @@
         <v>62.5</v>
       </c>
       <c r="AJ45">
-        <v>8.4360000000000004E-2</v>
+        <v>8.4379999999999997E-2</v>
       </c>
       <c r="AK45">
         <v>62.5</v>
@@ -5854,7 +5854,7 @@
         <v>62.5</v>
       </c>
       <c r="AP45">
-        <v>8.4370000000000001E-2</v>
+        <v>8.4169999999999995E-2</v>
       </c>
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.25">
@@ -5874,7 +5874,7 @@
         <v>64.0625</v>
       </c>
       <c r="F46" s="1">
-        <v>8.6489999999999997E-2</v>
+        <v>8.6389999999999995E-2</v>
       </c>
       <c r="G46">
         <v>64.0625</v>
@@ -5964,7 +5964,7 @@
         <v>64.0625</v>
       </c>
       <c r="AJ46">
-        <v>8.6480000000000001E-2</v>
+        <v>8.6489999999999997E-2</v>
       </c>
       <c r="AK46">
         <v>64.0625</v>
@@ -6002,7 +6002,7 @@
         <v>65.625</v>
       </c>
       <c r="F47" s="1">
-        <v>8.863E-2</v>
+        <v>8.8730000000000003E-2</v>
       </c>
       <c r="G47">
         <v>65.625</v>
@@ -6092,7 +6092,7 @@
         <v>65.625</v>
       </c>
       <c r="AJ47">
-        <v>8.8620000000000004E-2</v>
+        <v>8.8639999999999997E-2</v>
       </c>
       <c r="AK47">
         <v>65.625</v>
@@ -6130,7 +6130,7 @@
         <v>67.1875</v>
       </c>
       <c r="F48">
-        <v>9.0749999999999997E-2</v>
+        <v>9.0950000000000003E-2</v>
       </c>
       <c r="G48">
         <v>67.1875</v>
@@ -6220,7 +6220,7 @@
         <v>67.1875</v>
       </c>
       <c r="AJ48">
-        <v>9.0730000000000005E-2</v>
+        <v>9.0759999999999993E-2</v>
       </c>
       <c r="AK48">
         <v>67.1875</v>
@@ -6238,7 +6238,7 @@
         <v>67.1875</v>
       </c>
       <c r="AP48">
-        <v>9.0749999999999997E-2</v>
+        <v>9.0649999999999994E-2</v>
       </c>
     </row>
     <row r="49" spans="1:42" x14ac:dyDescent="0.25">
@@ -6258,7 +6258,7 @@
         <v>68.75</v>
       </c>
       <c r="F49">
-        <v>9.289E-2</v>
+        <v>9.2789999999999997E-2</v>
       </c>
       <c r="G49">
         <v>68.75</v>
@@ -6348,7 +6348,7 @@
         <v>68.75</v>
       </c>
       <c r="AJ49">
-        <v>9.2859999999999998E-2</v>
+        <v>9.2880000000000004E-2</v>
       </c>
       <c r="AK49">
         <v>68.75</v>
@@ -6476,7 +6476,7 @@
         <v>70.3125</v>
       </c>
       <c r="AJ50">
-        <v>9.4990000000000005E-2</v>
+        <v>9.4979999999999995E-2</v>
       </c>
       <c r="AK50">
         <v>70.3125</v>
@@ -6494,7 +6494,7 @@
         <v>70.3125</v>
       </c>
       <c r="AP50">
-        <v>9.5000000000000001E-2</v>
+        <v>9.4899999999999998E-2</v>
       </c>
     </row>
     <row r="51" spans="1:42" x14ac:dyDescent="0.25">
@@ -6604,7 +6604,7 @@
         <v>71.875</v>
       </c>
       <c r="AJ51">
-        <v>9.7129999999999994E-2</v>
+        <v>9.7110000000000002E-2</v>
       </c>
       <c r="AK51">
         <v>71.875</v>
@@ -6622,7 +6622,7 @@
         <v>71.875</v>
       </c>
       <c r="AP51">
-        <v>9.715E-2</v>
+        <v>9.6949999999999995E-2</v>
       </c>
     </row>
     <row r="52" spans="1:42" x14ac:dyDescent="0.25">
@@ -6642,7 +6642,7 @@
         <v>73.4375</v>
       </c>
       <c r="F52">
-        <v>9.9279999999999993E-2</v>
+        <v>9.9180000000000004E-2</v>
       </c>
       <c r="G52">
         <v>73.4375</v>
@@ -6732,7 +6732,7 @@
         <v>73.4375</v>
       </c>
       <c r="AJ52">
-        <v>9.9269999999999997E-2</v>
+        <v>9.9220000000000003E-2</v>
       </c>
       <c r="AK52">
         <v>73.4375</v>
@@ -6750,7 +6750,7 @@
         <v>73.4375</v>
       </c>
       <c r="AP52">
-        <v>9.9279999999999993E-2</v>
+        <v>9.9180000000000004E-2</v>
       </c>
     </row>
     <row r="53" spans="1:42" x14ac:dyDescent="0.25">
@@ -6770,7 +6770,7 @@
         <v>75</v>
       </c>
       <c r="F53">
-        <v>0.10142</v>
+        <v>0.10131999999999999</v>
       </c>
       <c r="G53">
         <v>75</v>
@@ -6860,7 +6860,7 @@
         <v>75</v>
       </c>
       <c r="AJ53">
-        <v>0.1014</v>
+        <v>0.10138</v>
       </c>
       <c r="AK53">
         <v>75</v>
@@ -6988,7 +6988,7 @@
         <v>76.5625</v>
       </c>
       <c r="AJ54">
-        <v>0.10355</v>
+        <v>0.10349999999999999</v>
       </c>
       <c r="AK54">
         <v>76.5625</v>
@@ -7006,7 +7006,7 @@
         <v>76.5625</v>
       </c>
       <c r="AP54">
-        <v>0.10356</v>
+        <v>0.10335999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:42" x14ac:dyDescent="0.25">
@@ -7026,7 +7026,7 @@
         <v>78.125</v>
       </c>
       <c r="F55">
-        <v>0.10573</v>
+        <v>0.10582999999999999</v>
       </c>
       <c r="G55">
         <v>78.125</v>
@@ -7116,7 +7116,7 @@
         <v>78.125</v>
       </c>
       <c r="AJ55">
-        <v>0.1057</v>
+        <v>0.1056</v>
       </c>
       <c r="AK55">
         <v>78.125</v>
@@ -7134,7 +7134,7 @@
         <v>78.125</v>
       </c>
       <c r="AP55">
-        <v>0.10571</v>
+        <v>0.10551000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:42" x14ac:dyDescent="0.25">
@@ -7154,7 +7154,7 @@
         <v>79.6875</v>
       </c>
       <c r="F56">
-        <v>0.10786999999999999</v>
+        <v>0.10777</v>
       </c>
       <c r="G56">
         <v>79.6875</v>
@@ -7244,7 +7244,7 @@
         <v>79.6875</v>
       </c>
       <c r="AJ56">
-        <v>0.10786</v>
+        <v>0.10788</v>
       </c>
       <c r="AK56">
         <v>79.6875</v>
@@ -7262,7 +7262,7 @@
         <v>79.6875</v>
       </c>
       <c r="AP56">
-        <v>0.10785</v>
+        <v>0.10795</v>
       </c>
     </row>
     <row r="57" spans="1:42" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
         <v>81.25</v>
       </c>
       <c r="F57">
-        <v>0.11002000000000001</v>
+        <v>0.11022</v>
       </c>
       <c r="G57">
         <v>81.25</v>
@@ -7390,7 +7390,7 @@
         <v>81.25</v>
       </c>
       <c r="AP57">
-        <v>0.11001</v>
+        <v>0.11021</v>
       </c>
     </row>
     <row r="58" spans="1:42" x14ac:dyDescent="0.25">
@@ -7500,7 +7500,7 @@
         <v>82.8125</v>
       </c>
       <c r="AJ58">
-        <v>0.11217000000000001</v>
+        <v>0.11216</v>
       </c>
       <c r="AK58">
         <v>82.8125</v>
@@ -7518,7 +7518,7 @@
         <v>82.8125</v>
       </c>
       <c r="AP58">
-        <v>0.11217000000000001</v>
+        <v>0.11237</v>
       </c>
     </row>
     <row r="59" spans="1:42" x14ac:dyDescent="0.25">
@@ -7538,7 +7538,7 @@
         <v>84.375</v>
       </c>
       <c r="F59">
-        <v>0.11434999999999999</v>
+        <v>0.11425</v>
       </c>
       <c r="G59">
         <v>84.375</v>
@@ -7628,7 +7628,7 @@
         <v>84.375</v>
       </c>
       <c r="AJ59">
-        <v>0.11434999999999999</v>
+        <v>0.11432</v>
       </c>
       <c r="AK59">
         <v>84.375</v>
@@ -7646,7 +7646,7 @@
         <v>84.375</v>
       </c>
       <c r="AP59">
-        <v>0.11434</v>
+        <v>0.11444</v>
       </c>
     </row>
     <row r="60" spans="1:42" x14ac:dyDescent="0.25">
@@ -7666,7 +7666,7 @@
         <v>85.9375</v>
       </c>
       <c r="F60" s="1">
-        <v>0.11652</v>
+        <v>0.11662</v>
       </c>
       <c r="G60">
         <v>85.9375</v>
@@ -7774,7 +7774,7 @@
         <v>85.9375</v>
       </c>
       <c r="AP60">
-        <v>0.11651</v>
+        <v>0.11631</v>
       </c>
     </row>
     <row r="61" spans="1:42" x14ac:dyDescent="0.25">
@@ -7794,7 +7794,7 @@
         <v>87.5</v>
       </c>
       <c r="F61" s="1">
-        <v>0.11871</v>
+        <v>0.11860999999999999</v>
       </c>
       <c r="G61">
         <v>87.5</v>
@@ -7884,7 +7884,7 @@
         <v>87.5</v>
       </c>
       <c r="AJ61">
-        <v>0.11869</v>
+        <v>0.11866</v>
       </c>
       <c r="AK61">
         <v>87.5</v>
@@ -7922,7 +7922,7 @@
         <v>89.0625</v>
       </c>
       <c r="F62" s="1">
-        <v>0.12089</v>
+        <v>0.12078999999999999</v>
       </c>
       <c r="G62">
         <v>89.0625</v>
@@ -8012,7 +8012,7 @@
         <v>89.0625</v>
       </c>
       <c r="AJ62">
-        <v>0.12087000000000001</v>
+        <v>0.12088</v>
       </c>
       <c r="AK62">
         <v>89.0625</v>
@@ -8030,7 +8030,7 @@
         <v>89.0625</v>
       </c>
       <c r="AP62">
-        <v>0.12087000000000001</v>
+        <v>0.12096999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:42" x14ac:dyDescent="0.25">
@@ -8050,7 +8050,7 @@
         <v>90.625</v>
       </c>
       <c r="F63">
-        <v>0.12307999999999999</v>
+        <v>0.12288</v>
       </c>
       <c r="G63">
         <v>90.625</v>
@@ -8140,7 +8140,7 @@
         <v>90.625</v>
       </c>
       <c r="AJ63">
-        <v>0.12307</v>
+        <v>0.12306</v>
       </c>
       <c r="AK63">
         <v>90.625</v>
@@ -8158,7 +8158,7 @@
         <v>90.625</v>
       </c>
       <c r="AP63">
-        <v>0.12307</v>
+        <v>0.12286999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:42" x14ac:dyDescent="0.25">
@@ -8178,7 +8178,7 @@
         <v>92.1875</v>
       </c>
       <c r="F64">
-        <v>0.12526999999999999</v>
+        <v>0.12517</v>
       </c>
       <c r="G64">
         <v>92.1875</v>
@@ -8268,7 +8268,7 @@
         <v>92.1875</v>
       </c>
       <c r="AJ64">
-        <v>0.12525</v>
+        <v>0.12523999999999999</v>
       </c>
       <c r="AK64">
         <v>92.1875</v>
@@ -8286,7 +8286,7 @@
         <v>92.1875</v>
       </c>
       <c r="AP64">
-        <v>0.12526000000000001</v>
+        <v>0.12515999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:42" x14ac:dyDescent="0.25">
@@ -8306,7 +8306,7 @@
         <v>93.75</v>
       </c>
       <c r="F65">
-        <v>0.12747</v>
+        <v>0.12737000000000001</v>
       </c>
       <c r="G65">
         <v>93.75</v>
@@ -8396,7 +8396,7 @@
         <v>93.75</v>
       </c>
       <c r="AJ65">
-        <v>0.12745000000000001</v>
+        <v>0.12744</v>
       </c>
       <c r="AK65">
         <v>93.75</v>
@@ -8434,7 +8434,7 @@
         <v>95.3125</v>
       </c>
       <c r="F66">
-        <v>0.12967000000000001</v>
+        <v>0.12947</v>
       </c>
       <c r="G66">
         <v>95.3125</v>
@@ -8524,7 +8524,7 @@
         <v>95.3125</v>
       </c>
       <c r="AJ66">
-        <v>0.12964999999999999</v>
+        <v>0.12964000000000001</v>
       </c>
       <c r="AK66">
         <v>95.3125</v>
@@ -8542,7 +8542,7 @@
         <v>95.3125</v>
       </c>
       <c r="AP66">
-        <v>0.12966</v>
+        <v>0.12956000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:42" x14ac:dyDescent="0.25">
@@ -8562,7 +8562,7 @@
         <v>96.875</v>
       </c>
       <c r="F67">
-        <v>0.13189000000000001</v>
+        <v>0.13209000000000001</v>
       </c>
       <c r="G67">
         <v>96.875</v>
@@ -8652,7 +8652,7 @@
         <v>96.875</v>
       </c>
       <c r="AJ67">
-        <v>0.13186999999999999</v>
+        <v>0.13186</v>
       </c>
       <c r="AK67">
         <v>96.875</v>
@@ -8670,7 +8670,7 @@
         <v>96.875</v>
       </c>
       <c r="AP67">
-        <v>0.13188</v>
+        <v>0.13178000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
@@ -8780,7 +8780,7 @@
         <v>98.4375</v>
       </c>
       <c r="AJ68">
-        <v>0.13408999999999999</v>
+        <v>0.13408</v>
       </c>
       <c r="AK68">
         <v>98.4375</v>
@@ -8818,7 +8818,7 @@
         <v>100</v>
       </c>
       <c r="F69">
-        <v>0.13603000000000001</v>
+        <v>0.13613</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -8926,7 +8926,7 @@
         <v>100</v>
       </c>
       <c r="AP69">
-        <v>0.13603000000000001</v>
+        <v>0.13583000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:42" x14ac:dyDescent="0.25">
@@ -9036,7 +9036,7 @@
         <v>98.4375</v>
       </c>
       <c r="AJ70">
-        <v>0.13389999999999999</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="AK70">
         <v>98.4375</v>
@@ -9054,7 +9054,7 @@
         <v>98.4375</v>
       </c>
       <c r="AP70">
-        <v>0.13391</v>
+        <v>0.13411000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:42" x14ac:dyDescent="0.25">
@@ -9074,7 +9074,7 @@
         <v>96.875</v>
       </c>
       <c r="F71">
-        <v>0.13170999999999999</v>
+        <v>0.13191</v>
       </c>
       <c r="G71">
         <v>96.875</v>
@@ -9164,7 +9164,7 @@
         <v>96.875</v>
       </c>
       <c r="AJ71">
-        <v>0.13170000000000001</v>
+        <v>0.13170999999999999</v>
       </c>
       <c r="AK71">
         <v>96.875</v>
@@ -9202,7 +9202,7 @@
         <v>95.3125</v>
       </c>
       <c r="F72">
-        <v>0.12950999999999999</v>
+        <v>0.12941</v>
       </c>
       <c r="G72">
         <v>95.3125</v>
@@ -9292,7 +9292,7 @@
         <v>95.3125</v>
       </c>
       <c r="AJ72">
-        <v>0.1295</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="AK72">
         <v>95.3125</v>
@@ -9310,7 +9310,7 @@
         <v>95.3125</v>
       </c>
       <c r="AP72">
-        <v>0.12948999999999999</v>
+        <v>0.12928999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:42" x14ac:dyDescent="0.25">
@@ -9330,7 +9330,7 @@
         <v>93.75</v>
       </c>
       <c r="F73">
-        <v>0.12728999999999999</v>
+        <v>0.12719</v>
       </c>
       <c r="G73">
         <v>93.75</v>
@@ -9420,7 +9420,7 @@
         <v>93.75</v>
       </c>
       <c r="AJ73">
-        <v>0.12731000000000001</v>
+        <v>0.1273</v>
       </c>
       <c r="AK73">
         <v>93.75</v>
@@ -9438,7 +9438,7 @@
         <v>93.75</v>
       </c>
       <c r="AP73">
-        <v>0.12728999999999999</v>
+        <v>0.12739</v>
       </c>
     </row>
     <row r="74" spans="1:42" x14ac:dyDescent="0.25">
@@ -9458,7 +9458,7 @@
         <v>92.1875</v>
       </c>
       <c r="F74">
-        <v>0.12509999999999999</v>
+        <v>0.12529999999999999</v>
       </c>
       <c r="G74">
         <v>92.1875</v>
@@ -9548,7 +9548,7 @@
         <v>92.1875</v>
       </c>
       <c r="AJ74">
-        <v>0.12511</v>
+        <v>0.12512000000000001</v>
       </c>
       <c r="AK74">
         <v>92.1875</v>
@@ -9566,7 +9566,7 @@
         <v>92.1875</v>
       </c>
       <c r="AP74">
-        <v>0.12509000000000001</v>
+        <v>0.12489</v>
       </c>
     </row>
     <row r="75" spans="1:42" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>90.625</v>
       </c>
       <c r="F75">
-        <v>0.1229</v>
+        <v>0.12280000000000001</v>
       </c>
       <c r="G75">
         <v>90.625</v>
@@ -9676,7 +9676,7 @@
         <v>90.625</v>
       </c>
       <c r="AJ75">
-        <v>0.12289</v>
+        <v>0.12286999999999999</v>
       </c>
       <c r="AK75">
         <v>90.625</v>
@@ -9694,7 +9694,7 @@
         <v>90.625</v>
       </c>
       <c r="AP75">
-        <v>0.12289</v>
+        <v>0.12299</v>
       </c>
     </row>
     <row r="76" spans="1:42" x14ac:dyDescent="0.25">
@@ -9714,7 +9714,7 @@
         <v>89.0625</v>
       </c>
       <c r="F76" s="1">
-        <v>0.12071999999999999</v>
+        <v>0.12092</v>
       </c>
       <c r="G76">
         <v>89.0625</v>
@@ -9804,7 +9804,7 @@
         <v>89.0625</v>
       </c>
       <c r="AJ76">
-        <v>0.1207</v>
+        <v>0.1208</v>
       </c>
       <c r="AK76">
         <v>89.0625</v>
@@ -9822,7 +9822,7 @@
         <v>89.0625</v>
       </c>
       <c r="AP76">
-        <v>0.12071</v>
+        <v>0.12081</v>
       </c>
     </row>
     <row r="77" spans="1:42" x14ac:dyDescent="0.25">
@@ -9842,7 +9842,7 @@
         <v>87.5</v>
       </c>
       <c r="F77" s="1">
-        <v>0.11851</v>
+        <v>0.11871</v>
       </c>
       <c r="G77">
         <v>87.5</v>
@@ -9932,7 +9932,7 @@
         <v>87.5</v>
       </c>
       <c r="AJ77">
-        <v>0.11851</v>
+        <v>0.11852</v>
       </c>
       <c r="AK77">
         <v>87.5</v>
@@ -9950,7 +9950,7 @@
         <v>87.5</v>
       </c>
       <c r="AP77">
-        <v>0.11851</v>
+        <v>0.11871</v>
       </c>
     </row>
     <row r="78" spans="1:42" x14ac:dyDescent="0.25">
@@ -9970,7 +9970,7 @@
         <v>85.9375</v>
       </c>
       <c r="F78" s="1">
-        <v>0.11633</v>
+        <v>0.11643000000000001</v>
       </c>
       <c r="G78">
         <v>85.9375</v>
@@ -10060,7 +10060,7 @@
         <v>85.9375</v>
       </c>
       <c r="AJ78">
-        <v>0.11633</v>
+        <v>0.11632000000000001</v>
       </c>
       <c r="AK78">
         <v>85.9375</v>
@@ -10078,7 +10078,7 @@
         <v>85.9375</v>
       </c>
       <c r="AP78">
-        <v>0.11633</v>
+        <v>0.11623</v>
       </c>
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.25">
@@ -10098,7 +10098,7 @@
         <v>84.375</v>
       </c>
       <c r="F79" s="1">
-        <v>0.11415</v>
+        <v>0.11405</v>
       </c>
       <c r="G79">
         <v>84.375</v>
@@ -10188,7 +10188,7 @@
         <v>84.375</v>
       </c>
       <c r="AJ79">
-        <v>0.11415</v>
+        <v>0.11416</v>
       </c>
       <c r="AK79">
         <v>84.375</v>
@@ -10226,7 +10226,7 @@
         <v>82.8125</v>
       </c>
       <c r="F80">
-        <v>0.11198</v>
+        <v>0.11218</v>
       </c>
       <c r="G80">
         <v>82.8125</v>
@@ -10316,7 +10316,7 @@
         <v>82.8125</v>
       </c>
       <c r="AJ80">
-        <v>0.11198</v>
+        <v>0.11194</v>
       </c>
       <c r="AK80">
         <v>82.8125</v>
@@ -10334,7 +10334,7 @@
         <v>82.8125</v>
       </c>
       <c r="AP80">
-        <v>0.11198</v>
+        <v>0.11208</v>
       </c>
     </row>
     <row r="81" spans="1:42" x14ac:dyDescent="0.25">
@@ -10354,7 +10354,7 @@
         <v>81.25</v>
       </c>
       <c r="F81" s="1">
-        <v>0.10981</v>
+        <v>0.10971</v>
       </c>
       <c r="G81">
         <v>81.25</v>
@@ -10444,7 +10444,7 @@
         <v>81.25</v>
       </c>
       <c r="AJ81">
-        <v>0.10981</v>
+        <v>0.10982</v>
       </c>
       <c r="AK81">
         <v>81.25</v>
@@ -10572,7 +10572,7 @@
         <v>79.6875</v>
       </c>
       <c r="AJ82">
-        <v>0.10765</v>
+        <v>0.10761999999999999</v>
       </c>
       <c r="AK82">
         <v>79.6875</v>
@@ -10590,7 +10590,7 @@
         <v>79.6875</v>
       </c>
       <c r="AP82">
-        <v>0.10767</v>
+        <v>0.10757</v>
       </c>
     </row>
     <row r="83" spans="1:42" x14ac:dyDescent="0.25">
@@ -10700,7 +10700,7 @@
         <v>78.125</v>
       </c>
       <c r="AJ83" s="1">
-        <v>0.10549</v>
+        <v>0.10546</v>
       </c>
       <c r="AK83">
         <v>78.125</v>
@@ -10718,7 +10718,7 @@
         <v>78.125</v>
       </c>
       <c r="AP83">
-        <v>0.10551000000000001</v>
+        <v>0.10541</v>
       </c>
     </row>
     <row r="84" spans="1:42" x14ac:dyDescent="0.25">
@@ -10738,7 +10738,7 @@
         <v>76.5625</v>
       </c>
       <c r="F84">
-        <v>0.10335</v>
+        <v>0.10355</v>
       </c>
       <c r="G84">
         <v>76.5625</v>
@@ -10828,7 +10828,7 @@
         <v>76.5625</v>
       </c>
       <c r="AJ84">
-        <v>0.10334</v>
+        <v>0.10335</v>
       </c>
       <c r="AK84">
         <v>76.5625</v>
@@ -10846,7 +10846,7 @@
         <v>76.5625</v>
       </c>
       <c r="AP84">
-        <v>0.10335</v>
+        <v>0.10345</v>
       </c>
     </row>
     <row r="85" spans="1:42" x14ac:dyDescent="0.25">
@@ -10866,7 +10866,7 @@
         <v>75</v>
       </c>
       <c r="F85" s="1">
-        <v>0.10120999999999999</v>
+        <v>0.10101</v>
       </c>
       <c r="G85">
         <v>75</v>
@@ -10956,7 +10956,7 @@
         <v>75</v>
       </c>
       <c r="AJ85" s="1">
-        <v>0.1012</v>
+        <v>0.1014</v>
       </c>
       <c r="AK85">
         <v>75</v>
@@ -10974,7 +10974,7 @@
         <v>75</v>
       </c>
       <c r="AP85">
-        <v>0.1012</v>
+        <v>0.1011</v>
       </c>
     </row>
     <row r="86" spans="1:42" x14ac:dyDescent="0.25">
@@ -10994,7 +10994,7 @@
         <v>73.4375</v>
       </c>
       <c r="F86" s="1">
-        <v>9.9070000000000005E-2</v>
+        <v>9.9169999999999994E-2</v>
       </c>
       <c r="G86">
         <v>73.4375</v>
@@ -11084,7 +11084,7 @@
         <v>73.4375</v>
       </c>
       <c r="AJ86">
-        <v>9.9059999999999995E-2</v>
+        <v>9.912E-2</v>
       </c>
       <c r="AK86">
         <v>73.4375</v>
@@ -11122,7 +11122,7 @@
         <v>71.875</v>
       </c>
       <c r="F87" s="1">
-        <v>9.6930000000000002E-2</v>
+        <v>9.6829999999999999E-2</v>
       </c>
       <c r="G87">
         <v>71.875</v>
@@ -11212,7 +11212,7 @@
         <v>71.875</v>
       </c>
       <c r="AJ87">
-        <v>9.6909999999999996E-2</v>
+        <v>9.6820000000000003E-2</v>
       </c>
       <c r="AK87">
         <v>71.875</v>
@@ -11250,7 +11250,7 @@
         <v>70.3125</v>
       </c>
       <c r="F88">
-        <v>9.4780000000000003E-2</v>
+        <v>9.4979999999999995E-2</v>
       </c>
       <c r="G88">
         <v>70.3125</v>
@@ -11340,7 +11340,7 @@
         <v>70.3125</v>
       </c>
       <c r="AJ88">
-        <v>9.4769999999999993E-2</v>
+        <v>9.4740000000000005E-2</v>
       </c>
       <c r="AK88">
         <v>70.3125</v>
@@ -11468,7 +11468,7 @@
         <v>68.75</v>
       </c>
       <c r="AJ89">
-        <v>9.264E-2</v>
+        <v>9.2619999999999994E-2</v>
       </c>
       <c r="AK89">
         <v>68.75</v>
@@ -11486,7 +11486,7 @@
         <v>68.75</v>
       </c>
       <c r="AP89">
-        <v>9.2649999999999996E-2</v>
+        <v>9.2850000000000002E-2</v>
       </c>
     </row>
     <row r="90" spans="1:42" x14ac:dyDescent="0.25">
@@ -11506,7 +11506,7 @@
         <v>67.1875</v>
       </c>
       <c r="F90">
-        <v>9.0529999999999999E-2</v>
+        <v>9.0730000000000005E-2</v>
       </c>
       <c r="G90">
         <v>67.1875</v>
@@ -11596,7 +11596,7 @@
         <v>67.1875</v>
       </c>
       <c r="AJ90">
-        <v>9.0509999999999993E-2</v>
+        <v>9.0520000000000003E-2</v>
       </c>
       <c r="AK90">
         <v>67.1875</v>
@@ -11634,7 +11634,7 @@
         <v>65.625</v>
       </c>
       <c r="F91">
-        <v>8.8389999999999996E-2</v>
+        <v>8.8289999999999993E-2</v>
       </c>
       <c r="G91">
         <v>65.625</v>
@@ -11724,7 +11724,7 @@
         <v>65.625</v>
       </c>
       <c r="AJ91">
-        <v>8.838E-2</v>
+        <v>8.8359999999999994E-2</v>
       </c>
       <c r="AK91">
         <v>65.625</v>
@@ -11762,7 +11762,7 @@
         <v>64.0625</v>
       </c>
       <c r="F92">
-        <v>8.6269999999999999E-2</v>
+        <v>8.6069999999999994E-2</v>
       </c>
       <c r="G92">
         <v>64.0625</v>
@@ -11852,7 +11852,7 @@
         <v>64.0625</v>
       </c>
       <c r="AJ92">
-        <v>8.6249999999999993E-2</v>
+        <v>8.6220000000000005E-2</v>
       </c>
       <c r="AK92">
         <v>64.0625</v>
@@ -11870,7 +11870,7 @@
         <v>64.0625</v>
       </c>
       <c r="AP92">
-        <v>8.6260000000000003E-2</v>
+        <v>8.6459999999999995E-2</v>
       </c>
     </row>
     <row r="93" spans="1:42" x14ac:dyDescent="0.25">
@@ -11890,7 +11890,7 @@
         <v>62.5</v>
       </c>
       <c r="F93">
-        <v>8.4129999999999996E-2</v>
+        <v>8.3930000000000005E-2</v>
       </c>
       <c r="G93">
         <v>62.5</v>
@@ -11980,7 +11980,7 @@
         <v>62.5</v>
       </c>
       <c r="AJ93">
-        <v>8.412E-2</v>
+        <v>8.4159999999999999E-2</v>
       </c>
       <c r="AK93">
         <v>62.5</v>
@@ -11998,7 +11998,7 @@
         <v>62.5</v>
       </c>
       <c r="AP93">
-        <v>8.412E-2</v>
+        <v>8.4320000000000006E-2</v>
       </c>
     </row>
     <row r="94" spans="1:42" x14ac:dyDescent="0.25">
@@ -12018,7 +12018,7 @@
         <v>60.9375</v>
       </c>
       <c r="F94">
-        <v>8.201E-2</v>
+        <v>8.1909999999999997E-2</v>
       </c>
       <c r="G94">
         <v>60.9375</v>
@@ -12108,7 +12108,7 @@
         <v>60.9375</v>
       </c>
       <c r="AJ94">
-        <v>8.2000000000000003E-2</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="AK94">
         <v>60.9375</v>
@@ -12126,7 +12126,7 @@
         <v>60.9375</v>
       </c>
       <c r="AP94">
-        <v>8.2000000000000003E-2</v>
+        <v>8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="95" spans="1:42" x14ac:dyDescent="0.25">
@@ -12146,7 +12146,7 @@
         <v>59.375</v>
       </c>
       <c r="F95">
-        <v>7.9880000000000007E-2</v>
+        <v>7.9680000000000001E-2</v>
       </c>
       <c r="G95">
         <v>59.375</v>
@@ -12236,7 +12236,7 @@
         <v>59.375</v>
       </c>
       <c r="AJ95">
-        <v>7.9880000000000007E-2</v>
+        <v>7.9839999999999994E-2</v>
       </c>
       <c r="AK95">
         <v>59.375</v>
@@ -12364,7 +12364,7 @@
         <v>57.8125</v>
       </c>
       <c r="AJ96">
-        <v>7.7770000000000006E-2</v>
+        <v>7.7740000000000004E-2</v>
       </c>
       <c r="AK96">
         <v>57.8125</v>
@@ -12382,7 +12382,7 @@
         <v>57.8125</v>
       </c>
       <c r="AP96">
-        <v>7.7770000000000006E-2</v>
+        <v>7.7869999999999995E-2</v>
       </c>
     </row>
     <row r="97" spans="1:42" x14ac:dyDescent="0.25">
@@ -12492,7 +12492,7 @@
         <v>56.25</v>
       </c>
       <c r="AJ97">
-        <v>7.5649999999999995E-2</v>
+        <v>7.5620000000000007E-2</v>
       </c>
       <c r="AK97">
         <v>56.25</v>
@@ -12510,7 +12510,7 @@
         <v>56.25</v>
       </c>
       <c r="AP97">
-        <v>7.5660000000000005E-2</v>
+        <v>7.5459999999999999E-2</v>
       </c>
     </row>
     <row r="98" spans="1:42" x14ac:dyDescent="0.25">
@@ -12530,7 +12530,7 @@
         <v>54.6875</v>
       </c>
       <c r="F98">
-        <v>7.3550000000000004E-2</v>
+        <v>7.3649999999999993E-2</v>
       </c>
       <c r="G98">
         <v>54.6875</v>
@@ -12620,7 +12620,7 @@
         <v>54.6875</v>
       </c>
       <c r="AJ98">
-        <v>7.3539999999999994E-2</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="AK98">
         <v>54.6875</v>
@@ -12748,7 +12748,7 @@
         <v>53.125</v>
       </c>
       <c r="AJ99">
-        <v>7.1419999999999997E-2</v>
+        <v>7.1400000000000005E-2</v>
       </c>
       <c r="AK99">
         <v>53.125</v>
@@ -12876,7 +12876,7 @@
         <v>51.5625</v>
       </c>
       <c r="AJ100">
-        <v>6.9309999999999997E-2</v>
+        <v>6.9320000000000007E-2</v>
       </c>
       <c r="AK100">
         <v>51.5625</v>
@@ -12914,7 +12914,7 @@
         <v>50</v>
       </c>
       <c r="F101" s="1">
-        <v>6.7150000000000001E-2</v>
+        <v>6.7049999999999998E-2</v>
       </c>
       <c r="G101">
         <v>50</v>
@@ -13004,7 +13004,7 @@
         <v>50</v>
       </c>
       <c r="AJ101">
-        <v>6.7129999999999995E-2</v>
+        <v>6.7100000000000007E-2</v>
       </c>
       <c r="AK101">
         <v>50</v>
@@ -13022,7 +13022,7 @@
         <v>50</v>
       </c>
       <c r="AP101">
-        <v>6.7129999999999995E-2</v>
+        <v>6.6930000000000003E-2</v>
       </c>
     </row>
     <row r="102" spans="1:42" x14ac:dyDescent="0.25">
@@ -13042,7 +13042,7 @@
         <v>48.4375</v>
       </c>
       <c r="F102" s="1">
-        <v>6.5040000000000001E-2</v>
+        <v>6.5140000000000003E-2</v>
       </c>
       <c r="G102">
         <v>48.4375</v>
@@ -13132,7 +13132,7 @@
         <v>48.4375</v>
       </c>
       <c r="AJ102">
-        <v>6.5030000000000004E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="AK102">
         <v>48.4375</v>
@@ -13150,7 +13150,7 @@
         <v>48.4375</v>
       </c>
       <c r="AP102">
-        <v>6.5019999999999994E-2</v>
+        <v>6.4820000000000003E-2</v>
       </c>
     </row>
     <row r="103" spans="1:42" x14ac:dyDescent="0.25">
@@ -13170,7 +13170,7 @@
         <v>46.875</v>
       </c>
       <c r="F103">
-        <v>6.293E-2</v>
+        <v>6.2729999999999994E-2</v>
       </c>
       <c r="G103">
         <v>46.875</v>
@@ -13260,7 +13260,7 @@
         <v>46.875</v>
       </c>
       <c r="AJ103">
-        <v>6.2909999999999994E-2</v>
+        <v>6.2899999999999998E-2</v>
       </c>
       <c r="AK103">
         <v>46.875</v>
@@ -13278,7 +13278,7 @@
         <v>46.875</v>
       </c>
       <c r="AP103">
-        <v>6.2909999999999994E-2</v>
+        <v>6.3109999999999999E-2</v>
       </c>
     </row>
     <row r="104" spans="1:42" x14ac:dyDescent="0.25">
@@ -13388,7 +13388,7 @@
         <v>45.3125</v>
       </c>
       <c r="AJ104">
-        <v>6.0810000000000003E-2</v>
+        <v>6.0749999999999998E-2</v>
       </c>
       <c r="AK104">
         <v>45.3125</v>
@@ -13406,7 +13406,7 @@
         <v>45.3125</v>
       </c>
       <c r="AP104">
-        <v>6.0810000000000003E-2</v>
+        <v>6.1010000000000002E-2</v>
       </c>
     </row>
     <row r="105" spans="1:42" x14ac:dyDescent="0.25">
@@ -13426,7 +13426,7 @@
         <v>43.75</v>
       </c>
       <c r="F105" s="1">
-        <v>5.8720000000000001E-2</v>
+        <v>5.8819999999999997E-2</v>
       </c>
       <c r="G105">
         <v>43.75</v>
@@ -13516,7 +13516,7 @@
         <v>43.75</v>
       </c>
       <c r="AJ105">
-        <v>5.8709999999999998E-2</v>
+        <v>5.8700000000000002E-2</v>
       </c>
       <c r="AK105">
         <v>43.75</v>
@@ -13534,7 +13534,7 @@
         <v>43.75</v>
       </c>
       <c r="AP105">
-        <v>5.8709999999999998E-2</v>
+        <v>5.851E-2</v>
       </c>
     </row>
     <row r="106" spans="1:42" x14ac:dyDescent="0.25">
@@ -13554,7 +13554,7 @@
         <v>42.1875</v>
       </c>
       <c r="F106" s="1">
-        <v>5.6610000000000001E-2</v>
+        <v>5.6710000000000003E-2</v>
       </c>
       <c r="G106">
         <v>42.1875</v>
@@ -13644,7 +13644,7 @@
         <v>42.1875</v>
       </c>
       <c r="AJ106">
-        <v>5.6599999999999998E-2</v>
+        <v>5.654E-2</v>
       </c>
       <c r="AK106">
         <v>42.1875</v>
@@ -13662,7 +13662,7 @@
         <v>42.1875</v>
       </c>
       <c r="AP106">
-        <v>5.6599999999999998E-2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
     </row>
     <row r="107" spans="1:42" x14ac:dyDescent="0.25">
@@ -13682,7 +13682,7 @@
         <v>40.625</v>
       </c>
       <c r="F107">
-        <v>5.45E-2</v>
+        <v>5.4699999999999999E-2</v>
       </c>
       <c r="G107">
         <v>40.625</v>
@@ -13790,7 +13790,7 @@
         <v>40.625</v>
       </c>
       <c r="AP107">
-        <v>5.45E-2</v>
+        <v>5.4399999999999997E-2</v>
       </c>
     </row>
     <row r="108" spans="1:42" x14ac:dyDescent="0.25">
@@ -13810,7 +13810,7 @@
         <v>39.0625</v>
       </c>
       <c r="F108">
-        <v>5.2400000000000002E-2</v>
+        <v>5.2200000000000003E-2</v>
       </c>
       <c r="G108">
         <v>39.0625</v>
@@ -13900,7 +13900,7 @@
         <v>39.0625</v>
       </c>
       <c r="AJ108">
-        <v>5.2389999999999999E-2</v>
+        <v>5.2380000000000003E-2</v>
       </c>
       <c r="AK108">
         <v>39.0625</v>
@@ -13918,7 +13918,7 @@
         <v>39.0625</v>
       </c>
       <c r="AP108">
-        <v>5.2400000000000002E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
     </row>
     <row r="109" spans="1:42" x14ac:dyDescent="0.25">
@@ -14028,7 +14028,7 @@
         <v>37.5</v>
       </c>
       <c r="AJ109">
-        <v>5.0270000000000002E-2</v>
+        <v>5.0259999999999999E-2</v>
       </c>
       <c r="AK109">
         <v>37.5</v>
@@ -14066,7 +14066,7 @@
         <v>35.9375</v>
       </c>
       <c r="F110">
-        <v>4.8180000000000001E-2</v>
+        <v>4.8379999999999999E-2</v>
       </c>
       <c r="G110">
         <v>35.9375</v>
@@ -14156,7 +14156,7 @@
         <v>35.9375</v>
       </c>
       <c r="AJ110">
-        <v>4.8169999999999998E-2</v>
+        <v>4.8160000000000001E-2</v>
       </c>
       <c r="AK110">
         <v>35.9375</v>
@@ -14174,7 +14174,7 @@
         <v>35.9375</v>
       </c>
       <c r="AP110">
-        <v>4.8180000000000001E-2</v>
+        <v>4.8379999999999999E-2</v>
       </c>
     </row>
     <row r="111" spans="1:42" x14ac:dyDescent="0.25">
@@ -14194,7 +14194,7 @@
         <v>34.375</v>
       </c>
       <c r="F111">
-        <v>4.607E-2</v>
+        <v>4.5969999999999997E-2</v>
       </c>
       <c r="G111">
         <v>34.375</v>
@@ -14284,7 +14284,7 @@
         <v>34.375</v>
       </c>
       <c r="AJ111">
-        <v>4.607E-2</v>
+        <v>4.6080000000000003E-2</v>
       </c>
       <c r="AK111">
         <v>34.375</v>
@@ -14302,7 +14302,7 @@
         <v>34.375</v>
       </c>
       <c r="AP111">
-        <v>4.607E-2</v>
+        <v>4.6269999999999999E-2</v>
       </c>
     </row>
     <row r="112" spans="1:42" x14ac:dyDescent="0.25">
@@ -14430,7 +14430,7 @@
         <v>32.8125</v>
       </c>
       <c r="AP112">
-        <v>4.3970000000000002E-2</v>
+        <v>4.3770000000000003E-2</v>
       </c>
     </row>
     <row r="113" spans="1:42" x14ac:dyDescent="0.25">
@@ -14450,7 +14450,7 @@
         <v>31.25</v>
       </c>
       <c r="F113">
-        <v>4.1880000000000001E-2</v>
+        <v>4.1779999999999998E-2</v>
       </c>
       <c r="G113">
         <v>31.25</v>
@@ -14540,7 +14540,7 @@
         <v>31.25</v>
       </c>
       <c r="AJ113">
-        <v>4.1869999999999997E-2</v>
+        <v>4.1860000000000001E-2</v>
       </c>
       <c r="AK113">
         <v>31.25</v>
@@ -14558,7 +14558,7 @@
         <v>31.25</v>
       </c>
       <c r="AP113">
-        <v>4.1869999999999997E-2</v>
+        <v>4.197E-2</v>
       </c>
     </row>
     <row r="114" spans="1:42" x14ac:dyDescent="0.25">
@@ -14578,7 +14578,7 @@
         <v>29.6875</v>
       </c>
       <c r="F114">
-        <v>3.9780000000000003E-2</v>
+        <v>3.9980000000000002E-2</v>
       </c>
       <c r="G114">
         <v>29.6875</v>
@@ -14668,7 +14668,7 @@
         <v>29.6875</v>
       </c>
       <c r="AJ114">
-        <v>3.9759999999999997E-2</v>
+        <v>3.977E-2</v>
       </c>
       <c r="AK114">
         <v>29.6875</v>
@@ -14686,7 +14686,7 @@
         <v>29.6875</v>
       </c>
       <c r="AP114">
-        <v>3.9759999999999997E-2</v>
+        <v>3.9960000000000002E-2</v>
       </c>
     </row>
     <row r="115" spans="1:42" x14ac:dyDescent="0.25">
@@ -14706,7 +14706,7 @@
         <v>28.125</v>
       </c>
       <c r="F115">
-        <v>3.7670000000000002E-2</v>
+        <v>3.7769999999999998E-2</v>
       </c>
       <c r="G115">
         <v>28.125</v>
@@ -14796,7 +14796,7 @@
         <v>28.125</v>
       </c>
       <c r="AJ115">
-        <v>3.7650000000000003E-2</v>
+        <v>3.7699999999999997E-2</v>
       </c>
       <c r="AK115">
         <v>28.125</v>
@@ -14814,7 +14814,7 @@
         <v>28.125</v>
       </c>
       <c r="AP115">
-        <v>3.7659999999999999E-2</v>
+        <v>3.7760000000000002E-2</v>
       </c>
     </row>
     <row r="116" spans="1:42" x14ac:dyDescent="0.25">
@@ -14834,7 +14834,7 @@
         <v>26.5625</v>
       </c>
       <c r="F116">
-        <v>3.499E-2</v>
+        <v>3.5189999999999999E-2</v>
       </c>
       <c r="G116">
         <v>26.5625</v>
@@ -14924,7 +14924,7 @@
         <v>26.5625</v>
       </c>
       <c r="AJ116">
-        <v>3.5549999999999998E-2</v>
+        <v>3.5560000000000001E-2</v>
       </c>
       <c r="AK116">
         <v>26.5625</v>
@@ -14962,7 +14962,7 @@
         <v>25</v>
       </c>
       <c r="F117">
-        <v>3.3149999999999999E-2</v>
+        <v>3.3349999999999998E-2</v>
       </c>
       <c r="G117">
         <v>25</v>
@@ -15052,7 +15052,7 @@
         <v>25</v>
       </c>
       <c r="AJ117">
-        <v>3.347E-2</v>
+        <v>3.3419999999999998E-2</v>
       </c>
       <c r="AK117">
         <v>25</v>
@@ -15180,7 +15180,7 @@
         <v>23.4375</v>
       </c>
       <c r="AJ118">
-        <v>3.1359999999999999E-2</v>
+        <v>3.1320000000000001E-2</v>
       </c>
       <c r="AK118">
         <v>23.4375</v>
@@ -15198,7 +15198,7 @@
         <v>23.4375</v>
       </c>
       <c r="AP118">
-        <v>3.1379999999999998E-2</v>
+        <v>3.1579999999999997E-2</v>
       </c>
     </row>
     <row r="119" spans="1:42" x14ac:dyDescent="0.25">
@@ -15218,7 +15218,7 @@
         <v>21.875</v>
       </c>
       <c r="F119">
-        <v>2.7810000000000001E-2</v>
+        <v>2.7910000000000001E-2</v>
       </c>
       <c r="G119">
         <v>21.875</v>
@@ -15308,7 +15308,7 @@
         <v>21.875</v>
       </c>
       <c r="AJ119">
-        <v>2.9250000000000002E-2</v>
+        <v>2.9229999999999999E-2</v>
       </c>
       <c r="AK119">
         <v>21.875</v>
@@ -15326,7 +15326,7 @@
         <v>21.875</v>
       </c>
       <c r="AP119">
-        <v>2.9270000000000001E-2</v>
+        <v>2.947E-2</v>
       </c>
     </row>
     <row r="120" spans="1:42" x14ac:dyDescent="0.25">
@@ -15346,7 +15346,7 @@
         <v>20.3125</v>
       </c>
       <c r="F120">
-        <v>2.4969999999999999E-2</v>
+        <v>2.487E-2</v>
       </c>
       <c r="G120">
         <v>20.3125</v>
@@ -15436,7 +15436,7 @@
         <v>20.3125</v>
       </c>
       <c r="AJ120">
-        <v>2.7150000000000001E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="AK120">
         <v>20.3125</v>
@@ -15454,7 +15454,7 @@
         <v>20.3125</v>
       </c>
       <c r="AP120">
-        <v>2.717E-2</v>
+        <v>2.7269999999999999E-2</v>
       </c>
     </row>
     <row r="121" spans="1:42" x14ac:dyDescent="0.25">
@@ -15474,7 +15474,7 @@
         <v>18.75</v>
       </c>
       <c r="F121">
-        <v>2.1930000000000002E-2</v>
+        <v>2.1729999999999999E-2</v>
       </c>
       <c r="G121">
         <v>18.75</v>
@@ -15564,7 +15564,7 @@
         <v>18.75</v>
       </c>
       <c r="AJ121">
-        <v>2.5049999999999999E-2</v>
+        <v>2.5020000000000001E-2</v>
       </c>
       <c r="AK121">
         <v>18.75</v>
@@ -15692,7 +15692,7 @@
         <v>17.1875</v>
       </c>
       <c r="AJ122">
-        <v>2.2950000000000002E-2</v>
+        <v>2.2970000000000001E-2</v>
       </c>
       <c r="AK122">
         <v>17.1875</v>
@@ -15820,7 +15820,7 @@
         <v>15.625</v>
       </c>
       <c r="AJ123">
-        <v>2.0840000000000001E-2</v>
+        <v>2.0820000000000002E-2</v>
       </c>
       <c r="AK123">
         <v>15.625</v>
@@ -15838,7 +15838,7 @@
         <v>15.625</v>
       </c>
       <c r="AP123">
-        <v>2.085E-2</v>
+        <v>2.0650000000000002E-2</v>
       </c>
     </row>
     <row r="124" spans="1:42" x14ac:dyDescent="0.25">
@@ -15948,7 +15948,7 @@
         <v>14.0625</v>
       </c>
       <c r="AJ124">
-        <v>1.874E-2</v>
+        <v>1.8720000000000001E-2</v>
       </c>
       <c r="AK124">
         <v>14.0625</v>
@@ -15966,7 +15966,7 @@
         <v>14.0625</v>
       </c>
       <c r="AP124">
-        <v>1.874E-2</v>
+        <v>1.8939999999999999E-2</v>
       </c>
     </row>
     <row r="125" spans="1:42" x14ac:dyDescent="0.25">
@@ -16076,7 +16076,7 @@
         <v>12.5</v>
       </c>
       <c r="AJ125">
-        <v>1.6619999999999999E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="AK125">
         <v>12.5</v>
@@ -16094,7 +16094,7 @@
         <v>12.5</v>
       </c>
       <c r="AP125">
-        <v>1.66E-2</v>
+        <v>1.6400000000000001E-2</v>
       </c>
     </row>
     <row r="126" spans="1:42" x14ac:dyDescent="0.25">
@@ -16204,7 +16204,7 @@
         <v>10.9375</v>
       </c>
       <c r="AJ126">
-        <v>1.4449999999999999E-2</v>
+        <v>1.4420000000000001E-2</v>
       </c>
       <c r="AK126">
         <v>10.9375</v>
@@ -16222,7 +16222,7 @@
         <v>10.9375</v>
       </c>
       <c r="AP126">
-        <v>1.4069999999999999E-2</v>
+        <v>1.427E-2</v>
       </c>
     </row>
     <row r="127" spans="1:42" x14ac:dyDescent="0.25">
@@ -16332,7 +16332,7 @@
         <v>9.375</v>
       </c>
       <c r="AJ127">
-        <v>1.172E-2</v>
+        <v>1.171E-2</v>
       </c>
       <c r="AK127">
         <v>9.375</v>
@@ -16350,7 +16350,7 @@
         <v>9.375</v>
       </c>
       <c r="AP127">
-        <v>9.8300000000000002E-3</v>
+        <v>9.9299999999999996E-3</v>
       </c>
     </row>
     <row r="128" spans="1:42" x14ac:dyDescent="0.25">
@@ -16478,7 +16478,7 @@
         <v>7.8125</v>
       </c>
       <c r="AP128">
-        <v>3.9899999999999996E-3</v>
+        <v>4.1900000000000001E-3</v>
       </c>
     </row>
     <row r="129" spans="1:44" x14ac:dyDescent="0.25">
@@ -17889,7 +17889,7 @@
         <v>-9.375</v>
       </c>
       <c r="AP139">
-        <v>-1.217E-2</v>
+        <v>-1.227E-2</v>
       </c>
     </row>
     <row r="140" spans="1:44" x14ac:dyDescent="0.25">
@@ -18145,7 +18145,7 @@
         <v>-12.5</v>
       </c>
       <c r="AP141">
-        <v>-1.643E-2</v>
+        <v>-1.6230000000000001E-2</v>
       </c>
     </row>
     <row r="142" spans="1:44" x14ac:dyDescent="0.25">
@@ -18273,7 +18273,7 @@
         <v>-14.0625</v>
       </c>
       <c r="AP142">
-        <v>-1.8960000000000001E-2</v>
+        <v>-1.916E-2</v>
       </c>
     </row>
     <row r="143" spans="1:44" x14ac:dyDescent="0.25">
@@ -18529,7 +18529,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AP144">
-        <v>-2.3189999999999999E-2</v>
+        <v>-2.3290000000000002E-2</v>
       </c>
     </row>
     <row r="145" spans="1:42" x14ac:dyDescent="0.25">
@@ -18657,7 +18657,7 @@
         <v>-18.75</v>
       </c>
       <c r="AP145">
-        <v>-2.53E-2</v>
+        <v>-2.52E-2</v>
       </c>
     </row>
     <row r="146" spans="1:42" x14ac:dyDescent="0.25">
@@ -18767,7 +18767,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AJ146">
-        <v>-2.741E-2</v>
+        <v>-2.742E-2</v>
       </c>
       <c r="AK146">
         <v>-20.3125</v>
@@ -18785,7 +18785,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AP146">
-        <v>-2.7390000000000001E-2</v>
+        <v>-2.7289999999999998E-2</v>
       </c>
     </row>
     <row r="147" spans="1:42" x14ac:dyDescent="0.25">
@@ -18895,7 +18895,7 @@
         <v>-21.875</v>
       </c>
       <c r="AJ147">
-        <v>-2.9510000000000002E-2</v>
+        <v>-2.9520000000000001E-2</v>
       </c>
       <c r="AK147">
         <v>-21.875</v>
@@ -18913,7 +18913,7 @@
         <v>-21.875</v>
       </c>
       <c r="AP147">
-        <v>-2.9489999999999999E-2</v>
+        <v>-2.9590000000000002E-2</v>
       </c>
     </row>
     <row r="148" spans="1:42" x14ac:dyDescent="0.25">
@@ -19041,7 +19041,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AP148">
-        <v>-3.1600000000000003E-2</v>
+        <v>-3.1399999999999997E-2</v>
       </c>
     </row>
     <row r="149" spans="1:42" x14ac:dyDescent="0.25">
@@ -19169,7 +19169,7 @@
         <v>-25</v>
       </c>
       <c r="AP149">
-        <v>-3.3700000000000001E-2</v>
+        <v>-3.3799999999999997E-2</v>
       </c>
     </row>
     <row r="150" spans="1:42" x14ac:dyDescent="0.25">
@@ -19279,7 +19279,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AJ150">
-        <v>-3.5819999999999998E-2</v>
+        <v>-3.5830000000000001E-2</v>
       </c>
       <c r="AK150">
         <v>-26.5625</v>
@@ -19297,7 +19297,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AP150">
-        <v>-3.5799999999999998E-2</v>
+        <v>-3.5999999999999997E-2</v>
       </c>
     </row>
     <row r="151" spans="1:42" x14ac:dyDescent="0.25">
@@ -19407,7 +19407,7 @@
         <v>-28.125</v>
       </c>
       <c r="AJ151">
-        <v>-3.7920000000000002E-2</v>
+        <v>-3.7900000000000003E-2</v>
       </c>
       <c r="AK151">
         <v>-28.125</v>
@@ -19425,7 +19425,7 @@
         <v>-28.125</v>
       </c>
       <c r="AP151">
-        <v>-3.7900000000000003E-2</v>
+        <v>-3.78E-2</v>
       </c>
     </row>
     <row r="152" spans="1:42" x14ac:dyDescent="0.25">
@@ -19535,7 +19535,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AJ152">
-        <v>-4.0030000000000003E-2</v>
+        <v>-4.0009999999999997E-2</v>
       </c>
       <c r="AK152">
         <v>-29.6875</v>
@@ -19663,7 +19663,7 @@
         <v>-31.25</v>
       </c>
       <c r="AJ153">
-        <v>-4.2119999999999998E-2</v>
+        <v>-4.2099999999999999E-2</v>
       </c>
       <c r="AK153">
         <v>-31.25</v>
@@ -19681,7 +19681,7 @@
         <v>-31.25</v>
       </c>
       <c r="AP153">
-        <v>-4.2110000000000002E-2</v>
+        <v>-4.1910000000000003E-2</v>
       </c>
     </row>
     <row r="154" spans="1:42" x14ac:dyDescent="0.25">
@@ -19809,7 +19809,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AP154">
-        <v>-4.4209999999999999E-2</v>
+        <v>-4.4010000000000001E-2</v>
       </c>
     </row>
     <row r="155" spans="1:42" x14ac:dyDescent="0.25">
@@ -20047,7 +20047,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AJ156">
-        <v>-4.8430000000000001E-2</v>
+        <v>-4.8419999999999998E-2</v>
       </c>
       <c r="AK156">
         <v>-35.9375</v>
@@ -20065,7 +20065,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AP156">
-        <v>-4.8419999999999998E-2</v>
+        <v>-4.8520000000000001E-2</v>
       </c>
     </row>
     <row r="157" spans="1:42" x14ac:dyDescent="0.25">
@@ -20175,7 +20175,7 @@
         <v>-37.5</v>
       </c>
       <c r="AJ157">
-        <v>-5.0529999999999999E-2</v>
+        <v>-5.0520000000000002E-2</v>
       </c>
       <c r="AK157">
         <v>-37.5</v>
@@ -20193,7 +20193,7 @@
         <v>-37.5</v>
       </c>
       <c r="AP157">
-        <v>-5.0509999999999999E-2</v>
+        <v>-5.0310000000000001E-2</v>
       </c>
     </row>
     <row r="158" spans="1:42" x14ac:dyDescent="0.25">
@@ -20303,7 +20303,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AJ158">
-        <v>-5.2650000000000002E-2</v>
+        <v>-5.262E-2</v>
       </c>
       <c r="AK158">
         <v>-39.0625</v>
@@ -20321,7 +20321,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AP158">
-        <v>-5.2630000000000003E-2</v>
+        <v>-5.253E-2</v>
       </c>
     </row>
     <row r="159" spans="1:42" x14ac:dyDescent="0.25">
@@ -20431,7 +20431,7 @@
         <v>-40.625</v>
       </c>
       <c r="AJ159">
-        <v>-5.4739999999999997E-2</v>
+        <v>-5.4719999999999998E-2</v>
       </c>
       <c r="AK159">
         <v>-40.625</v>
@@ -20449,7 +20449,7 @@
         <v>-40.625</v>
       </c>
       <c r="AP159">
-        <v>-5.4730000000000001E-2</v>
+        <v>-5.4530000000000002E-2</v>
       </c>
     </row>
     <row r="160" spans="1:42" x14ac:dyDescent="0.25">
@@ -20559,7 +20559,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AJ160">
-        <v>-5.6849999999999998E-2</v>
+        <v>-5.6820000000000002E-2</v>
       </c>
       <c r="AK160">
         <v>-42.1875</v>
@@ -20687,7 +20687,7 @@
         <v>-43.75</v>
       </c>
       <c r="AJ161">
-        <v>-5.8959999999999999E-2</v>
+        <v>-5.892E-2</v>
       </c>
       <c r="AK161">
         <v>-43.75</v>
@@ -20705,7 +20705,7 @@
         <v>-43.75</v>
       </c>
       <c r="AP161">
-        <v>-5.8939999999999999E-2</v>
+        <v>-5.9139999999999998E-2</v>
       </c>
     </row>
     <row r="162" spans="1:42" x14ac:dyDescent="0.25">
@@ -20815,7 +20815,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AJ162" s="1">
-        <v>-6.1060000000000003E-2</v>
+        <v>-6.105E-2</v>
       </c>
       <c r="AK162">
         <v>-45.3125</v>
@@ -20833,7 +20833,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AP162">
-        <v>-6.1039999999999997E-2</v>
+        <v>-6.114E-2</v>
       </c>
     </row>
     <row r="163" spans="1:42" x14ac:dyDescent="0.25">
@@ -20943,7 +20943,7 @@
         <v>-46.875</v>
       </c>
       <c r="AJ163">
-        <v>-6.3170000000000004E-2</v>
+        <v>-6.3109999999999999E-2</v>
       </c>
       <c r="AK163">
         <v>-46.875</v>
@@ -20961,7 +20961,7 @@
         <v>-46.875</v>
       </c>
       <c r="AP163">
-        <v>-6.3140000000000002E-2</v>
+        <v>-6.2939999999999996E-2</v>
       </c>
     </row>
     <row r="164" spans="1:42" x14ac:dyDescent="0.25">
@@ -21071,7 +21071,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AJ164">
-        <v>-6.5280000000000005E-2</v>
+        <v>-6.5269999999999995E-2</v>
       </c>
       <c r="AK164">
         <v>-48.4375</v>
@@ -21089,7 +21089,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AP164">
-        <v>-6.5250000000000002E-2</v>
+        <v>-6.5049999999999997E-2</v>
       </c>
     </row>
     <row r="165" spans="1:42" x14ac:dyDescent="0.25">
@@ -21199,7 +21199,7 @@
         <v>-50</v>
       </c>
       <c r="AJ165">
-        <v>-6.7379999999999995E-2</v>
+        <v>-6.7349999999999993E-2</v>
       </c>
       <c r="AK165">
         <v>-50</v>
@@ -21345,7 +21345,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AP166">
-        <v>-6.9529999999999995E-2</v>
+        <v>-6.973E-2</v>
       </c>
     </row>
     <row r="167" spans="1:42" x14ac:dyDescent="0.25">
@@ -21365,7 +21365,7 @@
         <v>-53.125</v>
       </c>
       <c r="F167">
-        <v>-7.1639999999999995E-2</v>
+        <v>-7.1840000000000001E-2</v>
       </c>
       <c r="G167">
         <v>-53.125</v>
@@ -21455,7 +21455,7 @@
         <v>-53.125</v>
       </c>
       <c r="AJ167">
-        <v>-7.1669999999999998E-2</v>
+        <v>-7.1679999999999994E-2</v>
       </c>
       <c r="AK167">
         <v>-53.125</v>
@@ -21473,7 +21473,7 @@
         <v>-53.125</v>
       </c>
       <c r="AP167">
-        <v>-7.1639999999999995E-2</v>
+        <v>-7.1739999999999998E-2</v>
       </c>
     </row>
     <row r="168" spans="1:42" x14ac:dyDescent="0.25">
@@ -21583,7 +21583,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AJ168">
-        <v>-7.3779999999999998E-2</v>
+        <v>-7.3800000000000004E-2</v>
       </c>
       <c r="AK168">
         <v>-54.6875</v>
@@ -21621,7 +21621,7 @@
         <v>-56.25</v>
       </c>
       <c r="F169">
-        <v>-7.5859999999999997E-2</v>
+        <v>-7.596E-2</v>
       </c>
       <c r="G169">
         <v>-56.25</v>
@@ -21711,7 +21711,7 @@
         <v>-56.25</v>
       </c>
       <c r="AJ169">
-        <v>-7.5899999999999995E-2</v>
+        <v>-7.5999999999999998E-2</v>
       </c>
       <c r="AK169">
         <v>-56.25</v>
@@ -21839,7 +21839,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AJ170">
-        <v>-7.8E-2</v>
+        <v>-7.7799999999999994E-2</v>
       </c>
       <c r="AK170">
         <v>-57.8125</v>
@@ -21857,7 +21857,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AP170">
-        <v>-7.7969999999999998E-2</v>
+        <v>-7.7869999999999995E-2</v>
       </c>
     </row>
     <row r="171" spans="1:42" x14ac:dyDescent="0.25">
@@ -21877,7 +21877,7 @@
         <v>-59.375</v>
       </c>
       <c r="F171">
-        <v>-8.0089999999999995E-2</v>
+        <v>-7.9890000000000003E-2</v>
       </c>
       <c r="G171">
         <v>-59.375</v>
@@ -21967,7 +21967,7 @@
         <v>-59.375</v>
       </c>
       <c r="AJ171">
-        <v>-8.0110000000000001E-2</v>
+        <v>-8.0119999999999997E-2</v>
       </c>
       <c r="AK171">
         <v>-59.375</v>
@@ -21985,7 +21985,7 @@
         <v>-59.375</v>
       </c>
       <c r="AP171">
-        <v>-8.0079999999999998E-2</v>
+        <v>-8.0180000000000001E-2</v>
       </c>
     </row>
     <row r="172" spans="1:42" x14ac:dyDescent="0.25">
@@ -22005,7 +22005,7 @@
         <v>-60.9375</v>
       </c>
       <c r="F172">
-        <v>-8.2210000000000005E-2</v>
+        <v>-8.2409999999999997E-2</v>
       </c>
       <c r="G172">
         <v>-60.9375</v>
@@ -22095,7 +22095,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AJ172">
-        <v>-8.2229999999999998E-2</v>
+        <v>-8.2280000000000006E-2</v>
       </c>
       <c r="AK172">
         <v>-60.9375</v>
@@ -22113,7 +22113,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AP172">
-        <v>-8.2210000000000005E-2</v>
+        <v>-8.2409999999999997E-2</v>
       </c>
     </row>
     <row r="173" spans="1:42" x14ac:dyDescent="0.25">
@@ -22133,7 +22133,7 @@
         <v>-62.5</v>
       </c>
       <c r="F173">
-        <v>-8.4330000000000002E-2</v>
+        <v>-8.4529999999999994E-2</v>
       </c>
       <c r="G173">
         <v>-62.5</v>
@@ -22223,7 +22223,7 @@
         <v>-62.5</v>
       </c>
       <c r="AJ173">
-        <v>-8.4349999999999994E-2</v>
+        <v>-8.4320000000000006E-2</v>
       </c>
       <c r="AK173">
         <v>-62.5</v>
@@ -22241,7 +22241,7 @@
         <v>-62.5</v>
       </c>
       <c r="AP173">
-        <v>-8.4320000000000006E-2</v>
+        <v>-8.4519999999999998E-2</v>
       </c>
     </row>
     <row r="174" spans="1:42" x14ac:dyDescent="0.25">
@@ -22261,7 +22261,7 @@
         <v>-64.0625</v>
       </c>
       <c r="F174">
-        <v>-8.6470000000000005E-2</v>
+        <v>-8.6669999999999997E-2</v>
       </c>
       <c r="G174">
         <v>-64.0625</v>
@@ -22351,7 +22351,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AJ174">
-        <v>-8.6489999999999997E-2</v>
+        <v>-8.6480000000000001E-2</v>
       </c>
       <c r="AK174">
         <v>-64.0625</v>
@@ -22369,7 +22369,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AP174">
-        <v>-8.6459999999999995E-2</v>
+        <v>-8.6260000000000003E-2</v>
       </c>
     </row>
     <row r="175" spans="1:42" x14ac:dyDescent="0.25">
@@ -22479,7 +22479,7 @@
         <v>-65.625</v>
       </c>
       <c r="AJ175">
-        <v>-8.8620000000000004E-2</v>
+        <v>-8.8609999999999994E-2</v>
       </c>
       <c r="AK175">
         <v>-65.625</v>
@@ -22497,7 +22497,7 @@
         <v>-65.625</v>
       </c>
       <c r="AP175">
-        <v>-8.8569999999999996E-2</v>
+        <v>-8.8770000000000002E-2</v>
       </c>
     </row>
     <row r="176" spans="1:42" x14ac:dyDescent="0.25">
@@ -22517,7 +22517,7 @@
         <v>-67.1875</v>
       </c>
       <c r="F176">
-        <v>-9.0709999999999999E-2</v>
+        <v>-9.0910000000000005E-2</v>
       </c>
       <c r="G176">
         <v>-67.1875</v>
@@ -22607,7 +22607,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AJ176">
-        <v>-9.0749999999999997E-2</v>
+        <v>-9.0719999999999995E-2</v>
       </c>
       <c r="AK176">
         <v>-67.1875</v>
@@ -22625,7 +22625,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AP176">
-        <v>-9.0709999999999999E-2</v>
+        <v>-9.0609999999999996E-2</v>
       </c>
     </row>
     <row r="177" spans="1:42" x14ac:dyDescent="0.25">
@@ -22645,7 +22645,7 @@
         <v>-68.75</v>
       </c>
       <c r="F177">
-        <v>-9.2840000000000006E-2</v>
+        <v>-9.2740000000000003E-2</v>
       </c>
       <c r="G177">
         <v>-68.75</v>
@@ -22735,7 +22735,7 @@
         <v>-68.75</v>
       </c>
       <c r="AJ177">
-        <v>-9.2869999999999994E-2</v>
+        <v>-9.2859999999999998E-2</v>
       </c>
       <c r="AK177">
         <v>-68.75</v>
@@ -22863,7 +22863,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AJ178">
-        <v>-9.5000000000000001E-2</v>
+        <v>-9.5100000000000004E-2</v>
       </c>
       <c r="AK178">
         <v>-70.3125</v>
@@ -22901,7 +22901,7 @@
         <v>-71.875</v>
       </c>
       <c r="F179">
-        <v>-9.7089999999999996E-2</v>
+        <v>-9.6990000000000007E-2</v>
       </c>
       <c r="G179">
         <v>-71.875</v>
@@ -22991,7 +22991,7 @@
         <v>-71.875</v>
       </c>
       <c r="AJ179">
-        <v>-9.7119999999999998E-2</v>
+        <v>-9.7129999999999994E-2</v>
       </c>
       <c r="AK179">
         <v>-71.875</v>
@@ -23009,7 +23009,7 @@
         <v>-71.875</v>
       </c>
       <c r="AP179">
-        <v>-9.7100000000000006E-2</v>
+        <v>-9.7199999999999995E-2</v>
       </c>
     </row>
     <row r="180" spans="1:42" x14ac:dyDescent="0.25">
@@ -23119,7 +23119,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AJ180">
-        <v>-9.9260000000000001E-2</v>
+        <v>-9.9299999999999999E-2</v>
       </c>
       <c r="AK180">
         <v>-73.4375</v>
@@ -23247,7 +23247,7 @@
         <v>-75</v>
       </c>
       <c r="AJ181">
-        <v>-0.1014</v>
+        <v>-0.1012</v>
       </c>
       <c r="AK181">
         <v>-75</v>
@@ -23265,7 +23265,7 @@
         <v>-75</v>
       </c>
       <c r="AP181">
-        <v>-0.10138</v>
+        <v>-0.10118000000000001</v>
       </c>
     </row>
     <row r="182" spans="1:42" x14ac:dyDescent="0.25">
@@ -23285,7 +23285,7 @@
         <v>-76.5625</v>
       </c>
       <c r="F182">
-        <v>-0.10349</v>
+        <v>-0.10339</v>
       </c>
       <c r="G182">
         <v>-76.5625</v>
@@ -23375,7 +23375,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AJ182">
-        <v>-0.10353999999999999</v>
+        <v>-0.10356</v>
       </c>
       <c r="AK182">
         <v>-76.5625</v>
@@ -23393,7 +23393,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AP182">
-        <v>-0.10353</v>
+        <v>-0.10363</v>
       </c>
     </row>
     <row r="183" spans="1:42" x14ac:dyDescent="0.25">
@@ -23413,7 +23413,7 @@
         <v>-78.125</v>
       </c>
       <c r="F183">
-        <v>-0.10564</v>
+        <v>-0.10544000000000001</v>
       </c>
       <c r="G183">
         <v>-78.125</v>
@@ -23503,7 +23503,7 @@
         <v>-78.125</v>
       </c>
       <c r="AJ183">
-        <v>-0.10569000000000001</v>
+        <v>-0.10568</v>
       </c>
       <c r="AK183">
         <v>-78.125</v>
@@ -23521,7 +23521,7 @@
         <v>-78.125</v>
       </c>
       <c r="AP183">
-        <v>-0.10566</v>
+        <v>-0.10586</v>
       </c>
     </row>
     <row r="184" spans="1:42" x14ac:dyDescent="0.25">
@@ -23631,7 +23631,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AJ184">
-        <v>-0.10784000000000001</v>
+        <v>-0.10782</v>
       </c>
       <c r="AK184">
         <v>-79.6875</v>
@@ -23649,7 +23649,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AP184">
-        <v>-0.10782</v>
+        <v>-0.10772</v>
       </c>
     </row>
     <row r="185" spans="1:42" x14ac:dyDescent="0.25">
@@ -23669,7 +23669,7 @@
         <v>-81.25</v>
       </c>
       <c r="F185">
-        <v>-0.10994</v>
+        <v>-0.10983999999999999</v>
       </c>
       <c r="G185">
         <v>-81.25</v>
@@ -23759,7 +23759,7 @@
         <v>-81.25</v>
       </c>
       <c r="AJ185">
-        <v>-0.10999</v>
+        <v>-0.10997999999999999</v>
       </c>
       <c r="AK185">
         <v>-81.25</v>
@@ -23777,7 +23777,7 @@
         <v>-81.25</v>
       </c>
       <c r="AP185">
-        <v>-0.10996</v>
+        <v>-0.11006000000000001</v>
       </c>
     </row>
     <row r="186" spans="1:42" x14ac:dyDescent="0.25">
@@ -23797,7 +23797,7 @@
         <v>-82.8125</v>
       </c>
       <c r="F186">
-        <v>-0.11210000000000001</v>
+        <v>-0.1119</v>
       </c>
       <c r="G186">
         <v>-82.8125</v>
@@ -23887,7 +23887,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AJ186">
-        <v>-0.11215</v>
+        <v>-0.11214</v>
       </c>
       <c r="AK186">
         <v>-82.8125</v>
@@ -23905,7 +23905,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AP186">
-        <v>-0.11212</v>
+        <v>-0.11192000000000001</v>
       </c>
     </row>
     <row r="187" spans="1:42" x14ac:dyDescent="0.25">
@@ -23925,7 +23925,7 @@
         <v>-84.375</v>
       </c>
       <c r="F187">
-        <v>-0.11425</v>
+        <v>-0.11434999999999999</v>
       </c>
       <c r="G187">
         <v>-84.375</v>
@@ -24015,7 +24015,7 @@
         <v>-84.375</v>
       </c>
       <c r="AJ187">
-        <v>-0.11430999999999999</v>
+        <v>-0.11432</v>
       </c>
       <c r="AK187">
         <v>-84.375</v>
@@ -24053,7 +24053,7 @@
         <v>-85.9375</v>
       </c>
       <c r="F188">
-        <v>-0.11644</v>
+        <v>-0.11663999999999999</v>
       </c>
       <c r="G188">
         <v>-85.9375</v>
@@ -24143,7 +24143,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AJ188">
-        <v>-0.11647</v>
+        <v>-0.11642</v>
       </c>
       <c r="AK188">
         <v>-85.9375</v>
@@ -24161,7 +24161,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AP188">
-        <v>-0.11645</v>
+        <v>-0.11635</v>
       </c>
     </row>
     <row r="189" spans="1:42" x14ac:dyDescent="0.25">
@@ -24181,7 +24181,7 @@
         <v>-87.5</v>
       </c>
       <c r="F189">
-        <v>-0.1186</v>
+        <v>-0.1187</v>
       </c>
       <c r="G189">
         <v>-87.5</v>
@@ -24271,7 +24271,7 @@
         <v>-87.5</v>
       </c>
       <c r="AJ189">
-        <v>-0.11863</v>
+        <v>-0.11862</v>
       </c>
       <c r="AK189">
         <v>-87.5</v>
@@ -24309,7 +24309,7 @@
         <v>-89.0625</v>
       </c>
       <c r="F190">
-        <v>-0.12078999999999999</v>
+        <v>-0.12089</v>
       </c>
       <c r="G190">
         <v>-89.0625</v>
@@ -24399,7 +24399,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AJ190">
-        <v>-0.12082</v>
+        <v>-0.12081</v>
       </c>
       <c r="AK190">
         <v>-89.0625</v>
@@ -24437,7 +24437,7 @@
         <v>-90.625</v>
       </c>
       <c r="F191">
-        <v>-0.12298000000000001</v>
+        <v>-0.12318</v>
       </c>
       <c r="G191">
         <v>-90.625</v>
@@ -24527,7 +24527,7 @@
         <v>-90.625</v>
       </c>
       <c r="AJ191">
-        <v>-0.12300999999999999</v>
+        <v>-0.12302</v>
       </c>
       <c r="AK191">
         <v>-90.625</v>
@@ -24545,7 +24545,7 @@
         <v>-90.625</v>
       </c>
       <c r="AP191">
-        <v>-0.12298000000000001</v>
+        <v>-0.12278</v>
       </c>
     </row>
     <row r="192" spans="1:42" x14ac:dyDescent="0.25">
@@ -24565,7 +24565,7 @@
         <v>-92.1875</v>
       </c>
       <c r="F192">
-        <v>-0.12518000000000001</v>
+        <v>-0.12528</v>
       </c>
       <c r="G192">
         <v>-92.1875</v>
@@ -24655,7 +24655,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AJ192">
-        <v>-0.12520999999999999</v>
+        <v>-0.12522</v>
       </c>
       <c r="AK192">
         <v>-92.1875</v>
@@ -24673,7 +24673,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AP192">
-        <v>-0.12519</v>
+        <v>-0.12499</v>
       </c>
     </row>
     <row r="193" spans="1:42" x14ac:dyDescent="0.25">
@@ -24693,7 +24693,7 @@
         <v>-93.75</v>
       </c>
       <c r="F193">
-        <v>-0.12736</v>
+        <v>-0.12716</v>
       </c>
       <c r="G193">
         <v>-93.75</v>
@@ -24783,7 +24783,7 @@
         <v>-93.75</v>
       </c>
       <c r="AJ193">
-        <v>-0.12740000000000001</v>
+        <v>-0.1275</v>
       </c>
       <c r="AK193">
         <v>-93.75</v>
@@ -24801,7 +24801,7 @@
         <v>-93.75</v>
       </c>
       <c r="AP193">
-        <v>-0.12737000000000001</v>
+        <v>-0.12726999999999999</v>
       </c>
     </row>
     <row r="194" spans="1:42" x14ac:dyDescent="0.25">
@@ -24821,7 +24821,7 @@
         <v>-95.3125</v>
       </c>
       <c r="F194">
-        <v>-0.12956000000000001</v>
+        <v>-0.12936</v>
       </c>
       <c r="G194">
         <v>-95.3125</v>
@@ -24911,7 +24911,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AJ194">
-        <v>-0.12959000000000001</v>
+        <v>-0.12958</v>
       </c>
       <c r="AK194">
         <v>-95.3125</v>
@@ -24929,7 +24929,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AP194">
-        <v>-0.12956000000000001</v>
+        <v>-0.12966</v>
       </c>
     </row>
     <row r="195" spans="1:42" x14ac:dyDescent="0.25">
@@ -24949,7 +24949,7 @@
         <v>-96.875</v>
       </c>
       <c r="F195">
-        <v>-0.13177</v>
+        <v>-0.13186999999999999</v>
       </c>
       <c r="G195">
         <v>-96.875</v>
@@ -25039,7 +25039,7 @@
         <v>-96.875</v>
       </c>
       <c r="AJ195">
-        <v>-0.13178999999999999</v>
+        <v>-0.13177</v>
       </c>
       <c r="AK195">
         <v>-96.875</v>
@@ -25057,7 +25057,7 @@
         <v>-96.875</v>
       </c>
       <c r="AP195">
-        <v>-0.13177</v>
+        <v>-0.13186999999999999</v>
       </c>
     </row>
     <row r="196" spans="1:42" x14ac:dyDescent="0.25">
@@ -25185,7 +25185,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AP196">
-        <v>-0.13400000000000001</v>
+        <v>-0.13420000000000001</v>
       </c>
     </row>
     <row r="197" spans="1:42" x14ac:dyDescent="0.25">
@@ -25205,7 +25205,7 @@
         <v>-100</v>
       </c>
       <c r="F197">
-        <v>-0.13594000000000001</v>
+        <v>-0.13574</v>
       </c>
       <c r="G197">
         <v>-100</v>
@@ -25295,7 +25295,7 @@
         <v>-100</v>
       </c>
       <c r="AJ197">
-        <v>-0.13597999999999999</v>
+        <v>-0.13597000000000001</v>
       </c>
       <c r="AK197">
         <v>-100</v>
@@ -25313,7 +25313,7 @@
         <v>-100</v>
       </c>
       <c r="AP197">
-        <v>-0.13596</v>
+        <v>-0.13575999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:42" x14ac:dyDescent="0.25">
@@ -25423,7 +25423,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AJ198">
-        <v>-0.13385</v>
+        <v>-0.13386000000000001</v>
       </c>
       <c r="AK198">
         <v>-98.4375</v>
@@ -25461,7 +25461,7 @@
         <v>-96.875</v>
       </c>
       <c r="F199">
-        <v>-0.13161999999999999</v>
+        <v>-0.13152</v>
       </c>
       <c r="G199">
         <v>-96.875</v>
@@ -25551,7 +25551,7 @@
         <v>-96.875</v>
       </c>
       <c r="AJ199">
-        <v>-0.13164999999999999</v>
+        <v>-0.13167999999999999</v>
       </c>
       <c r="AK199">
         <v>-96.875</v>
@@ -25569,7 +25569,7 @@
         <v>-96.875</v>
       </c>
       <c r="AP199">
-        <v>-0.13163</v>
+        <v>-0.13183</v>
       </c>
     </row>
     <row r="200" spans="1:42" x14ac:dyDescent="0.25">
@@ -25589,7 +25589,7 @@
         <v>-95.3125</v>
       </c>
       <c r="F200">
-        <v>-0.12941</v>
+        <v>-0.12961</v>
       </c>
       <c r="G200">
         <v>-95.3125</v>
@@ -25679,7 +25679,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AJ200">
-        <v>-0.12944</v>
+        <v>-0.12945000000000001</v>
       </c>
       <c r="AK200">
         <v>-95.3125</v>
@@ -25717,7 +25717,7 @@
         <v>-93.75</v>
       </c>
       <c r="F201">
-        <v>-0.12719</v>
+        <v>-0.12709000000000001</v>
       </c>
       <c r="G201">
         <v>-93.75</v>
@@ -25807,7 +25807,7 @@
         <v>-93.75</v>
       </c>
       <c r="AJ201">
-        <v>-0.12725</v>
+        <v>-0.12728</v>
       </c>
       <c r="AK201">
         <v>-93.75</v>
@@ -25845,7 +25845,7 @@
         <v>-92.1875</v>
       </c>
       <c r="F202">
-        <v>-0.12501000000000001</v>
+        <v>-0.12481</v>
       </c>
       <c r="G202">
         <v>-92.1875</v>
@@ -25935,7 +25935,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AJ202">
-        <v>-0.12506</v>
+        <v>-0.12506999999999999</v>
       </c>
       <c r="AK202">
         <v>-92.1875</v>
@@ -25973,7 +25973,7 @@
         <v>-90.625</v>
       </c>
       <c r="F203">
-        <v>-0.12282</v>
+        <v>-0.12262000000000001</v>
       </c>
       <c r="G203">
         <v>-90.625</v>
@@ -26063,7 +26063,7 @@
         <v>-90.625</v>
       </c>
       <c r="AJ203">
-        <v>-0.12285</v>
+        <v>-0.12286999999999999</v>
       </c>
       <c r="AK203">
         <v>-90.625</v>
@@ -26081,7 +26081,7 @@
         <v>-90.625</v>
       </c>
       <c r="AP203">
-        <v>-0.12282999999999999</v>
+        <v>-0.12293</v>
       </c>
     </row>
     <row r="204" spans="1:42" x14ac:dyDescent="0.25">
@@ -26101,7 +26101,7 @@
         <v>-89.0625</v>
       </c>
       <c r="F204">
-        <v>-0.12064</v>
+        <v>-0.12053999999999999</v>
       </c>
       <c r="G204">
         <v>-89.0625</v>
@@ -26191,7 +26191,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AJ204">
-        <v>-0.12067</v>
+        <v>-0.12064999999999999</v>
       </c>
       <c r="AK204">
         <v>-89.0625</v>
@@ -26209,7 +26209,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AP204">
-        <v>-0.12064</v>
+        <v>-0.12044000000000001</v>
       </c>
     </row>
     <row r="205" spans="1:42" x14ac:dyDescent="0.25">
@@ -26229,7 +26229,7 @@
         <v>-87.5</v>
       </c>
       <c r="F205">
-        <v>-0.11844</v>
+        <v>-0.11834</v>
       </c>
       <c r="G205">
         <v>-87.5</v>
@@ -26319,7 +26319,7 @@
         <v>-87.5</v>
       </c>
       <c r="AJ205">
-        <v>-0.11848</v>
+        <v>-0.11849999999999999</v>
       </c>
       <c r="AK205">
         <v>-87.5</v>
@@ -26337,7 +26337,7 @@
         <v>-87.5</v>
       </c>
       <c r="AP205">
-        <v>-0.11846</v>
+        <v>-0.11826</v>
       </c>
     </row>
     <row r="206" spans="1:42" x14ac:dyDescent="0.25">
@@ -26357,7 +26357,7 @@
         <v>-85.9375</v>
       </c>
       <c r="F206">
-        <v>-0.11626</v>
+        <v>-0.11636000000000001</v>
       </c>
       <c r="G206">
         <v>-85.9375</v>
@@ -26447,7 +26447,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AJ206">
-        <v>-0.11631</v>
+        <v>-0.11632000000000001</v>
       </c>
       <c r="AK206">
         <v>-85.9375</v>
@@ -26465,7 +26465,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AP206">
-        <v>-0.11629</v>
+        <v>-0.11609</v>
       </c>
     </row>
     <row r="207" spans="1:42" x14ac:dyDescent="0.25">
@@ -26485,7 +26485,7 @@
         <v>-84.375</v>
       </c>
       <c r="F207">
-        <v>-0.11409</v>
+        <v>-0.11429</v>
       </c>
       <c r="G207">
         <v>-84.375</v>
@@ -26575,7 +26575,7 @@
         <v>-84.375</v>
       </c>
       <c r="AJ207">
-        <v>-0.11413</v>
+        <v>-0.11412</v>
       </c>
       <c r="AK207">
         <v>-84.375</v>
@@ -26593,7 +26593,7 @@
         <v>-84.375</v>
       </c>
       <c r="AP207">
-        <v>-0.11411</v>
+        <v>-0.11401</v>
       </c>
     </row>
     <row r="208" spans="1:42" x14ac:dyDescent="0.25">
@@ -26613,7 +26613,7 @@
         <v>-82.8125</v>
       </c>
       <c r="F208">
-        <v>-0.11193</v>
+        <v>-0.11183</v>
       </c>
       <c r="G208">
         <v>-82.8125</v>
@@ -26703,7 +26703,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AJ208">
-        <v>-0.11196</v>
+        <v>-0.11197</v>
       </c>
       <c r="AK208">
         <v>-82.8125</v>
@@ -26721,7 +26721,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AP208">
-        <v>-0.11194</v>
+        <v>-0.11214</v>
       </c>
     </row>
     <row r="209" spans="1:42" x14ac:dyDescent="0.25">
@@ -26741,7 +26741,7 @@
         <v>-81.25</v>
       </c>
       <c r="F209">
-        <v>-0.10976</v>
+        <v>-0.10956</v>
       </c>
       <c r="G209">
         <v>-81.25</v>
@@ -26831,7 +26831,7 @@
         <v>-81.25</v>
       </c>
       <c r="AJ209">
-        <v>-0.10979999999999999</v>
+        <v>-0.1099</v>
       </c>
       <c r="AK209">
         <v>-81.25</v>
@@ -26849,7 +26849,7 @@
         <v>-81.25</v>
       </c>
       <c r="AP209">
-        <v>-0.10978</v>
+        <v>-0.10988000000000001</v>
       </c>
     </row>
     <row r="210" spans="1:42" x14ac:dyDescent="0.25">
@@ -26959,7 +26959,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AJ210">
-        <v>-0.10764</v>
+        <v>-0.10765</v>
       </c>
       <c r="AK210">
         <v>-79.6875</v>
@@ -26977,7 +26977,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AP210">
-        <v>-0.10761999999999999</v>
+        <v>-0.10772</v>
       </c>
     </row>
     <row r="211" spans="1:42" x14ac:dyDescent="0.25">
@@ -26997,7 +26997,7 @@
         <v>-78.125</v>
       </c>
       <c r="F211">
-        <v>-0.10544000000000001</v>
+        <v>-0.10524</v>
       </c>
       <c r="G211">
         <v>-78.125</v>
@@ -27087,7 +27087,7 @@
         <v>-78.125</v>
       </c>
       <c r="AJ211">
-        <v>-0.10548</v>
+        <v>-0.1055</v>
       </c>
       <c r="AK211">
         <v>-78.125</v>
@@ -27125,7 +27125,7 @@
         <v>-76.5625</v>
       </c>
       <c r="F212">
-        <v>-0.1033</v>
+        <v>-0.1032</v>
       </c>
       <c r="G212">
         <v>-76.5625</v>
@@ -27215,7 +27215,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AJ212">
-        <v>-0.10334</v>
+        <v>-0.10335</v>
       </c>
       <c r="AK212">
         <v>-76.5625</v>
@@ -27233,7 +27233,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AP212">
-        <v>-0.10333000000000001</v>
+        <v>-0.10313</v>
       </c>
     </row>
     <row r="213" spans="1:42" x14ac:dyDescent="0.25">
@@ -27253,7 +27253,7 @@
         <v>-75</v>
       </c>
       <c r="F213">
-        <v>-0.10116</v>
+        <v>-0.10106</v>
       </c>
       <c r="G213">
         <v>-75</v>
@@ -27343,7 +27343,7 @@
         <v>-75</v>
       </c>
       <c r="AJ213">
-        <v>-0.1012</v>
+        <v>-0.1011</v>
       </c>
       <c r="AK213">
         <v>-75</v>
@@ -27361,7 +27361,7 @@
         <v>-75</v>
       </c>
       <c r="AP213">
-        <v>-0.10118000000000001</v>
+        <v>-0.10128</v>
       </c>
     </row>
     <row r="214" spans="1:42" x14ac:dyDescent="0.25">
@@ -27471,7 +27471,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AJ214">
-        <v>-9.9059999999999995E-2</v>
+        <v>-9.9070000000000005E-2</v>
       </c>
       <c r="AK214">
         <v>-73.4375</v>
@@ -27489,7 +27489,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AP214">
-        <v>-9.9040000000000003E-2</v>
+        <v>-9.9239999999999995E-2</v>
       </c>
     </row>
     <row r="215" spans="1:42" x14ac:dyDescent="0.25">
@@ -27509,7 +27509,7 @@
         <v>-71.875</v>
       </c>
       <c r="F215">
-        <v>-9.6869999999999998E-2</v>
+        <v>-9.7070000000000004E-2</v>
       </c>
       <c r="G215">
         <v>-71.875</v>
@@ -27599,7 +27599,7 @@
         <v>-71.875</v>
       </c>
       <c r="AJ215">
-        <v>-9.6909999999999996E-2</v>
+        <v>-9.6920000000000006E-2</v>
       </c>
       <c r="AK215">
         <v>-71.875</v>
@@ -27617,7 +27617,7 @@
         <v>-71.875</v>
       </c>
       <c r="AP215">
-        <v>-9.6890000000000004E-2</v>
+        <v>-9.6790000000000001E-2</v>
       </c>
     </row>
     <row r="216" spans="1:42" x14ac:dyDescent="0.25">
@@ -27727,7 +27727,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AJ216">
-        <v>-9.4769999999999993E-2</v>
+        <v>-9.4780000000000003E-2</v>
       </c>
       <c r="AK216">
         <v>-70.3125</v>
@@ -27745,7 +27745,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AP216">
-        <v>-9.4769999999999993E-2</v>
+        <v>-9.4969999999999999E-2</v>
       </c>
     </row>
     <row r="217" spans="1:42" x14ac:dyDescent="0.25">
@@ -27765,7 +27765,7 @@
         <v>-68.75</v>
       </c>
       <c r="F217">
-        <v>-9.2600000000000002E-2</v>
+        <v>-9.2499999999999999E-2</v>
       </c>
       <c r="G217">
         <v>-68.75</v>
@@ -27855,7 +27855,7 @@
         <v>-68.75</v>
       </c>
       <c r="AJ217">
-        <v>-9.2649999999999996E-2</v>
+        <v>-9.2689999999999995E-2</v>
       </c>
       <c r="AK217">
         <v>-68.75</v>
@@ -27873,7 +27873,7 @@
         <v>-68.75</v>
       </c>
       <c r="AP217">
-        <v>-9.264E-2</v>
+        <v>-9.2740000000000003E-2</v>
       </c>
     </row>
     <row r="218" spans="1:42" x14ac:dyDescent="0.25">
@@ -27893,7 +27893,7 @@
         <v>-67.1875</v>
       </c>
       <c r="F218">
-        <v>-9.0469999999999995E-2</v>
+        <v>-9.0270000000000003E-2</v>
       </c>
       <c r="G218">
         <v>-67.1875</v>
@@ -27983,7 +27983,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AJ218">
-        <v>-9.0520000000000003E-2</v>
+        <v>-9.0529999999999999E-2</v>
       </c>
       <c r="AK218">
         <v>-67.1875</v>
@@ -28111,7 +28111,7 @@
         <v>-65.625</v>
       </c>
       <c r="AJ219">
-        <v>-8.8389999999999996E-2</v>
+        <v>-8.8400000000000006E-2</v>
       </c>
       <c r="AK219">
         <v>-65.625</v>
@@ -28129,7 +28129,7 @@
         <v>-65.625</v>
       </c>
       <c r="AP219">
-        <v>-8.838E-2</v>
+        <v>-8.8179999999999994E-2</v>
       </c>
     </row>
     <row r="220" spans="1:42" x14ac:dyDescent="0.25">
@@ -28149,7 +28149,7 @@
         <v>-64.0625</v>
       </c>
       <c r="F220">
-        <v>-8.6209999999999995E-2</v>
+        <v>-8.6410000000000001E-2</v>
       </c>
       <c r="G220">
         <v>-64.0625</v>
@@ -28239,7 +28239,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AJ220">
-        <v>-8.6269999999999999E-2</v>
+        <v>-8.6300000000000002E-2</v>
       </c>
       <c r="AK220">
         <v>-64.0625</v>
@@ -28257,7 +28257,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AP220">
-        <v>-8.6260000000000003E-2</v>
+        <v>-8.6459999999999995E-2</v>
       </c>
     </row>
     <row r="221" spans="1:42" x14ac:dyDescent="0.25">
@@ -28367,7 +28367,7 @@
         <v>-62.5</v>
       </c>
       <c r="AJ221">
-        <v>-8.4129999999999996E-2</v>
+        <v>-8.4110000000000004E-2</v>
       </c>
       <c r="AK221">
         <v>-62.5</v>
@@ -28385,7 +28385,7 @@
         <v>-62.5</v>
       </c>
       <c r="AP221">
-        <v>-8.412E-2</v>
+        <v>-8.4019999999999997E-2</v>
       </c>
     </row>
     <row r="222" spans="1:42" x14ac:dyDescent="0.25">
@@ -28405,7 +28405,7 @@
         <v>-60.9375</v>
       </c>
       <c r="F222">
-        <v>-8.1960000000000005E-2</v>
+        <v>-8.2059999999999994E-2</v>
       </c>
       <c r="G222">
         <v>-60.9375</v>
@@ -28495,7 +28495,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AJ222">
-        <v>-8.2019999999999996E-2</v>
+        <v>-8.201E-2</v>
       </c>
       <c r="AK222">
         <v>-60.9375</v>
@@ -28513,7 +28513,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AP222">
-        <v>-8.2000000000000003E-2</v>
+        <v>-8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="223" spans="1:42" x14ac:dyDescent="0.25">
@@ -28533,7 +28533,7 @@
         <v>-59.375</v>
       </c>
       <c r="F223">
-        <v>-7.9839999999999994E-2</v>
+        <v>-7.9740000000000005E-2</v>
       </c>
       <c r="G223">
         <v>-59.375</v>
@@ -28623,7 +28623,7 @@
         <v>-59.375</v>
       </c>
       <c r="AJ223">
-        <v>-7.9890000000000003E-2</v>
+        <v>-7.9899999999999999E-2</v>
       </c>
       <c r="AK223">
         <v>-59.375</v>
@@ -28641,7 +28641,7 @@
         <v>-59.375</v>
       </c>
       <c r="AP223">
-        <v>-7.9880000000000007E-2</v>
+        <v>-7.9979999999999996E-2</v>
       </c>
     </row>
     <row r="224" spans="1:42" x14ac:dyDescent="0.25">
@@ -28751,7 +28751,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AJ224">
-        <v>-7.7770000000000006E-2</v>
+        <v>-7.775E-2</v>
       </c>
       <c r="AK224">
         <v>-57.8125</v>
@@ -28769,7 +28769,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AP224">
-        <v>-7.7770000000000006E-2</v>
+        <v>-7.7869999999999995E-2</v>
       </c>
     </row>
     <row r="225" spans="1:42" x14ac:dyDescent="0.25">
@@ -28789,7 +28789,7 @@
         <v>-56.25</v>
       </c>
       <c r="F225">
-        <v>-7.5620000000000007E-2</v>
+        <v>-7.5520000000000004E-2</v>
       </c>
       <c r="G225">
         <v>-56.25</v>
@@ -28879,7 +28879,7 @@
         <v>-56.25</v>
       </c>
       <c r="AJ225">
-        <v>-7.5660000000000005E-2</v>
+        <v>-7.5639999999999999E-2</v>
       </c>
       <c r="AK225">
         <v>-56.25</v>
@@ -28917,7 +28917,7 @@
         <v>-54.6875</v>
       </c>
       <c r="F226">
-        <v>-7.3510000000000006E-2</v>
+        <v>-7.3709999999999998E-2</v>
       </c>
       <c r="G226">
         <v>-54.6875</v>
@@ -29025,7 +29025,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AP226">
-        <v>-7.3539999999999994E-2</v>
+        <v>-7.3639999999999997E-2</v>
       </c>
     </row>
     <row r="227" spans="1:42" x14ac:dyDescent="0.25">
@@ -29045,7 +29045,7 @@
         <v>-53.125</v>
       </c>
       <c r="F227">
-        <v>-7.1389999999999995E-2</v>
+        <v>-7.1190000000000003E-2</v>
       </c>
       <c r="G227">
         <v>-53.125</v>
@@ -29173,7 +29173,7 @@
         <v>-51.5625</v>
       </c>
       <c r="F228">
-        <v>-6.9279999999999994E-2</v>
+        <v>-6.9180000000000005E-2</v>
       </c>
       <c r="G228">
         <v>-51.5625</v>
@@ -29263,7 +29263,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AJ228">
-        <v>-6.9320000000000007E-2</v>
+        <v>-6.9309999999999997E-2</v>
       </c>
       <c r="AK228">
         <v>-51.5625</v>
@@ -29281,7 +29281,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AP228">
-        <v>-6.9309999999999997E-2</v>
+        <v>-6.9110000000000005E-2</v>
       </c>
     </row>
     <row r="229" spans="1:42" x14ac:dyDescent="0.25">
@@ -29301,7 +29301,7 @@
         <v>-50</v>
       </c>
       <c r="F229">
-        <v>-6.7110000000000003E-2</v>
+        <v>-6.701E-2</v>
       </c>
       <c r="G229">
         <v>-50</v>
@@ -29391,7 +29391,7 @@
         <v>-50</v>
       </c>
       <c r="AJ229">
-        <v>-6.7150000000000001E-2</v>
+        <v>-6.7119999999999999E-2</v>
       </c>
       <c r="AK229">
         <v>-50</v>
@@ -29409,7 +29409,7 @@
         <v>-50</v>
       </c>
       <c r="AP229">
-        <v>-6.7140000000000005E-2</v>
+        <v>-6.7040000000000002E-2</v>
       </c>
     </row>
     <row r="230" spans="1:42" x14ac:dyDescent="0.25">
@@ -29519,7 +29519,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AJ230">
-        <v>-6.5040000000000001E-2</v>
+        <v>-6.5049999999999997E-2</v>
       </c>
       <c r="AK230">
         <v>-48.4375</v>
@@ -29557,7 +29557,7 @@
         <v>-46.875</v>
       </c>
       <c r="F231">
-        <v>-6.2890000000000001E-2</v>
+        <v>-6.2990000000000004E-2</v>
       </c>
       <c r="G231">
         <v>-46.875</v>
@@ -29647,7 +29647,7 @@
         <v>-46.875</v>
       </c>
       <c r="AJ231">
-        <v>-6.293E-2</v>
+        <v>-6.2950000000000006E-2</v>
       </c>
       <c r="AK231">
         <v>-46.875</v>
@@ -29665,7 +29665,7 @@
         <v>-46.875</v>
       </c>
       <c r="AP231">
-        <v>-6.2920000000000004E-2</v>
+        <v>-6.2820000000000001E-2</v>
       </c>
     </row>
     <row r="232" spans="1:42" x14ac:dyDescent="0.25">
@@ -29685,7 +29685,7 @@
         <v>-45.3125</v>
       </c>
       <c r="F232">
-        <v>-6.0789999999999997E-2</v>
+        <v>-6.089E-2</v>
       </c>
       <c r="G232">
         <v>-45.3125</v>
@@ -29775,7 +29775,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AJ232">
-        <v>-6.0819999999999999E-2</v>
+        <v>-6.0810000000000003E-2</v>
       </c>
       <c r="AK232">
         <v>-45.3125</v>
@@ -29793,7 +29793,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AP232">
-        <v>-6.0819999999999999E-2</v>
+        <v>-6.0920000000000002E-2</v>
       </c>
     </row>
     <row r="233" spans="1:42" x14ac:dyDescent="0.25">
@@ -29813,7 +29813,7 @@
         <v>-43.75</v>
       </c>
       <c r="F233">
-        <v>-5.8689999999999999E-2</v>
+        <v>-5.8889999999999998E-2</v>
       </c>
       <c r="G233">
         <v>-43.75</v>
@@ -29903,7 +29903,7 @@
         <v>-43.75</v>
       </c>
       <c r="AJ233">
-        <v>-5.8709999999999998E-2</v>
+        <v>-5.8720000000000001E-2</v>
       </c>
       <c r="AK233">
         <v>-43.75</v>
@@ -29921,7 +29921,7 @@
         <v>-43.75</v>
       </c>
       <c r="AP233">
-        <v>-5.8720000000000001E-2</v>
+        <v>-5.892E-2</v>
       </c>
     </row>
     <row r="234" spans="1:42" x14ac:dyDescent="0.25">
@@ -30031,7 +30031,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AJ234">
-        <v>-5.6619999999999997E-2</v>
+        <v>-5.6610000000000001E-2</v>
       </c>
       <c r="AK234">
         <v>-42.1875</v>
@@ -30049,7 +30049,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AP234">
-        <v>-5.6619999999999997E-2</v>
+        <v>-5.6520000000000001E-2</v>
       </c>
     </row>
     <row r="235" spans="1:42" x14ac:dyDescent="0.25">
@@ -30069,7 +30069,7 @@
         <v>-40.625</v>
       </c>
       <c r="F235">
-        <v>-5.4469999999999998E-2</v>
+        <v>-5.4670000000000003E-2</v>
       </c>
       <c r="G235">
         <v>-40.625</v>
@@ -30159,7 +30159,7 @@
         <v>-40.625</v>
       </c>
       <c r="AJ235">
-        <v>-5.4510000000000003E-2</v>
+        <v>-5.45E-2</v>
       </c>
       <c r="AK235">
         <v>-40.625</v>
@@ -30177,7 +30177,7 @@
         <v>-40.625</v>
       </c>
       <c r="AP235">
-        <v>-5.4510000000000003E-2</v>
+        <v>-5.4710000000000002E-2</v>
       </c>
     </row>
     <row r="236" spans="1:42" x14ac:dyDescent="0.25">
@@ -30197,7 +30197,7 @@
         <v>-39.0625</v>
       </c>
       <c r="F236">
-        <v>-5.237E-2</v>
+        <v>-5.2269999999999997E-2</v>
       </c>
       <c r="G236">
         <v>-39.0625</v>
@@ -30287,7 +30287,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AJ236">
-        <v>-5.2409999999999998E-2</v>
+        <v>-5.2400000000000002E-2</v>
       </c>
       <c r="AK236">
         <v>-39.0625</v>
@@ -30305,7 +30305,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AP236">
-        <v>-5.2400000000000002E-2</v>
+        <v>-5.2499999999999998E-2</v>
       </c>
     </row>
     <row r="237" spans="1:42" x14ac:dyDescent="0.25">
@@ -30325,7 +30325,7 @@
         <v>-37.5</v>
       </c>
       <c r="F237">
-        <v>-5.0250000000000003E-2</v>
+        <v>-5.0049999999999997E-2</v>
       </c>
       <c r="G237">
         <v>-37.5</v>
@@ -30415,7 +30415,7 @@
         <v>-37.5</v>
       </c>
       <c r="AJ237">
-        <v>-5.0279999999999998E-2</v>
+        <v>-5.0270000000000002E-2</v>
       </c>
       <c r="AK237">
         <v>-37.5</v>
@@ -30453,7 +30453,7 @@
         <v>-35.9375</v>
       </c>
       <c r="F238">
-        <v>-4.8149999999999998E-2</v>
+        <v>-4.8050000000000002E-2</v>
       </c>
       <c r="G238">
         <v>-35.9375</v>
@@ -30543,7 +30543,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AJ238">
-        <v>-4.8180000000000001E-2</v>
+        <v>-4.8169999999999998E-2</v>
       </c>
       <c r="AK238">
         <v>-35.9375</v>
@@ -30561,7 +30561,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AP238">
-        <v>-4.8180000000000001E-2</v>
+        <v>-4.8379999999999999E-2</v>
       </c>
     </row>
     <row r="239" spans="1:42" x14ac:dyDescent="0.25">
@@ -30671,7 +30671,7 @@
         <v>-34.375</v>
       </c>
       <c r="AJ239">
-        <v>-4.607E-2</v>
+        <v>-4.6019999999999998E-2</v>
       </c>
       <c r="AK239">
         <v>-34.375</v>
@@ -30689,7 +30689,7 @@
         <v>-34.375</v>
       </c>
       <c r="AP239">
-        <v>-4.6080000000000003E-2</v>
+        <v>-4.6280000000000002E-2</v>
       </c>
     </row>
     <row r="240" spans="1:42" x14ac:dyDescent="0.25">
@@ -30709,7 +30709,7 @@
         <v>-32.8125</v>
       </c>
       <c r="F240">
-        <v>-4.394E-2</v>
+        <v>-4.4040000000000003E-2</v>
       </c>
       <c r="G240">
         <v>-32.8125</v>
@@ -30799,7 +30799,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AJ240">
-        <v>-4.3979999999999998E-2</v>
+        <v>-4.3990000000000001E-2</v>
       </c>
       <c r="AK240">
         <v>-32.8125</v>
@@ -30817,7 +30817,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AP240">
-        <v>-4.3979999999999998E-2</v>
+        <v>-4.3880000000000002E-2</v>
       </c>
     </row>
     <row r="241" spans="1:42" x14ac:dyDescent="0.25">
@@ -30837,7 +30837,7 @@
         <v>-31.25</v>
       </c>
       <c r="F241">
-        <v>-4.1849999999999998E-2</v>
+        <v>-4.1950000000000001E-2</v>
       </c>
       <c r="G241">
         <v>-31.25</v>
@@ -30927,7 +30927,7 @@
         <v>-31.25</v>
       </c>
       <c r="AJ241">
-        <v>-4.1869999999999997E-2</v>
+        <v>-4.1880000000000001E-2</v>
       </c>
       <c r="AK241">
         <v>-31.25</v>
@@ -30945,7 +30945,7 @@
         <v>-31.25</v>
       </c>
       <c r="AP241">
-        <v>-4.1880000000000001E-2</v>
+        <v>-4.2079999999999999E-2</v>
       </c>
     </row>
     <row r="242" spans="1:42" x14ac:dyDescent="0.25">
@@ -30965,7 +30965,7 @@
         <v>-29.6875</v>
       </c>
       <c r="F242">
-        <v>-3.9750000000000001E-2</v>
+        <v>-3.9949999999999999E-2</v>
       </c>
       <c r="G242">
         <v>-29.6875</v>
@@ -31055,7 +31055,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AJ242">
-        <v>-3.977E-2</v>
+        <v>-3.9800000000000002E-2</v>
       </c>
       <c r="AK242">
         <v>-29.6875</v>
@@ -31093,7 +31093,7 @@
         <v>-28.125</v>
       </c>
       <c r="F243">
-        <v>-3.7650000000000003E-2</v>
+        <v>-3.7850000000000002E-2</v>
       </c>
       <c r="G243">
         <v>-28.125</v>
@@ -31183,7 +31183,7 @@
         <v>-28.125</v>
       </c>
       <c r="AJ243">
-        <v>-3.7670000000000002E-2</v>
+        <v>-3.7679999999999998E-2</v>
       </c>
       <c r="AK243">
         <v>-28.125</v>
@@ -31201,7 +31201,7 @@
         <v>-28.125</v>
       </c>
       <c r="AP243">
-        <v>-3.7670000000000002E-2</v>
+        <v>-3.7769999999999998E-2</v>
       </c>
     </row>
     <row r="244" spans="1:42" x14ac:dyDescent="0.25">
@@ -31221,7 +31221,7 @@
         <v>-26.5625</v>
       </c>
       <c r="F244">
-        <v>-3.5540000000000002E-2</v>
+        <v>-3.5639999999999998E-2</v>
       </c>
       <c r="G244">
         <v>-26.5625</v>
@@ -31311,7 +31311,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AJ244">
-        <v>-3.5560000000000001E-2</v>
+        <v>-3.56E-2</v>
       </c>
       <c r="AK244">
         <v>-26.5625</v>
@@ -31329,7 +31329,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AP244">
-        <v>-3.5569999999999997E-2</v>
+        <v>-3.5470000000000002E-2</v>
       </c>
     </row>
     <row r="245" spans="1:42" x14ac:dyDescent="0.25">
@@ -31349,7 +31349,7 @@
         <v>-25</v>
       </c>
       <c r="F245">
-        <v>-3.3450000000000001E-2</v>
+        <v>-3.3250000000000002E-2</v>
       </c>
       <c r="G245">
         <v>-25</v>
@@ -31457,7 +31457,7 @@
         <v>-25</v>
       </c>
       <c r="AP245">
-        <v>-3.347E-2</v>
+        <v>-3.3270000000000001E-2</v>
       </c>
     </row>
     <row r="246" spans="1:42" x14ac:dyDescent="0.25">
@@ -31477,7 +31477,7 @@
         <v>-23.4375</v>
       </c>
       <c r="F246">
-        <v>-3.134E-2</v>
+        <v>-3.1440000000000003E-2</v>
       </c>
       <c r="G246">
         <v>-23.4375</v>
@@ -31567,7 +31567,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AJ246">
-        <v>-3.1370000000000002E-2</v>
+        <v>-3.1379999999999998E-2</v>
       </c>
       <c r="AK246">
         <v>-23.4375</v>
@@ -31585,7 +31585,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AP246">
-        <v>-3.1379999999999998E-2</v>
+        <v>-3.1179999999999999E-2</v>
       </c>
     </row>
     <row r="247" spans="1:42" x14ac:dyDescent="0.25">
@@ -31605,7 +31605,7 @@
         <v>-21.875</v>
       </c>
       <c r="F247">
-        <v>-2.9229999999999999E-2</v>
+        <v>-2.913E-2</v>
       </c>
       <c r="G247">
         <v>-21.875</v>
@@ -31695,7 +31695,7 @@
         <v>-21.875</v>
       </c>
       <c r="AJ247">
-        <v>-2.9250000000000002E-2</v>
+        <v>-2.929E-2</v>
       </c>
       <c r="AK247">
         <v>-21.875</v>
@@ -31713,7 +31713,7 @@
         <v>-21.875</v>
       </c>
       <c r="AP247">
-        <v>-2.9260000000000001E-2</v>
+        <v>-2.9159999999999998E-2</v>
       </c>
     </row>
     <row r="248" spans="1:42" x14ac:dyDescent="0.25">
@@ -31733,7 +31733,7 @@
         <v>-20.3125</v>
       </c>
       <c r="F248">
-        <v>-2.7130000000000001E-2</v>
+        <v>-2.733E-2</v>
       </c>
       <c r="G248">
         <v>-20.3125</v>
@@ -31823,7 +31823,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AJ248">
-        <v>-2.716E-2</v>
+        <v>-2.7150000000000001E-2</v>
       </c>
       <c r="AK248">
         <v>-20.3125</v>
@@ -31841,7 +31841,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AP248">
-        <v>-2.716E-2</v>
+        <v>-2.7359999999999999E-2</v>
       </c>
     </row>
     <row r="249" spans="1:42" x14ac:dyDescent="0.25">
@@ -31861,7 +31861,7 @@
         <v>-18.75</v>
       </c>
       <c r="F249">
-        <v>-2.503E-2</v>
+        <v>-2.5229999999999999E-2</v>
       </c>
       <c r="G249">
         <v>-18.75</v>
@@ -31951,7 +31951,7 @@
         <v>-18.75</v>
       </c>
       <c r="AJ249">
-        <v>-2.5049999999999999E-2</v>
+        <v>-2.5020000000000001E-2</v>
       </c>
       <c r="AK249">
         <v>-18.75</v>
@@ -31989,7 +31989,7 @@
         <v>-17.1875</v>
       </c>
       <c r="F250">
-        <v>-2.2919999999999999E-2</v>
+        <v>-2.3019999999999999E-2</v>
       </c>
       <c r="G250">
         <v>-17.1875</v>
@@ -32079,7 +32079,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AJ250">
-        <v>-2.2960000000000001E-2</v>
+        <v>-2.3E-2</v>
       </c>
       <c r="AK250">
         <v>-17.1875</v>
@@ -32207,7 +32207,7 @@
         <v>-15.625</v>
       </c>
       <c r="AJ251">
-        <v>-2.0840000000000001E-2</v>
+        <v>-2.0799999999999999E-2</v>
       </c>
       <c r="AK251">
         <v>-15.625</v>
@@ -32245,7 +32245,7 @@
         <v>-14.0625</v>
       </c>
       <c r="F252">
-        <v>-1.8020000000000001E-2</v>
+        <v>-1.822E-2</v>
       </c>
       <c r="G252">
         <v>-14.0625</v>
@@ -32335,7 +32335,7 @@
         <v>-14.0625</v>
       </c>
       <c r="AJ252">
-        <v>-1.874E-2</v>
+        <v>-1.8700000000000001E-2</v>
       </c>
       <c r="AK252">
         <v>-14.0625</v>
@@ -32463,7 +32463,7 @@
         <v>-12.5</v>
       </c>
       <c r="AJ253">
-        <v>-1.6619999999999999E-2</v>
+        <v>-1.66E-2</v>
       </c>
       <c r="AK253">
         <v>-12.5</v>
@@ -32591,7 +32591,7 @@
         <v>-10.9375</v>
       </c>
       <c r="AJ254">
-        <v>-1.452E-2</v>
+        <v>-1.451E-2</v>
       </c>
       <c r="AK254">
         <v>-10.9375</v>
@@ -32609,7 +32609,7 @@
         <v>-10.9375</v>
       </c>
       <c r="AP254">
-        <v>-1.452E-2</v>
+        <v>-1.472E-2</v>
       </c>
     </row>
     <row r="255" spans="1:42" x14ac:dyDescent="0.25">
@@ -32719,7 +32719,7 @@
         <v>-9.375</v>
       </c>
       <c r="AJ255">
-        <v>-1.24E-2</v>
+        <v>-1.29E-2</v>
       </c>
       <c r="AK255">
         <v>-9.375</v>
@@ -32737,7 +32737,7 @@
         <v>-9.375</v>
       </c>
       <c r="AP255">
-        <v>-1.231E-2</v>
+        <v>-1.251E-2</v>
       </c>
     </row>
     <row r="256" spans="1:42" x14ac:dyDescent="0.25">
@@ -32847,7 +32847,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AJ256">
-        <v>-1.0200000000000001E-2</v>
+        <v>-1.01E-2</v>
       </c>
       <c r="AK256">
         <v>-7.8125</v>
@@ -32865,7 +32865,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AP256">
-        <v>-1.042E-2</v>
+        <v>-1.022E-2</v>
       </c>
     </row>
     <row r="257" spans="1:42" x14ac:dyDescent="0.25">
@@ -32975,7 +32975,7 @@
         <v>-6.25</v>
       </c>
       <c r="AJ257">
-        <v>-7.7200000000000003E-3</v>
+        <v>-7.7299999999999999E-3</v>
       </c>
       <c r="AK257">
         <v>-6.25</v>
@@ -32993,7 +32993,7 @@
         <v>-6.25</v>
       </c>
       <c r="AP257">
-        <v>-7.9299999999999995E-3</v>
+        <v>-7.8300000000000002E-3</v>
       </c>
     </row>
     <row r="258" spans="1:42" x14ac:dyDescent="0.25">
@@ -33103,7 +33103,7 @@
         <v>-4.6875</v>
       </c>
       <c r="AJ258">
-        <v>-5.0899999999999999E-3</v>
+        <v>-5.1200000000000004E-3</v>
       </c>
       <c r="AK258">
         <v>-4.6875</v>
@@ -33231,7 +33231,7 @@
         <v>-3.125</v>
       </c>
       <c r="AJ259">
-        <v>-2.6900000000000001E-3</v>
+        <v>-2.6800000000000001E-3</v>
       </c>
       <c r="AK259">
         <v>-3.125</v>

--- a/IV_3.5K_T1.xlsx
+++ b/IV_3.5K_T1.xlsx
@@ -8848,7 +8848,7 @@
         <v>100</v>
       </c>
       <c r="P69">
-        <v>0.13602</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="Q69">
         <v>100</v>

--- a/IV_3.5K_T1.xlsx
+++ b/IV_3.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -414,6 +414,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AR260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4538,7 +4541,7 @@
         <v>46.875</v>
       </c>
       <c r="AD35">
-        <v>6.3189999999999996E-2</v>
+        <v>6.3200000000000006E-2</v>
       </c>
       <c r="AE35">
         <v>46.875</v>
@@ -4666,7 +4669,7 @@
         <v>48.4375</v>
       </c>
       <c r="AD36">
-        <v>6.5280000000000005E-2</v>
+        <v>6.5269999999999995E-2</v>
       </c>
       <c r="AE36">
         <v>48.4375</v>
@@ -4922,7 +4925,7 @@
         <v>51.5625</v>
       </c>
       <c r="AD38">
-        <v>6.9559999999999997E-2</v>
+        <v>6.9550000000000001E-2</v>
       </c>
       <c r="AE38">
         <v>51.5625</v>
@@ -5026,7 +5029,7 @@
         <v>53.125</v>
       </c>
       <c r="V39">
-        <v>7.1679999999999994E-2</v>
+        <v>7.1669999999999998E-2</v>
       </c>
       <c r="W39">
         <v>53.125</v>
@@ -5050,7 +5053,7 @@
         <v>53.125</v>
       </c>
       <c r="AD39">
-        <v>7.1679999999999994E-2</v>
+        <v>7.1669999999999998E-2</v>
       </c>
       <c r="AE39">
         <v>53.125</v>
@@ -5270,7 +5273,7 @@
         <v>56.25</v>
       </c>
       <c r="R41">
-        <v>7.5899999999999995E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="S41">
         <v>56.25</v>
@@ -5282,7 +5285,7 @@
         <v>56.25</v>
       </c>
       <c r="V41">
-        <v>7.5910000000000005E-2</v>
+        <v>7.5920000000000001E-2</v>
       </c>
       <c r="W41">
         <v>56.25</v>
@@ -5410,7 +5413,7 @@
         <v>57.8125</v>
       </c>
       <c r="V42">
-        <v>7.8020000000000006E-2</v>
+        <v>7.8E-2</v>
       </c>
       <c r="W42">
         <v>57.8125</v>
@@ -5434,7 +5437,7 @@
         <v>57.8125</v>
       </c>
       <c r="AD42">
-        <v>7.8020000000000006E-2</v>
+        <v>7.8030000000000002E-2</v>
       </c>
       <c r="AE42">
         <v>57.8125</v>
@@ -5538,13 +5541,13 @@
         <v>59.375</v>
       </c>
       <c r="V43">
-        <v>8.0140000000000003E-2</v>
+        <v>8.0149999999999999E-2</v>
       </c>
       <c r="W43">
         <v>59.375</v>
       </c>
       <c r="X43">
-        <v>8.0119999999999997E-2</v>
+        <v>8.0140000000000003E-2</v>
       </c>
       <c r="Y43">
         <v>59.375</v>
@@ -5562,7 +5565,7 @@
         <v>59.375</v>
       </c>
       <c r="AD43">
-        <v>8.0140000000000003E-2</v>
+        <v>8.0149999999999999E-2</v>
       </c>
       <c r="AE43">
         <v>59.375</v>
@@ -5690,7 +5693,7 @@
         <v>60.9375</v>
       </c>
       <c r="AD44">
-        <v>8.2250000000000004E-2</v>
+        <v>8.226E-2</v>
       </c>
       <c r="AE44">
         <v>60.9375</v>
@@ -5818,7 +5821,7 @@
         <v>62.5</v>
       </c>
       <c r="AD45">
-        <v>8.4390000000000007E-2</v>
+        <v>8.4360000000000004E-2</v>
       </c>
       <c r="AE45">
         <v>62.5</v>
@@ -5922,7 +5925,7 @@
         <v>64.0625</v>
       </c>
       <c r="V46">
-        <v>8.6489999999999997E-2</v>
+        <v>8.6510000000000004E-2</v>
       </c>
       <c r="W46">
         <v>64.0625</v>
@@ -6074,7 +6077,7 @@
         <v>65.625</v>
       </c>
       <c r="AD47">
-        <v>8.863E-2</v>
+        <v>8.8650000000000007E-2</v>
       </c>
       <c r="AE47">
         <v>65.625</v>
@@ -6208,7 +6211,7 @@
         <v>67.1875</v>
       </c>
       <c r="AF48">
-        <v>9.0749999999999997E-2</v>
+        <v>9.0759999999999993E-2</v>
       </c>
       <c r="AG48">
         <v>67.1875</v>
@@ -6306,7 +6309,7 @@
         <v>68.75</v>
       </c>
       <c r="V49">
-        <v>9.2880000000000004E-2</v>
+        <v>9.2910000000000006E-2</v>
       </c>
       <c r="W49">
         <v>68.75</v>
@@ -6330,7 +6333,7 @@
         <v>68.75</v>
       </c>
       <c r="AD49">
-        <v>9.289E-2</v>
+        <v>9.2899999999999996E-2</v>
       </c>
       <c r="AE49">
         <v>68.75</v>
@@ -6464,7 +6467,7 @@
         <v>70.3125</v>
       </c>
       <c r="AF50">
-        <v>9.5000000000000001E-2</v>
+        <v>9.5200000000000007E-2</v>
       </c>
       <c r="AG50">
         <v>70.3125</v>
@@ -6550,7 +6553,7 @@
         <v>71.875</v>
       </c>
       <c r="R51">
-        <v>9.7180000000000002E-2</v>
+        <v>9.7199999999999995E-2</v>
       </c>
       <c r="S51">
         <v>71.875</v>
@@ -6562,7 +6565,7 @@
         <v>71.875</v>
       </c>
       <c r="V51">
-        <v>9.715E-2</v>
+        <v>9.7180000000000002E-2</v>
       </c>
       <c r="W51">
         <v>71.875</v>
@@ -6592,7 +6595,7 @@
         <v>71.875</v>
       </c>
       <c r="AF51">
-        <v>9.715E-2</v>
+        <v>9.7159999999999996E-2</v>
       </c>
       <c r="AG51">
         <v>71.875</v>
@@ -6690,7 +6693,7 @@
         <v>73.4375</v>
       </c>
       <c r="V52">
-        <v>9.9299999999999999E-2</v>
+        <v>9.9309999999999996E-2</v>
       </c>
       <c r="W52">
         <v>73.4375</v>
@@ -6714,7 +6717,7 @@
         <v>73.4375</v>
       </c>
       <c r="AD52">
-        <v>9.9309999999999996E-2</v>
+        <v>9.9330000000000002E-2</v>
       </c>
       <c r="AE52">
         <v>73.4375</v>
@@ -6842,7 +6845,7 @@
         <v>75</v>
       </c>
       <c r="AD53">
-        <v>0.10145</v>
+        <v>0.10144</v>
       </c>
       <c r="AE53">
         <v>75</v>
@@ -6946,7 +6949,7 @@
         <v>76.5625</v>
       </c>
       <c r="V54">
-        <v>0.10357</v>
+        <v>0.10356</v>
       </c>
       <c r="W54">
         <v>76.5625</v>
@@ -6970,7 +6973,7 @@
         <v>76.5625</v>
       </c>
       <c r="AD54">
-        <v>0.1036</v>
+        <v>0.10360999999999999</v>
       </c>
       <c r="AE54">
         <v>76.5625</v>
@@ -7098,7 +7101,7 @@
         <v>78.125</v>
       </c>
       <c r="AD55">
-        <v>0.10576000000000001</v>
+        <v>0.10577</v>
       </c>
       <c r="AE55">
         <v>78.125</v>
@@ -7202,7 +7205,7 @@
         <v>79.6875</v>
       </c>
       <c r="V56">
-        <v>0.10789</v>
+        <v>0.1079</v>
       </c>
       <c r="W56">
         <v>79.6875</v>
@@ -7226,7 +7229,7 @@
         <v>79.6875</v>
       </c>
       <c r="AD56">
-        <v>0.10791000000000001</v>
+        <v>0.10792</v>
       </c>
       <c r="AE56">
         <v>79.6875</v>
@@ -7330,13 +7333,13 @@
         <v>81.25</v>
       </c>
       <c r="V57">
-        <v>0.11005</v>
+        <v>0.11002000000000001</v>
       </c>
       <c r="W57">
         <v>81.25</v>
       </c>
       <c r="X57">
-        <v>0.11002000000000001</v>
+        <v>0.11003</v>
       </c>
       <c r="Y57">
         <v>81.25</v>
@@ -7458,7 +7461,7 @@
         <v>82.8125</v>
       </c>
       <c r="V58">
-        <v>0.11219999999999999</v>
+        <v>0.11221</v>
       </c>
       <c r="W58">
         <v>82.8125</v>
@@ -7482,7 +7485,7 @@
         <v>82.8125</v>
       </c>
       <c r="AD58">
-        <v>0.11224000000000001</v>
+        <v>0.11222</v>
       </c>
       <c r="AE58">
         <v>82.8125</v>
@@ -7610,7 +7613,7 @@
         <v>84.375</v>
       </c>
       <c r="AD59">
-        <v>0.1144</v>
+        <v>0.11441</v>
       </c>
       <c r="AE59">
         <v>84.375</v>
@@ -7714,7 +7717,7 @@
         <v>85.9375</v>
       </c>
       <c r="V60">
-        <v>0.11654</v>
+        <v>0.11655</v>
       </c>
       <c r="W60">
         <v>85.9375</v>
@@ -7830,7 +7833,7 @@
         <v>87.5</v>
       </c>
       <c r="R61">
-        <v>0.11877</v>
+        <v>0.11878</v>
       </c>
       <c r="S61">
         <v>87.5</v>
@@ -7970,7 +7973,7 @@
         <v>89.0625</v>
       </c>
       <c r="V62">
-        <v>0.12092</v>
+        <v>0.12093</v>
       </c>
       <c r="W62">
         <v>89.0625</v>
@@ -7994,7 +7997,7 @@
         <v>89.0625</v>
       </c>
       <c r="AD62">
-        <v>0.12093</v>
+        <v>0.12094000000000001</v>
       </c>
       <c r="AE62">
         <v>89.0625</v>
@@ -8098,7 +8101,7 @@
         <v>90.625</v>
       </c>
       <c r="V63">
-        <v>0.12311</v>
+        <v>0.12311999999999999</v>
       </c>
       <c r="W63">
         <v>90.625</v>
@@ -8226,7 +8229,7 @@
         <v>92.1875</v>
       </c>
       <c r="V64">
-        <v>0.12529999999999999</v>
+        <v>0.12531</v>
       </c>
       <c r="W64">
         <v>92.1875</v>
@@ -8250,7 +8253,7 @@
         <v>92.1875</v>
       </c>
       <c r="AD64">
-        <v>0.12531999999999999</v>
+        <v>0.12533</v>
       </c>
       <c r="AE64">
         <v>92.1875</v>
@@ -8378,7 +8381,7 @@
         <v>93.75</v>
       </c>
       <c r="AD65">
-        <v>0.12751000000000001</v>
+        <v>0.12751999999999999</v>
       </c>
       <c r="AE65">
         <v>93.75</v>
@@ -8610,7 +8613,7 @@
         <v>96.875</v>
       </c>
       <c r="V67">
-        <v>0.13192999999999999</v>
+        <v>0.13192000000000001</v>
       </c>
       <c r="W67">
         <v>96.875</v>
@@ -8634,7 +8637,7 @@
         <v>96.875</v>
       </c>
       <c r="AD67">
-        <v>0.13192999999999999</v>
+        <v>0.13194</v>
       </c>
       <c r="AE67">
         <v>96.875</v>
@@ -8726,7 +8729,7 @@
         <v>98.4375</v>
       </c>
       <c r="R68">
-        <v>0.13414999999999999</v>
+        <v>0.13414000000000001</v>
       </c>
       <c r="S68">
         <v>98.4375</v>
@@ -8866,7 +8869,7 @@
         <v>100</v>
       </c>
       <c r="V69">
-        <v>0.13608999999999999</v>
+        <v>0.1361</v>
       </c>
       <c r="W69">
         <v>100</v>
@@ -8890,7 +8893,7 @@
         <v>100</v>
       </c>
       <c r="AD69">
-        <v>0.13608999999999999</v>
+        <v>0.1361</v>
       </c>
       <c r="AE69">
         <v>100</v>
@@ -8952,7 +8955,7 @@
         <v>98.4375</v>
       </c>
       <c r="H70">
-        <v>0.13527</v>
+        <v>0.13525999999999999</v>
       </c>
       <c r="I70">
         <v>98.4375</v>
@@ -9122,7 +9125,7 @@
         <v>96.875</v>
       </c>
       <c r="V71">
-        <v>0.13175999999999999</v>
+        <v>0.13177</v>
       </c>
       <c r="W71">
         <v>96.875</v>
@@ -9146,7 +9149,7 @@
         <v>96.875</v>
       </c>
       <c r="AD71">
-        <v>0.13178000000000001</v>
+        <v>0.13181000000000001</v>
       </c>
       <c r="AE71">
         <v>96.875</v>
@@ -9208,7 +9211,7 @@
         <v>95.3125</v>
       </c>
       <c r="H72">
-        <v>0.13081000000000001</v>
+        <v>0.13081999999999999</v>
       </c>
       <c r="I72">
         <v>95.3125</v>
@@ -9226,7 +9229,7 @@
         <v>95.3125</v>
       </c>
       <c r="N72">
-        <v>0.12956000000000001</v>
+        <v>0.12955</v>
       </c>
       <c r="O72">
         <v>95.3125</v>
@@ -9274,7 +9277,7 @@
         <v>95.3125</v>
       </c>
       <c r="AD72">
-        <v>0.12956000000000001</v>
+        <v>0.12959999999999999</v>
       </c>
       <c r="AE72">
         <v>95.3125</v>
@@ -9464,7 +9467,7 @@
         <v>92.1875</v>
       </c>
       <c r="H74">
-        <v>0.12634999999999999</v>
+        <v>0.12640999999999999</v>
       </c>
       <c r="I74">
         <v>92.1875</v>
@@ -9506,7 +9509,7 @@
         <v>92.1875</v>
       </c>
       <c r="V74">
-        <v>0.12514</v>
+        <v>0.12515999999999999</v>
       </c>
       <c r="W74">
         <v>92.1875</v>
@@ -9530,7 +9533,7 @@
         <v>92.1875</v>
       </c>
       <c r="AD74">
-        <v>0.12515999999999999</v>
+        <v>0.12518000000000001</v>
       </c>
       <c r="AE74">
         <v>92.1875</v>
@@ -9622,7 +9625,7 @@
         <v>90.625</v>
       </c>
       <c r="R75">
-        <v>0.12293999999999999</v>
+        <v>0.12296</v>
       </c>
       <c r="S75">
         <v>90.625</v>
@@ -9634,7 +9637,7 @@
         <v>90.625</v>
       </c>
       <c r="V75">
-        <v>0.12293</v>
+        <v>0.12295</v>
       </c>
       <c r="W75">
         <v>90.625</v>
@@ -9664,7 +9667,7 @@
         <v>90.625</v>
       </c>
       <c r="AF75">
-        <v>0.12289</v>
+        <v>0.12288</v>
       </c>
       <c r="AG75">
         <v>90.625</v>
@@ -9786,7 +9789,7 @@
         <v>89.0625</v>
       </c>
       <c r="AD76">
-        <v>0.12076000000000001</v>
+        <v>0.12077</v>
       </c>
       <c r="AE76">
         <v>89.0625</v>
@@ -9866,7 +9869,7 @@
         <v>87.5</v>
       </c>
       <c r="N77">
-        <v>0.11855</v>
+        <v>0.11858</v>
       </c>
       <c r="O77">
         <v>87.5</v>
@@ -9914,13 +9917,13 @@
         <v>87.5</v>
       </c>
       <c r="AD77">
-        <v>0.11856</v>
+        <v>0.11856999999999999</v>
       </c>
       <c r="AE77">
         <v>87.5</v>
       </c>
       <c r="AF77">
-        <v>0.11851</v>
+        <v>0.11852</v>
       </c>
       <c r="AG77">
         <v>87.5</v>
@@ -9994,7 +9997,7 @@
         <v>85.9375</v>
       </c>
       <c r="N78" s="1">
-        <v>0.11636000000000001</v>
+        <v>0.11637</v>
       </c>
       <c r="O78">
         <v>85.9375</v>
@@ -10170,13 +10173,13 @@
         <v>84.375</v>
       </c>
       <c r="AD79">
-        <v>0.11419</v>
+        <v>0.1142</v>
       </c>
       <c r="AE79">
         <v>84.375</v>
       </c>
       <c r="AF79">
-        <v>0.11415</v>
+        <v>0.11411</v>
       </c>
       <c r="AG79">
         <v>84.375</v>
@@ -10274,7 +10277,7 @@
         <v>82.8125</v>
       </c>
       <c r="V80" s="1">
-        <v>0.11201</v>
+        <v>0.11205</v>
       </c>
       <c r="W80">
         <v>82.8125</v>
@@ -10402,7 +10405,7 @@
         <v>81.25</v>
       </c>
       <c r="V81" s="1">
-        <v>0.10986</v>
+        <v>0.10988000000000001</v>
       </c>
       <c r="W81">
         <v>81.25</v>
@@ -10426,13 +10429,13 @@
         <v>81.25</v>
       </c>
       <c r="AD81">
-        <v>0.10987</v>
+        <v>0.10988000000000001</v>
       </c>
       <c r="AE81">
         <v>81.25</v>
       </c>
       <c r="AF81">
-        <v>0.10982</v>
+        <v>0.10983</v>
       </c>
       <c r="AG81">
         <v>81.25</v>
@@ -10658,7 +10661,7 @@
         <v>78.125</v>
       </c>
       <c r="V83" s="1">
-        <v>0.10553</v>
+        <v>0.10555</v>
       </c>
       <c r="W83">
         <v>78.125</v>
@@ -10786,7 +10789,7 @@
         <v>76.5625</v>
       </c>
       <c r="V84" s="1">
-        <v>0.10338</v>
+        <v>0.10339</v>
       </c>
       <c r="W84">
         <v>76.5625</v>
@@ -10810,7 +10813,7 @@
         <v>76.5625</v>
       </c>
       <c r="AD84">
-        <v>0.10338</v>
+        <v>0.10335999999999999</v>
       </c>
       <c r="AE84">
         <v>76.5625</v>
@@ -10914,7 +10917,7 @@
         <v>75</v>
       </c>
       <c r="V85" s="1">
-        <v>0.10122</v>
+        <v>0.10120999999999999</v>
       </c>
       <c r="W85">
         <v>75</v>
@@ -11066,7 +11069,7 @@
         <v>73.4375</v>
       </c>
       <c r="AD86">
-        <v>9.9089999999999998E-2</v>
+        <v>9.9099999999999994E-2</v>
       </c>
       <c r="AE86">
         <v>73.4375</v>
@@ -11170,7 +11173,7 @@
         <v>71.875</v>
       </c>
       <c r="V87">
-        <v>9.6939999999999998E-2</v>
+        <v>9.6949999999999995E-2</v>
       </c>
       <c r="W87">
         <v>71.875</v>
@@ -11322,7 +11325,7 @@
         <v>70.3125</v>
       </c>
       <c r="AD88">
-        <v>9.4810000000000005E-2</v>
+        <v>9.4789999999999999E-2</v>
       </c>
       <c r="AE88">
         <v>70.3125</v>
@@ -11402,7 +11405,7 @@
         <v>68.75</v>
       </c>
       <c r="N89" s="1">
-        <v>9.2670000000000002E-2</v>
+        <v>9.2679999999999998E-2</v>
       </c>
       <c r="O89">
         <v>68.75</v>
@@ -11682,7 +11685,7 @@
         <v>65.625</v>
       </c>
       <c r="V91">
-        <v>8.8400000000000006E-2</v>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="W91">
         <v>65.625</v>
@@ -11706,7 +11709,7 @@
         <v>65.625</v>
       </c>
       <c r="AD91">
-        <v>8.8410000000000002E-2</v>
+        <v>8.8419999999999999E-2</v>
       </c>
       <c r="AE91">
         <v>65.625</v>
@@ -11810,7 +11813,7 @@
         <v>64.0625</v>
       </c>
       <c r="V92">
-        <v>8.6279999999999996E-2</v>
+        <v>8.6269999999999999E-2</v>
       </c>
       <c r="W92">
         <v>64.0625</v>
@@ -11834,7 +11837,7 @@
         <v>64.0625</v>
       </c>
       <c r="AD92">
-        <v>8.6290000000000006E-2</v>
+        <v>8.6309999999999998E-2</v>
       </c>
       <c r="AE92">
         <v>64.0625</v>
@@ -11962,7 +11965,7 @@
         <v>62.5</v>
       </c>
       <c r="AD93">
-        <v>8.4150000000000003E-2</v>
+        <v>8.4110000000000004E-2</v>
       </c>
       <c r="AE93">
         <v>62.5</v>
@@ -12090,7 +12093,7 @@
         <v>60.9375</v>
       </c>
       <c r="AD94">
-        <v>8.2030000000000006E-2</v>
+        <v>8.2049999999999998E-2</v>
       </c>
       <c r="AE94">
         <v>60.9375</v>
@@ -12218,7 +12221,7 @@
         <v>59.375</v>
       </c>
       <c r="AD95">
-        <v>7.9909999999999995E-2</v>
+        <v>7.9920000000000005E-2</v>
       </c>
       <c r="AE95">
         <v>59.375</v>
@@ -12322,7 +12325,7 @@
         <v>57.8125</v>
       </c>
       <c r="V96">
-        <v>7.7780000000000002E-2</v>
+        <v>7.7789999999999998E-2</v>
       </c>
       <c r="W96">
         <v>57.8125</v>
@@ -12346,7 +12349,7 @@
         <v>57.8125</v>
       </c>
       <c r="AD96">
-        <v>7.7799999999999994E-2</v>
+        <v>7.7770000000000006E-2</v>
       </c>
       <c r="AE96">
         <v>57.8125</v>
@@ -12450,7 +12453,7 @@
         <v>56.25</v>
       </c>
       <c r="V97">
-        <v>7.5660000000000005E-2</v>
+        <v>7.5670000000000001E-2</v>
       </c>
       <c r="W97">
         <v>56.25</v>
@@ -12578,7 +12581,7 @@
         <v>54.6875</v>
       </c>
       <c r="V98">
-        <v>7.3550000000000004E-2</v>
+        <v>7.3569999999999997E-2</v>
       </c>
       <c r="W98">
         <v>54.6875</v>
@@ -12858,7 +12861,7 @@
         <v>51.5625</v>
       </c>
       <c r="AD100">
-        <v>6.9339999999999999E-2</v>
+        <v>6.9349999999999995E-2</v>
       </c>
       <c r="AE100">
         <v>51.5625</v>
@@ -13090,7 +13093,7 @@
         <v>48.4375</v>
       </c>
       <c r="V102">
-        <v>6.5040000000000001E-2</v>
+        <v>6.5049999999999997E-2</v>
       </c>
       <c r="W102">
         <v>48.4375</v>
@@ -13114,7 +13117,7 @@
         <v>48.4375</v>
       </c>
       <c r="AD102">
-        <v>6.5060000000000007E-2</v>
+        <v>6.5049999999999997E-2</v>
       </c>
       <c r="AE102">
         <v>48.4375</v>
@@ -13176,7 +13179,7 @@
         <v>46.875</v>
       </c>
       <c r="H103" s="1">
-        <v>6.3530000000000003E-2</v>
+        <v>6.3549999999999995E-2</v>
       </c>
       <c r="I103">
         <v>46.875</v>
@@ -13218,7 +13221,7 @@
         <v>46.875</v>
       </c>
       <c r="V103">
-        <v>6.293E-2</v>
+        <v>6.2909999999999994E-2</v>
       </c>
       <c r="W103">
         <v>46.875</v>
@@ -13242,7 +13245,7 @@
         <v>46.875</v>
       </c>
       <c r="AD103">
-        <v>6.2950000000000006E-2</v>
+        <v>6.2960000000000002E-2</v>
       </c>
       <c r="AE103">
         <v>46.875</v>
@@ -13304,7 +13307,7 @@
         <v>45.3125</v>
       </c>
       <c r="H104" s="1">
-        <v>6.1400000000000003E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="I104">
         <v>45.3125</v>
@@ -13346,7 +13349,7 @@
         <v>45.3125</v>
       </c>
       <c r="V104">
-        <v>6.0819999999999999E-2</v>
+        <v>6.08E-2</v>
       </c>
       <c r="W104">
         <v>45.3125</v>
@@ -13370,7 +13373,7 @@
         <v>45.3125</v>
       </c>
       <c r="AD104">
-        <v>6.0839999999999998E-2</v>
+        <v>6.0850000000000001E-2</v>
       </c>
       <c r="AE104">
         <v>45.3125</v>
@@ -13560,7 +13563,7 @@
         <v>42.1875</v>
       </c>
       <c r="H106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7140000000000003E-2</v>
       </c>
       <c r="I106">
         <v>42.1875</v>
@@ -13602,7 +13605,7 @@
         <v>42.1875</v>
       </c>
       <c r="V106">
-        <v>5.6619999999999997E-2</v>
+        <v>5.6599999999999998E-2</v>
       </c>
       <c r="W106">
         <v>42.1875</v>
@@ -13816,7 +13819,7 @@
         <v>39.0625</v>
       </c>
       <c r="H108">
-        <v>5.2900000000000003E-2</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="I108">
         <v>39.0625</v>
@@ -13858,7 +13861,7 @@
         <v>39.0625</v>
       </c>
       <c r="V108">
-        <v>5.2400000000000002E-2</v>
+        <v>5.237E-2</v>
       </c>
       <c r="W108">
         <v>39.0625</v>
@@ -13882,7 +13885,7 @@
         <v>39.0625</v>
       </c>
       <c r="AD108">
-        <v>5.2409999999999998E-2</v>
+        <v>5.2389999999999999E-2</v>
       </c>
       <c r="AE108">
         <v>39.0625</v>
@@ -13986,7 +13989,7 @@
         <v>37.5</v>
       </c>
       <c r="V109">
-        <v>5.0290000000000001E-2</v>
+        <v>5.0299999999999997E-2</v>
       </c>
       <c r="W109">
         <v>37.5</v>
@@ -14022,7 +14025,7 @@
         <v>37.5</v>
       </c>
       <c r="AH109">
-        <v>5.0750000000000003E-2</v>
+        <v>5.0770000000000003E-2</v>
       </c>
       <c r="AI109">
         <v>37.5</v>
@@ -14114,7 +14117,7 @@
         <v>35.9375</v>
       </c>
       <c r="V110">
-        <v>4.82E-2</v>
+        <v>4.8210000000000003E-2</v>
       </c>
       <c r="W110">
         <v>35.9375</v>
@@ -14138,7 +14141,7 @@
         <v>35.9375</v>
       </c>
       <c r="AD110">
-        <v>4.82E-2</v>
+        <v>4.8099999999999997E-2</v>
       </c>
       <c r="AE110">
         <v>35.9375</v>
@@ -14278,7 +14281,7 @@
         <v>34.375</v>
       </c>
       <c r="AH111">
-        <v>4.6510000000000003E-2</v>
+        <v>4.6550000000000001E-2</v>
       </c>
       <c r="AI111">
         <v>34.375</v>
@@ -14358,7 +14361,7 @@
         <v>32.8125</v>
       </c>
       <c r="R112">
-        <v>4.3979999999999998E-2</v>
+        <v>4.3990000000000001E-2</v>
       </c>
       <c r="S112">
         <v>32.8125</v>
@@ -14370,7 +14373,7 @@
         <v>32.8125</v>
       </c>
       <c r="V112">
-        <v>4.3979999999999998E-2</v>
+        <v>4.3970000000000002E-2</v>
       </c>
       <c r="W112">
         <v>32.8125</v>
@@ -14382,7 +14385,7 @@
         <v>32.8125</v>
       </c>
       <c r="Z112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.437E-2</v>
       </c>
       <c r="AA112">
         <v>32.8125</v>
@@ -14406,7 +14409,7 @@
         <v>32.8125</v>
       </c>
       <c r="AH112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.4420000000000001E-2</v>
       </c>
       <c r="AI112">
         <v>32.8125</v>
@@ -14522,19 +14525,19 @@
         <v>31.25</v>
       </c>
       <c r="AD113">
-        <v>4.1889999999999997E-2</v>
+        <v>4.1880000000000001E-2</v>
       </c>
       <c r="AE113">
         <v>31.25</v>
       </c>
       <c r="AF113">
-        <v>4.1869999999999997E-2</v>
+        <v>4.1880000000000001E-2</v>
       </c>
       <c r="AG113">
         <v>31.25</v>
       </c>
       <c r="AH113">
-        <v>4.2259999999999999E-2</v>
+        <v>4.2209999999999998E-2</v>
       </c>
       <c r="AI113">
         <v>31.25</v>
@@ -14584,7 +14587,7 @@
         <v>29.6875</v>
       </c>
       <c r="H114">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0149999999999998E-2</v>
       </c>
       <c r="I114">
         <v>29.6875</v>
@@ -14626,7 +14629,7 @@
         <v>29.6875</v>
       </c>
       <c r="V114">
-        <v>3.9780000000000003E-2</v>
+        <v>3.977E-2</v>
       </c>
       <c r="W114">
         <v>29.6875</v>
@@ -14650,13 +14653,13 @@
         <v>29.6875</v>
       </c>
       <c r="AD114">
-        <v>3.9789999999999999E-2</v>
+        <v>3.9809999999999998E-2</v>
       </c>
       <c r="AE114">
         <v>29.6875</v>
       </c>
       <c r="AF114">
-        <v>3.9759999999999997E-2</v>
+        <v>3.9750000000000001E-2</v>
       </c>
       <c r="AG114">
         <v>29.6875</v>
@@ -14766,7 +14769,7 @@
         <v>28.125</v>
       </c>
       <c r="Z115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.8030000000000001E-2</v>
       </c>
       <c r="AA115">
         <v>28.125</v>
@@ -14778,7 +14781,7 @@
         <v>28.125</v>
       </c>
       <c r="AD115">
-        <v>3.7679999999999998E-2</v>
+        <v>3.7659999999999999E-2</v>
       </c>
       <c r="AE115">
         <v>28.125</v>
@@ -14882,7 +14885,7 @@
         <v>26.5625</v>
       </c>
       <c r="V116">
-        <v>3.5569999999999997E-2</v>
+        <v>3.5540000000000002E-2</v>
       </c>
       <c r="W116">
         <v>26.5625</v>
@@ -14912,7 +14915,7 @@
         <v>26.5625</v>
       </c>
       <c r="AF116">
-        <v>3.5560000000000001E-2</v>
+        <v>3.5540000000000002E-2</v>
       </c>
       <c r="AG116">
         <v>26.5625</v>
@@ -15034,7 +15037,7 @@
         <v>25</v>
       </c>
       <c r="AD117">
-        <v>3.3489999999999999E-2</v>
+        <v>3.3500000000000002E-2</v>
       </c>
       <c r="AE117">
         <v>25</v>
@@ -15114,7 +15117,7 @@
         <v>23.4375</v>
       </c>
       <c r="N118">
-        <v>3.1379999999999998E-2</v>
+        <v>3.1370000000000002E-2</v>
       </c>
       <c r="O118">
         <v>23.4375</v>
@@ -15162,7 +15165,7 @@
         <v>23.4375</v>
       </c>
       <c r="AD118">
-        <v>3.1399999999999997E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
       <c r="AE118">
         <v>23.4375</v>
@@ -15174,7 +15177,7 @@
         <v>23.4375</v>
       </c>
       <c r="AH118">
-        <v>3.1660000000000001E-2</v>
+        <v>3.1609999999999999E-2</v>
       </c>
       <c r="AI118">
         <v>23.4375</v>
@@ -15266,7 +15269,7 @@
         <v>21.875</v>
       </c>
       <c r="V119">
-        <v>2.9270000000000001E-2</v>
+        <v>2.928E-2</v>
       </c>
       <c r="W119">
         <v>21.875</v>
@@ -15394,7 +15397,7 @@
         <v>20.3125</v>
       </c>
       <c r="V120">
-        <v>2.7179999999999999E-2</v>
+        <v>2.7189999999999999E-2</v>
       </c>
       <c r="W120">
         <v>20.3125</v>
@@ -15522,7 +15525,7 @@
         <v>18.75</v>
       </c>
       <c r="V121">
-        <v>2.5069999999999999E-2</v>
+        <v>2.5080000000000002E-2</v>
       </c>
       <c r="W121">
         <v>18.75</v>
@@ -15546,7 +15549,7 @@
         <v>18.75</v>
       </c>
       <c r="AD121">
-        <v>2.5080000000000002E-2</v>
+        <v>2.5069999999999999E-2</v>
       </c>
       <c r="AE121">
         <v>18.75</v>
@@ -15650,7 +15653,7 @@
         <v>17.1875</v>
       </c>
       <c r="V122">
-        <v>2.291E-2</v>
+        <v>2.29E-2</v>
       </c>
       <c r="W122">
         <v>17.1875</v>
@@ -15778,7 +15781,7 @@
         <v>15.625</v>
       </c>
       <c r="V123">
-        <v>1.976E-2</v>
+        <v>1.9740000000000001E-2</v>
       </c>
       <c r="W123">
         <v>15.625</v>
@@ -15802,7 +15805,7 @@
         <v>15.625</v>
       </c>
       <c r="AD123">
-        <v>2.069E-2</v>
+        <v>2.068E-2</v>
       </c>
       <c r="AE123">
         <v>15.625</v>
@@ -16034,7 +16037,7 @@
         <v>12.5</v>
       </c>
       <c r="V125" s="1">
-        <v>9.2623399999999995E-4</v>
+        <v>8.1245500000000001E-4</v>
       </c>
       <c r="W125">
         <v>12.5</v>
@@ -16162,7 +16165,7 @@
         <v>10.9375</v>
       </c>
       <c r="V126" s="1">
-        <v>6.4321800000000003E-6</v>
+        <v>7.8457000000000001E-6</v>
       </c>
       <c r="W126">
         <v>10.9375</v>
@@ -16186,7 +16189,7 @@
         <v>10.9375</v>
       </c>
       <c r="AD126" s="1">
-        <v>7.7186200000000003E-5</v>
+        <v>8.5455400000000002E-5</v>
       </c>
       <c r="AE126">
         <v>10.9375</v>
@@ -16698,7 +16701,7 @@
         <v>4.6875</v>
       </c>
       <c r="AD130" s="1">
-        <v>6.4321800000000003E-6</v>
+        <v>5.3324500000000001E-6</v>
       </c>
       <c r="AE130">
         <v>4.6875</v>
@@ -16826,7 +16829,7 @@
         <v>3.125</v>
       </c>
       <c r="AD131" s="1">
-        <v>1.28644E-5</v>
+        <v>1.745575E-5</v>
       </c>
       <c r="AE131">
         <v>3.125</v>
@@ -17058,7 +17061,7 @@
         <v>0</v>
       </c>
       <c r="V133" s="1">
-        <v>1.28644E-5</v>
+        <v>0</v>
       </c>
       <c r="W133">
         <v>0</v>
@@ -17082,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="AD133" s="1">
-        <v>6.4321800000000003E-6</v>
+        <v>5.3256999999999997E-6</v>
       </c>
       <c r="AE133">
         <v>0</v>
@@ -17187,7 +17190,7 @@
         <v>-1.5625</v>
       </c>
       <c r="V134" s="1">
-        <v>6.4321800000000003E-6</v>
+        <v>6.6325800000000001E-6</v>
       </c>
       <c r="W134">
         <v>-1.5625</v>
@@ -17573,7 +17576,7 @@
         <v>-6.25</v>
       </c>
       <c r="V137" s="1">
-        <v>1.9296500000000001E-5</v>
+        <v>2.85455E-5</v>
       </c>
       <c r="W137">
         <v>-6.25</v>
@@ -17597,7 +17600,7 @@
         <v>-6.25</v>
       </c>
       <c r="AD137" s="1">
-        <v>1.28644E-5</v>
+        <v>1.332577E-5</v>
       </c>
       <c r="AE137">
         <v>-6.25</v>
@@ -17701,7 +17704,7 @@
         <v>-7.8125</v>
       </c>
       <c r="V138" s="1">
-        <v>1.9296500000000001E-5</v>
+        <v>3.6254999999999998E-5</v>
       </c>
       <c r="W138">
         <v>-7.8125</v>
@@ -17725,7 +17728,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AD138" s="1">
-        <v>1.28644E-5</v>
+        <v>1.8955400000000002E-5</v>
       </c>
       <c r="AE138">
         <v>-7.8125</v>
@@ -17957,7 +17960,7 @@
         <v>-10.9375</v>
       </c>
       <c r="V140" s="1">
-        <v>1.9296500000000001E-5</v>
+        <v>1.4785400000000001E-5</v>
       </c>
       <c r="W140">
         <v>-10.9375</v>
@@ -17981,7 +17984,7 @@
         <v>-10.9375</v>
       </c>
       <c r="AD140" s="1">
-        <v>6.4321800000000003E-6</v>
+        <v>5.4235099999999997E-6</v>
       </c>
       <c r="AE140">
         <v>-10.9375</v>
@@ -18365,7 +18368,7 @@
         <v>-15.625</v>
       </c>
       <c r="AD143" s="1">
-        <v>1.28644E-5</v>
+        <v>1.7957399999999999E-5</v>
       </c>
       <c r="AE143">
         <v>-15.625</v>
@@ -19237,7 +19240,7 @@
         <v>-26.5625</v>
       </c>
       <c r="V150" s="1">
-        <v>1.9296500000000001E-5</v>
+        <v>0</v>
       </c>
       <c r="W150">
         <v>-26.5625</v>
@@ -20157,7 +20160,7 @@
         <v>-37.5</v>
       </c>
       <c r="AD157">
-        <v>-5.0529999999999999E-2</v>
+        <v>-5.0549999999999998E-2</v>
       </c>
       <c r="AE157">
         <v>-37.5</v>
@@ -20285,7 +20288,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AD158">
-        <v>-5.2650000000000002E-2</v>
+        <v>-5.262E-2</v>
       </c>
       <c r="AE158">
         <v>-39.0625</v>
@@ -20517,7 +20520,7 @@
         <v>-42.1875</v>
       </c>
       <c r="V160">
-        <v>-5.6820000000000002E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="W160">
         <v>-42.1875</v>
@@ -20541,7 +20544,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AD160">
-        <v>-5.6849999999999998E-2</v>
+        <v>-5.6840000000000002E-2</v>
       </c>
       <c r="AE160">
         <v>-42.1875</v>
@@ -20669,7 +20672,7 @@
         <v>-43.75</v>
       </c>
       <c r="AD161">
-        <v>-5.8959999999999999E-2</v>
+        <v>-5.8950000000000002E-2</v>
       </c>
       <c r="AE161">
         <v>-43.75</v>
@@ -20901,7 +20904,7 @@
         <v>-46.875</v>
       </c>
       <c r="V163">
-        <v>-6.3140000000000002E-2</v>
+        <v>-6.3109999999999999E-2</v>
       </c>
       <c r="W163">
         <v>-46.875</v>
@@ -20925,7 +20928,7 @@
         <v>-46.875</v>
       </c>
       <c r="AD163">
-        <v>-6.318E-2</v>
+        <v>-6.3170000000000004E-2</v>
       </c>
       <c r="AE163">
         <v>-46.875</v>
@@ -21145,7 +21148,7 @@
         <v>-50</v>
       </c>
       <c r="R165">
-        <v>-6.7390000000000005E-2</v>
+        <v>-6.7400000000000002E-2</v>
       </c>
       <c r="S165">
         <v>-50</v>
@@ -21157,7 +21160,7 @@
         <v>-50</v>
       </c>
       <c r="V165">
-        <v>-6.7360000000000003E-2</v>
+        <v>-6.7339999999999997E-2</v>
       </c>
       <c r="W165">
         <v>-50</v>
@@ -21309,7 +21312,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AD166">
-        <v>-6.9559999999999997E-2</v>
+        <v>-6.9550000000000001E-2</v>
       </c>
       <c r="AE166">
         <v>-51.5625</v>
@@ -21413,7 +21416,7 @@
         <v>-53.125</v>
       </c>
       <c r="V167">
-        <v>-7.1639999999999995E-2</v>
+        <v>-7.1620000000000003E-2</v>
       </c>
       <c r="W167">
         <v>-53.125</v>
@@ -21437,7 +21440,7 @@
         <v>-53.125</v>
       </c>
       <c r="AD167">
-        <v>-7.1669999999999998E-2</v>
+        <v>-7.1650000000000005E-2</v>
       </c>
       <c r="AE167">
         <v>-53.125</v>
@@ -21669,7 +21672,7 @@
         <v>-56.25</v>
       </c>
       <c r="V169">
-        <v>-7.5859999999999997E-2</v>
+        <v>-7.5880000000000003E-2</v>
       </c>
       <c r="W169">
         <v>-56.25</v>
@@ -21693,13 +21696,13 @@
         <v>-56.25</v>
       </c>
       <c r="AD169">
-        <v>-7.5899999999999995E-2</v>
+        <v>-7.5910000000000005E-2</v>
       </c>
       <c r="AE169">
         <v>-56.25</v>
       </c>
       <c r="AF169">
-        <v>-7.5859999999999997E-2</v>
+        <v>-7.5889999999999999E-2</v>
       </c>
       <c r="AG169">
         <v>-56.25</v>
@@ -21755,7 +21758,7 @@
         <v>-57.8125</v>
       </c>
       <c r="H170">
-        <v>-7.8710000000000002E-2</v>
+        <v>-7.868E-2</v>
       </c>
       <c r="I170">
         <v>-57.8125</v>
@@ -21797,7 +21800,7 @@
         <v>-57.8125</v>
       </c>
       <c r="V170">
-        <v>-7.7979999999999994E-2</v>
+        <v>-7.7990000000000004E-2</v>
       </c>
       <c r="W170">
         <v>-57.8125</v>
@@ -21955,7 +21958,7 @@
         <v>-59.375</v>
       </c>
       <c r="AF171">
-        <v>-8.0079999999999998E-2</v>
+        <v>-8.0100000000000005E-2</v>
       </c>
       <c r="AG171">
         <v>-59.375</v>
@@ -22011,7 +22014,7 @@
         <v>-60.9375</v>
       </c>
       <c r="H172">
-        <v>-8.3000000000000004E-2</v>
+        <v>-8.3099999999999993E-2</v>
       </c>
       <c r="I172">
         <v>-60.9375</v>
@@ -22053,7 +22056,7 @@
         <v>-60.9375</v>
       </c>
       <c r="V172">
-        <v>-8.2220000000000001E-2</v>
+        <v>-8.2210000000000005E-2</v>
       </c>
       <c r="W172">
         <v>-60.9375</v>
@@ -22077,13 +22080,13 @@
         <v>-60.9375</v>
       </c>
       <c r="AD172">
-        <v>-8.2229999999999998E-2</v>
+        <v>-8.2220000000000001E-2</v>
       </c>
       <c r="AE172">
         <v>-60.9375</v>
       </c>
       <c r="AF172">
-        <v>-8.2210000000000005E-2</v>
+        <v>-8.2199999999999995E-2</v>
       </c>
       <c r="AG172">
         <v>-60.9375</v>
@@ -22157,7 +22160,7 @@
         <v>-62.5</v>
       </c>
       <c r="N173">
-        <v>-8.4339999999999998E-2</v>
+        <v>-8.4349999999999994E-2</v>
       </c>
       <c r="O173">
         <v>-62.5</v>
@@ -22267,7 +22270,7 @@
         <v>-64.0625</v>
       </c>
       <c r="H174">
-        <v>-8.7290000000000006E-2</v>
+        <v>-8.7309999999999999E-2</v>
       </c>
       <c r="I174">
         <v>-64.0625</v>
@@ -22291,7 +22294,7 @@
         <v>-64.0625</v>
       </c>
       <c r="P174">
-        <v>-8.6480000000000001E-2</v>
+        <v>-8.6489999999999997E-2</v>
       </c>
       <c r="Q174">
         <v>-64.0625</v>
@@ -22333,7 +22336,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AD174">
-        <v>-8.6480000000000001E-2</v>
+        <v>-8.6470000000000005E-2</v>
       </c>
       <c r="AE174">
         <v>-64.0625</v>
@@ -22461,7 +22464,7 @@
         <v>-65.625</v>
       </c>
       <c r="AD175">
-        <v>-8.8609999999999994E-2</v>
+        <v>-8.8599999999999998E-2</v>
       </c>
       <c r="AE175">
         <v>-65.625</v>
@@ -22547,7 +22550,7 @@
         <v>-67.1875</v>
       </c>
       <c r="P176">
-        <v>-9.0730000000000005E-2</v>
+        <v>-9.0740000000000001E-2</v>
       </c>
       <c r="Q176">
         <v>-67.1875</v>
@@ -22589,7 +22592,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AD176">
-        <v>-9.0740000000000001E-2</v>
+        <v>-9.0730000000000005E-2</v>
       </c>
       <c r="AE176">
         <v>-67.1875</v>
@@ -22687,19 +22690,19 @@
         <v>-68.75</v>
       </c>
       <c r="T177">
-        <v>-9.2840000000000006E-2</v>
+        <v>-9.2869999999999994E-2</v>
       </c>
       <c r="U177">
         <v>-68.75</v>
       </c>
       <c r="V177">
-        <v>-9.2850000000000002E-2</v>
+        <v>-9.289E-2</v>
       </c>
       <c r="W177">
         <v>-68.75</v>
       </c>
       <c r="X177">
-        <v>-9.2850000000000002E-2</v>
+        <v>-9.282E-2</v>
       </c>
       <c r="Y177">
         <v>-68.75</v>
@@ -22815,7 +22818,7 @@
         <v>-70.3125</v>
       </c>
       <c r="T178">
-        <v>-9.4960000000000003E-2</v>
+        <v>-9.4969999999999999E-2</v>
       </c>
       <c r="U178">
         <v>-70.3125</v>
@@ -22845,7 +22848,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AD178">
-        <v>-9.5000000000000001E-2</v>
+        <v>-9.5500000000000002E-2</v>
       </c>
       <c r="AE178">
         <v>-70.3125</v>
@@ -22895,7 +22898,7 @@
         <v>-71.875</v>
       </c>
       <c r="D179">
-        <v>-9.7110000000000002E-2</v>
+        <v>-9.7119999999999998E-2</v>
       </c>
       <c r="E179">
         <v>-71.875</v>
@@ -22949,7 +22952,7 @@
         <v>-71.875</v>
       </c>
       <c r="V179">
-        <v>-9.7110000000000002E-2</v>
+        <v>-9.7119999999999998E-2</v>
       </c>
       <c r="W179">
         <v>-71.875</v>
@@ -23193,7 +23196,7 @@
         <v>-75</v>
       </c>
       <c r="R181">
-        <v>-0.1014</v>
+        <v>-0.10150000000000001</v>
       </c>
       <c r="S181">
         <v>-75</v>
@@ -23205,13 +23208,13 @@
         <v>-75</v>
       </c>
       <c r="V181">
-        <v>-0.10138</v>
+        <v>-0.1014</v>
       </c>
       <c r="W181">
         <v>-75</v>
       </c>
       <c r="X181">
-        <v>-0.10138999999999999</v>
+        <v>-0.10141</v>
       </c>
       <c r="Y181">
         <v>-75</v>
@@ -23357,7 +23360,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AD182">
-        <v>-0.10353</v>
+        <v>-0.10353999999999999</v>
       </c>
       <c r="AE182">
         <v>-76.5625</v>
@@ -23461,7 +23464,7 @@
         <v>-78.125</v>
       </c>
       <c r="V183">
-        <v>-0.10566</v>
+        <v>-0.10569000000000001</v>
       </c>
       <c r="W183">
         <v>-78.125</v>
@@ -23565,7 +23568,7 @@
         <v>-79.6875</v>
       </c>
       <c r="N184">
-        <v>-0.10783</v>
+        <v>-0.10785</v>
       </c>
       <c r="O184">
         <v>-79.6875</v>
@@ -23613,7 +23616,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AD184">
-        <v>-0.10783</v>
+        <v>-0.10784000000000001</v>
       </c>
       <c r="AE184">
         <v>-79.6875</v>
@@ -23717,7 +23720,7 @@
         <v>-81.25</v>
       </c>
       <c r="V185">
-        <v>-0.10997999999999999</v>
+        <v>-0.10999</v>
       </c>
       <c r="W185">
         <v>-81.25</v>
@@ -23741,7 +23744,7 @@
         <v>-81.25</v>
       </c>
       <c r="AD185">
-        <v>-0.10997999999999999</v>
+        <v>-0.10996</v>
       </c>
       <c r="AE185">
         <v>-81.25</v>
@@ -23869,7 +23872,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AD186">
-        <v>-0.11215</v>
+        <v>-0.11211</v>
       </c>
       <c r="AE186">
         <v>-82.8125</v>
@@ -23973,7 +23976,7 @@
         <v>-84.375</v>
       </c>
       <c r="V187">
-        <v>-0.11430999999999999</v>
+        <v>-0.11428000000000001</v>
       </c>
       <c r="W187">
         <v>-84.375</v>
@@ -23997,7 +24000,7 @@
         <v>-84.375</v>
       </c>
       <c r="AD187">
-        <v>-0.11430999999999999</v>
+        <v>-0.11432</v>
       </c>
       <c r="AE187">
         <v>-84.375</v>
@@ -24077,7 +24080,7 @@
         <v>-85.9375</v>
       </c>
       <c r="N188">
-        <v>-0.11649</v>
+        <v>-0.11648</v>
       </c>
       <c r="O188">
         <v>-85.9375</v>
@@ -24125,7 +24128,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AD188">
-        <v>-0.11649</v>
+        <v>-0.11648</v>
       </c>
       <c r="AE188">
         <v>-85.9375</v>
@@ -24229,7 +24232,7 @@
         <v>-87.5</v>
       </c>
       <c r="V189">
-        <v>-0.11865000000000001</v>
+        <v>-0.11864</v>
       </c>
       <c r="W189">
         <v>-87.5</v>
@@ -24253,7 +24256,7 @@
         <v>-87.5</v>
       </c>
       <c r="AD189">
-        <v>-0.11865000000000001</v>
+        <v>-0.11866</v>
       </c>
       <c r="AE189">
         <v>-87.5</v>
@@ -24381,7 +24384,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AD190">
-        <v>-0.12085</v>
+        <v>-0.12086</v>
       </c>
       <c r="AE190">
         <v>-89.0625</v>
@@ -24485,7 +24488,7 @@
         <v>-90.625</v>
       </c>
       <c r="V191">
-        <v>-0.12302</v>
+        <v>-0.12300999999999999</v>
       </c>
       <c r="W191">
         <v>-90.625</v>
@@ -24613,7 +24616,7 @@
         <v>-92.1875</v>
       </c>
       <c r="V192">
-        <v>-0.12520999999999999</v>
+        <v>-0.12523000000000001</v>
       </c>
       <c r="W192">
         <v>-92.1875</v>
@@ -24637,7 +24640,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AD192">
-        <v>-0.12522</v>
+        <v>-0.12523000000000001</v>
       </c>
       <c r="AE192">
         <v>-92.1875</v>
@@ -24741,7 +24744,7 @@
         <v>-93.75</v>
       </c>
       <c r="V193">
-        <v>-0.12742000000000001</v>
+        <v>-0.12744</v>
       </c>
       <c r="W193">
         <v>-93.75</v>
@@ -24869,7 +24872,7 @@
         <v>-95.3125</v>
       </c>
       <c r="V194">
-        <v>-0.12961</v>
+        <v>-0.12962000000000001</v>
       </c>
       <c r="W194">
         <v>-95.3125</v>
@@ -24893,7 +24896,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AD194">
-        <v>-0.12961</v>
+        <v>-0.12962000000000001</v>
       </c>
       <c r="AE194">
         <v>-95.3125</v>
@@ -24985,7 +24988,7 @@
         <v>-96.875</v>
       </c>
       <c r="R195">
-        <v>-0.13183</v>
+        <v>-0.13184000000000001</v>
       </c>
       <c r="S195">
         <v>-96.875</v>
@@ -24997,7 +25000,7 @@
         <v>-96.875</v>
       </c>
       <c r="V195">
-        <v>-0.13181000000000001</v>
+        <v>-0.13181999999999999</v>
       </c>
       <c r="W195">
         <v>-96.875</v>
@@ -25277,7 +25280,7 @@
         <v>-100</v>
       </c>
       <c r="AD197">
-        <v>-0.13600999999999999</v>
+        <v>-0.13602</v>
       </c>
       <c r="AE197">
         <v>-100</v>
@@ -25381,7 +25384,7 @@
         <v>-98.4375</v>
       </c>
       <c r="V198">
-        <v>-0.13388</v>
+        <v>-0.13389000000000001</v>
       </c>
       <c r="W198">
         <v>-98.4375</v>
@@ -25405,7 +25408,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AD198">
-        <v>-0.13389000000000001</v>
+        <v>-0.13389999999999999</v>
       </c>
       <c r="AE198">
         <v>-98.4375</v>
@@ -25509,7 +25512,7 @@
         <v>-96.875</v>
       </c>
       <c r="V199">
-        <v>-0.13167000000000001</v>
+        <v>-0.13167999999999999</v>
       </c>
       <c r="W199">
         <v>-96.875</v>
@@ -25533,7 +25536,7 @@
         <v>-96.875</v>
       </c>
       <c r="AD199">
-        <v>-0.13169</v>
+        <v>-0.13170999999999999</v>
       </c>
       <c r="AE199">
         <v>-96.875</v>
@@ -25613,7 +25616,7 @@
         <v>-95.3125</v>
       </c>
       <c r="N200">
-        <v>-0.12945999999999999</v>
+        <v>-0.12945000000000001</v>
       </c>
       <c r="O200">
         <v>-95.3125</v>
@@ -25661,7 +25664,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AD200">
-        <v>-0.12948000000000001</v>
+        <v>-0.12950999999999999</v>
       </c>
       <c r="AE200">
         <v>-95.3125</v>
@@ -25789,7 +25792,7 @@
         <v>-93.75</v>
       </c>
       <c r="AD201">
-        <v>-0.12726999999999999</v>
+        <v>-0.12728999999999999</v>
       </c>
       <c r="AE201">
         <v>-93.75</v>
@@ -25917,7 +25920,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AD202">
-        <v>-0.12508</v>
+        <v>-0.12511</v>
       </c>
       <c r="AE202">
         <v>-92.1875</v>
@@ -26021,7 +26024,7 @@
         <v>-90.625</v>
       </c>
       <c r="V203">
-        <v>-0.12286</v>
+        <v>-0.12288</v>
       </c>
       <c r="W203">
         <v>-90.625</v>
@@ -26149,7 +26152,7 @@
         <v>-89.0625</v>
       </c>
       <c r="V204">
-        <v>-0.12067</v>
+        <v>-0.12068</v>
       </c>
       <c r="W204">
         <v>-89.0625</v>
@@ -26277,7 +26280,7 @@
         <v>-87.5</v>
       </c>
       <c r="V205">
-        <v>-0.11847000000000001</v>
+        <v>-0.11848</v>
       </c>
       <c r="W205">
         <v>-87.5</v>
@@ -26301,7 +26304,7 @@
         <v>-87.5</v>
       </c>
       <c r="AD205">
-        <v>-0.11849</v>
+        <v>-0.11851</v>
       </c>
       <c r="AE205">
         <v>-87.5</v>
@@ -26393,7 +26396,7 @@
         <v>-85.9375</v>
       </c>
       <c r="R206">
-        <v>-0.11632000000000001</v>
+        <v>-0.11633</v>
       </c>
       <c r="S206">
         <v>-85.9375</v>
@@ -26533,7 +26536,7 @@
         <v>-84.375</v>
       </c>
       <c r="V207">
-        <v>-0.11412</v>
+        <v>-0.11411</v>
       </c>
       <c r="W207">
         <v>-84.375</v>
@@ -26655,7 +26658,7 @@
         <v>-82.8125</v>
       </c>
       <c r="T208">
-        <v>-0.11193</v>
+        <v>-0.11192000000000001</v>
       </c>
       <c r="U208">
         <v>-82.8125</v>
@@ -26685,7 +26688,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AD208">
-        <v>-0.11198</v>
+        <v>-0.11199000000000001</v>
       </c>
       <c r="AE208">
         <v>-82.8125</v>
@@ -26813,7 +26816,7 @@
         <v>-81.25</v>
       </c>
       <c r="AD209">
-        <v>-0.10981</v>
+        <v>-0.10979999999999999</v>
       </c>
       <c r="AE209">
         <v>-81.25</v>
@@ -26911,7 +26914,7 @@
         <v>-79.6875</v>
       </c>
       <c r="T210">
-        <v>-0.10761999999999999</v>
+        <v>-0.10763</v>
       </c>
       <c r="U210">
         <v>-79.6875</v>
@@ -26947,7 +26950,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AF210">
-        <v>-0.10761999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="AG210">
         <v>-79.6875</v>
@@ -27039,7 +27042,7 @@
         <v>-78.125</v>
       </c>
       <c r="T211">
-        <v>-0.10546</v>
+        <v>-0.10544000000000001</v>
       </c>
       <c r="U211">
         <v>-78.125</v>
@@ -27069,7 +27072,7 @@
         <v>-78.125</v>
       </c>
       <c r="AD211">
-        <v>-0.10549</v>
+        <v>-0.1055</v>
       </c>
       <c r="AE211">
         <v>-78.125</v>
@@ -27119,7 +27122,7 @@
         <v>-76.5625</v>
       </c>
       <c r="D212">
-        <v>-0.10333000000000001</v>
+        <v>-0.10331</v>
       </c>
       <c r="E212">
         <v>-76.5625</v>
@@ -27173,7 +27176,7 @@
         <v>-76.5625</v>
       </c>
       <c r="V212">
-        <v>-0.10331</v>
+        <v>-0.10333000000000001</v>
       </c>
       <c r="W212">
         <v>-76.5625</v>
@@ -27197,7 +27200,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AD212">
-        <v>-0.10335</v>
+        <v>-0.10334</v>
       </c>
       <c r="AE212">
         <v>-76.5625</v>
@@ -27295,7 +27298,7 @@
         <v>-75</v>
       </c>
       <c r="T213">
-        <v>-0.10117</v>
+        <v>-0.10118000000000001</v>
       </c>
       <c r="U213">
         <v>-75</v>
@@ -27331,7 +27334,7 @@
         <v>-75</v>
       </c>
       <c r="AF213">
-        <v>-0.10118000000000001</v>
+        <v>-0.10116</v>
       </c>
       <c r="AG213">
         <v>-75</v>
@@ -27375,7 +27378,7 @@
         <v>-73.4375</v>
       </c>
       <c r="D214">
-        <v>-9.9040000000000003E-2</v>
+        <v>-9.9049999999999999E-2</v>
       </c>
       <c r="E214">
         <v>-73.4375</v>
@@ -27429,13 +27432,13 @@
         <v>-73.4375</v>
       </c>
       <c r="V214">
-        <v>-9.9040000000000003E-2</v>
+        <v>-9.9049999999999999E-2</v>
       </c>
       <c r="W214">
         <v>-73.4375</v>
       </c>
       <c r="X214">
-        <v>-9.9040000000000003E-2</v>
+        <v>-9.9049999999999999E-2</v>
       </c>
       <c r="Y214">
         <v>-73.4375</v>
@@ -27453,7 +27456,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AD214">
-        <v>-9.9059999999999995E-2</v>
+        <v>-9.9049999999999999E-2</v>
       </c>
       <c r="AE214">
         <v>-73.4375</v>
@@ -27551,7 +27554,7 @@
         <v>-71.875</v>
       </c>
       <c r="T215">
-        <v>-9.6879999999999994E-2</v>
+        <v>-9.6869999999999998E-2</v>
       </c>
       <c r="U215">
         <v>-71.875</v>
@@ -27685,7 +27688,7 @@
         <v>-70.3125</v>
       </c>
       <c r="V216">
-        <v>-9.4769999999999993E-2</v>
+        <v>-9.4780000000000003E-2</v>
       </c>
       <c r="W216">
         <v>-70.3125</v>
@@ -27715,7 +27718,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AF216">
-        <v>-9.4769999999999993E-2</v>
+        <v>-9.4759999999999997E-2</v>
       </c>
       <c r="AG216">
         <v>-70.3125</v>
@@ -27813,7 +27816,7 @@
         <v>-68.75</v>
       </c>
       <c r="V217">
-        <v>-9.2630000000000004E-2</v>
+        <v>-9.2660000000000006E-2</v>
       </c>
       <c r="W217">
         <v>-68.75</v>
@@ -27843,7 +27846,7 @@
         <v>-68.75</v>
       </c>
       <c r="AF217">
-        <v>-9.264E-2</v>
+        <v>-9.2660000000000006E-2</v>
       </c>
       <c r="AG217">
         <v>-68.75</v>
@@ -27929,7 +27932,7 @@
         <v>-67.1875</v>
       </c>
       <c r="R218">
-        <v>-9.0520000000000003E-2</v>
+        <v>-9.0509999999999993E-2</v>
       </c>
       <c r="S218">
         <v>-67.1875</v>
@@ -27971,7 +27974,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AF218">
-        <v>-9.0520000000000003E-2</v>
+        <v>-9.0550000000000005E-2</v>
       </c>
       <c r="AG218">
         <v>-67.1875</v>
@@ -28069,7 +28072,7 @@
         <v>-65.625</v>
       </c>
       <c r="V219">
-        <v>-8.8370000000000004E-2</v>
+        <v>-8.8359999999999994E-2</v>
       </c>
       <c r="W219">
         <v>-65.625</v>
@@ -28093,7 +28096,7 @@
         <v>-65.625</v>
       </c>
       <c r="AD219">
-        <v>-8.838E-2</v>
+        <v>-8.8370000000000004E-2</v>
       </c>
       <c r="AE219">
         <v>-65.625</v>
@@ -28221,13 +28224,13 @@
         <v>-64.0625</v>
       </c>
       <c r="AD220">
-        <v>-8.6260000000000003E-2</v>
+        <v>-8.6269999999999999E-2</v>
       </c>
       <c r="AE220">
         <v>-64.0625</v>
       </c>
       <c r="AF220">
-        <v>-8.6260000000000003E-2</v>
+        <v>-8.6249999999999993E-2</v>
       </c>
       <c r="AG220">
         <v>-64.0625</v>
@@ -28301,7 +28304,7 @@
         <v>-62.5</v>
       </c>
       <c r="N221">
-        <v>-8.4110000000000004E-2</v>
+        <v>-8.4099999999999994E-2</v>
       </c>
       <c r="O221">
         <v>-62.5</v>
@@ -28429,7 +28432,7 @@
         <v>-60.9375</v>
       </c>
       <c r="N222">
-        <v>-8.1989999999999993E-2</v>
+        <v>-8.1949999999999995E-2</v>
       </c>
       <c r="O222">
         <v>-60.9375</v>
@@ -28441,7 +28444,7 @@
         <v>-60.9375</v>
       </c>
       <c r="R222">
-        <v>-8.2019999999999996E-2</v>
+        <v>-8.2030000000000006E-2</v>
       </c>
       <c r="S222">
         <v>-60.9375</v>
@@ -28477,7 +28480,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AD222">
-        <v>-8.2019999999999996E-2</v>
+        <v>-8.201E-2</v>
       </c>
       <c r="AE222">
         <v>-60.9375</v>
@@ -28489,7 +28492,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AH222">
-        <v>-8.2750000000000004E-2</v>
+        <v>-8.2769999999999996E-2</v>
       </c>
       <c r="AI222">
         <v>-60.9375</v>
@@ -28605,13 +28608,13 @@
         <v>-59.375</v>
       </c>
       <c r="AD223">
-        <v>-7.9869999999999997E-2</v>
+        <v>-7.9880000000000007E-2</v>
       </c>
       <c r="AE223">
         <v>-59.375</v>
       </c>
       <c r="AF223">
-        <v>-7.9880000000000007E-2</v>
+        <v>-7.9890000000000003E-2</v>
       </c>
       <c r="AG223">
         <v>-59.375</v>
@@ -28685,7 +28688,7 @@
         <v>-57.8125</v>
       </c>
       <c r="N224">
-        <v>-7.775E-2</v>
+        <v>-7.7770000000000006E-2</v>
       </c>
       <c r="O224">
         <v>-57.8125</v>
@@ -28739,13 +28742,13 @@
         <v>-57.8125</v>
       </c>
       <c r="AF224">
-        <v>-7.7770000000000006E-2</v>
+        <v>-7.7759999999999996E-2</v>
       </c>
       <c r="AG224">
         <v>-57.8125</v>
       </c>
       <c r="AH224">
-        <v>-7.8469999999999998E-2</v>
+        <v>-7.8479999999999994E-2</v>
       </c>
       <c r="AI224">
         <v>-57.8125</v>
@@ -28795,7 +28798,7 @@
         <v>-56.25</v>
       </c>
       <c r="H225">
-        <v>-7.6340000000000005E-2</v>
+        <v>-7.6359999999999997E-2</v>
       </c>
       <c r="I225">
         <v>-56.25</v>
@@ -28867,7 +28870,7 @@
         <v>-56.25</v>
       </c>
       <c r="AF225">
-        <v>-7.5649999999999995E-2</v>
+        <v>-7.5660000000000005E-2</v>
       </c>
       <c r="AG225">
         <v>-56.25</v>
@@ -28965,7 +28968,7 @@
         <v>-54.6875</v>
       </c>
       <c r="V226">
-        <v>-7.3529999999999998E-2</v>
+        <v>-7.3550000000000004E-2</v>
       </c>
       <c r="W226">
         <v>-54.6875</v>
@@ -29117,7 +29120,7 @@
         <v>-53.125</v>
       </c>
       <c r="AD227">
-        <v>-7.1419999999999997E-2</v>
+        <v>-7.145E-2</v>
       </c>
       <c r="AE227">
         <v>-53.125</v>
@@ -29129,7 +29132,7 @@
         <v>-53.125</v>
       </c>
       <c r="AH227">
-        <v>-7.2080000000000005E-2</v>
+        <v>-7.2069999999999995E-2</v>
       </c>
       <c r="AI227">
         <v>-53.125</v>
@@ -29221,7 +29224,7 @@
         <v>-51.5625</v>
       </c>
       <c r="V228">
-        <v>-6.93E-2</v>
+        <v>-6.9309999999999997E-2</v>
       </c>
       <c r="W228">
         <v>-51.5625</v>
@@ -29349,7 +29352,7 @@
         <v>-50</v>
       </c>
       <c r="V229">
-        <v>-6.7129999999999995E-2</v>
+        <v>-6.7150000000000001E-2</v>
       </c>
       <c r="W229">
         <v>-50</v>
@@ -29379,7 +29382,7 @@
         <v>-50</v>
       </c>
       <c r="AF229">
-        <v>-6.7140000000000005E-2</v>
+        <v>-6.7150000000000001E-2</v>
       </c>
       <c r="AG229">
         <v>-50</v>
@@ -29423,7 +29426,7 @@
         <v>-48.4375</v>
       </c>
       <c r="D230">
-        <v>-6.5030000000000004E-2</v>
+        <v>-6.5019999999999994E-2</v>
       </c>
       <c r="E230">
         <v>-48.4375</v>
@@ -29453,7 +29456,7 @@
         <v>-48.4375</v>
       </c>
       <c r="N230">
-        <v>-6.5030000000000004E-2</v>
+        <v>-6.5040000000000001E-2</v>
       </c>
       <c r="O230">
         <v>-48.4375</v>
@@ -29507,7 +29510,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AF230">
-        <v>-6.5040000000000001E-2</v>
+        <v>-6.5049999999999997E-2</v>
       </c>
       <c r="AG230">
         <v>-48.4375</v>
@@ -29551,7 +29554,7 @@
         <v>-46.875</v>
       </c>
       <c r="D231">
-        <v>-6.2909999999999994E-2</v>
+        <v>-6.2920000000000004E-2</v>
       </c>
       <c r="E231">
         <v>-46.875</v>
@@ -29629,13 +29632,13 @@
         <v>-46.875</v>
       </c>
       <c r="AD231">
-        <v>-6.2920000000000004E-2</v>
+        <v>-6.2909999999999994E-2</v>
       </c>
       <c r="AE231">
         <v>-46.875</v>
       </c>
       <c r="AF231">
-        <v>-6.2920000000000004E-2</v>
+        <v>-6.293E-2</v>
       </c>
       <c r="AG231">
         <v>-46.875</v>
@@ -29733,7 +29736,7 @@
         <v>-45.3125</v>
       </c>
       <c r="V232">
-        <v>-6.08E-2</v>
+        <v>-6.0819999999999999E-2</v>
       </c>
       <c r="W232">
         <v>-45.3125</v>
@@ -29757,7 +29760,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AD232">
-        <v>-6.0819999999999999E-2</v>
+        <v>-6.08E-2</v>
       </c>
       <c r="AE232">
         <v>-45.3125</v>
@@ -29807,7 +29810,7 @@
         <v>-43.75</v>
       </c>
       <c r="D233">
-        <v>-5.8709999999999998E-2</v>
+        <v>-5.8720000000000001E-2</v>
       </c>
       <c r="E233">
         <v>-43.75</v>
@@ -29861,7 +29864,7 @@
         <v>-43.75</v>
       </c>
       <c r="V233">
-        <v>-5.8709999999999998E-2</v>
+        <v>-5.8720000000000001E-2</v>
       </c>
       <c r="W233">
         <v>-43.75</v>
@@ -29885,7 +29888,7 @@
         <v>-43.75</v>
       </c>
       <c r="AD233">
-        <v>-5.8709999999999998E-2</v>
+        <v>-5.8700000000000002E-2</v>
       </c>
       <c r="AE233">
         <v>-43.75</v>
@@ -29935,7 +29938,7 @@
         <v>-42.1875</v>
       </c>
       <c r="D234">
-        <v>-5.6599999999999998E-2</v>
+        <v>-5.6619999999999997E-2</v>
       </c>
       <c r="E234">
         <v>-42.1875</v>
@@ -30013,7 +30016,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AD234">
-        <v>-5.6599999999999998E-2</v>
+        <v>-5.67E-2</v>
       </c>
       <c r="AE234">
         <v>-42.1875</v>
@@ -30063,7 +30066,7 @@
         <v>-40.625</v>
       </c>
       <c r="D235">
-        <v>-5.4489999999999997E-2</v>
+        <v>-5.45E-2</v>
       </c>
       <c r="E235">
         <v>-40.625</v>
@@ -30117,7 +30120,7 @@
         <v>-40.625</v>
       </c>
       <c r="V235">
-        <v>-5.4489999999999997E-2</v>
+        <v>-5.45E-2</v>
       </c>
       <c r="W235">
         <v>-40.625</v>
@@ -30141,7 +30144,7 @@
         <v>-40.625</v>
       </c>
       <c r="AD235">
-        <v>-5.4489999999999997E-2</v>
+        <v>-5.45E-2</v>
       </c>
       <c r="AE235">
         <v>-40.625</v>
@@ -30245,7 +30248,7 @@
         <v>-39.0625</v>
       </c>
       <c r="V236">
-        <v>-5.2380000000000003E-2</v>
+        <v>-5.2389999999999999E-2</v>
       </c>
       <c r="W236">
         <v>-39.0625</v>
@@ -30263,13 +30266,13 @@
         <v>-39.0625</v>
       </c>
       <c r="AB236">
-        <v>-5.2380000000000003E-2</v>
+        <v>-5.237E-2</v>
       </c>
       <c r="AC236">
         <v>-39.0625</v>
       </c>
       <c r="AD236">
-        <v>-5.2400000000000002E-2</v>
+        <v>-5.2409999999999998E-2</v>
       </c>
       <c r="AE236">
         <v>-39.0625</v>
@@ -30319,7 +30322,7 @@
         <v>-37.5</v>
       </c>
       <c r="D237">
-        <v>-5.0270000000000002E-2</v>
+        <v>-5.0279999999999998E-2</v>
       </c>
       <c r="E237">
         <v>-37.5</v>
@@ -30391,13 +30394,13 @@
         <v>-37.5</v>
       </c>
       <c r="AB237">
-        <v>-5.0259999999999999E-2</v>
+        <v>-5.0270000000000002E-2</v>
       </c>
       <c r="AC237">
         <v>-37.5</v>
       </c>
       <c r="AD237">
-        <v>-5.0270000000000002E-2</v>
+        <v>-5.0279999999999998E-2</v>
       </c>
       <c r="AE237">
         <v>-37.5</v>
@@ -30501,7 +30504,7 @@
         <v>-35.9375</v>
       </c>
       <c r="V238">
-        <v>-4.8160000000000001E-2</v>
+        <v>-4.8149999999999998E-2</v>
       </c>
       <c r="W238">
         <v>-35.9375</v>
@@ -30519,13 +30522,13 @@
         <v>-35.9375</v>
       </c>
       <c r="AB238">
-        <v>-4.8160000000000001E-2</v>
+        <v>-4.8149999999999998E-2</v>
       </c>
       <c r="AC238">
         <v>-35.9375</v>
       </c>
       <c r="AD238">
-        <v>-4.8169999999999998E-2</v>
+        <v>-4.8180000000000001E-2</v>
       </c>
       <c r="AE238">
         <v>-35.9375</v>
@@ -30647,7 +30650,7 @@
         <v>-34.375</v>
       </c>
       <c r="AB239">
-        <v>-4.6050000000000001E-2</v>
+        <v>-4.6059999999999997E-2</v>
       </c>
       <c r="AC239">
         <v>-34.375</v>
@@ -30775,7 +30778,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AB240">
-        <v>-4.3950000000000003E-2</v>
+        <v>-4.3909999999999998E-2</v>
       </c>
       <c r="AC240">
         <v>-32.8125</v>
@@ -30885,7 +30888,7 @@
         <v>-31.25</v>
       </c>
       <c r="V241">
-        <v>-4.1849999999999998E-2</v>
+        <v>-4.1880000000000001E-2</v>
       </c>
       <c r="W241">
         <v>-31.25</v>
@@ -30909,7 +30912,7 @@
         <v>-31.25</v>
       </c>
       <c r="AD241">
-        <v>-4.1869999999999997E-2</v>
+        <v>-4.1880000000000001E-2</v>
       </c>
       <c r="AE241">
         <v>-31.25</v>
@@ -31031,13 +31034,13 @@
         <v>-29.6875</v>
       </c>
       <c r="AB242">
-        <v>-3.9750000000000001E-2</v>
+        <v>-3.9759999999999997E-2</v>
       </c>
       <c r="AC242">
         <v>-29.6875</v>
       </c>
       <c r="AD242">
-        <v>-3.9759999999999997E-2</v>
+        <v>-3.977E-2</v>
       </c>
       <c r="AE242">
         <v>-29.6875</v>
@@ -31135,13 +31138,13 @@
         <v>-28.125</v>
       </c>
       <c r="T243">
-        <v>-3.7650000000000003E-2</v>
+        <v>-3.764E-2</v>
       </c>
       <c r="U243">
         <v>-28.125</v>
       </c>
       <c r="V243">
-        <v>-3.7650000000000003E-2</v>
+        <v>-3.7659999999999999E-2</v>
       </c>
       <c r="W243">
         <v>-28.125</v>
@@ -31245,7 +31248,7 @@
         <v>-26.5625</v>
       </c>
       <c r="N244">
-        <v>-3.5540000000000002E-2</v>
+        <v>-3.5549999999999998E-2</v>
       </c>
       <c r="O244">
         <v>-26.5625</v>
@@ -31287,13 +31290,13 @@
         <v>-26.5625</v>
       </c>
       <c r="AB244">
-        <v>-3.5540000000000002E-2</v>
+        <v>-3.5549999999999998E-2</v>
       </c>
       <c r="AC244">
         <v>-26.5625</v>
       </c>
       <c r="AD244">
-        <v>-3.5549999999999998E-2</v>
+        <v>-3.5580000000000001E-2</v>
       </c>
       <c r="AE244">
         <v>-26.5625</v>
@@ -31397,7 +31400,7 @@
         <v>-25</v>
       </c>
       <c r="V245">
-        <v>-3.3439999999999998E-2</v>
+        <v>-3.3450000000000001E-2</v>
       </c>
       <c r="W245">
         <v>-25</v>
@@ -31525,7 +31528,7 @@
         <v>-23.4375</v>
       </c>
       <c r="V246">
-        <v>-3.1350000000000003E-2</v>
+        <v>-3.1359999999999999E-2</v>
       </c>
       <c r="W246">
         <v>-23.4375</v>
@@ -31543,13 +31546,13 @@
         <v>-23.4375</v>
       </c>
       <c r="AB246">
-        <v>-3.134E-2</v>
+        <v>-3.1320000000000001E-2</v>
       </c>
       <c r="AC246">
         <v>-23.4375</v>
       </c>
       <c r="AD246">
-        <v>-3.1350000000000003E-2</v>
+        <v>-3.1359999999999999E-2</v>
       </c>
       <c r="AE246">
         <v>-23.4375</v>
@@ -31653,7 +31656,7 @@
         <v>-21.875</v>
       </c>
       <c r="V247">
-        <v>-2.9229999999999999E-2</v>
+        <v>-2.9250000000000002E-2</v>
       </c>
       <c r="W247">
         <v>-21.875</v>
@@ -31805,7 +31808,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AD248">
-        <v>-2.7140000000000001E-2</v>
+        <v>-2.7150000000000001E-2</v>
       </c>
       <c r="AE248">
         <v>-20.3125</v>
@@ -31909,7 +31912,7 @@
         <v>-18.75</v>
       </c>
       <c r="V249">
-        <v>-2.503E-2</v>
+        <v>-2.504E-2</v>
       </c>
       <c r="W249">
         <v>-18.75</v>
@@ -32037,7 +32040,7 @@
         <v>-17.1875</v>
       </c>
       <c r="V250">
-        <v>-2.2939999999999999E-2</v>
+        <v>-2.2950000000000002E-2</v>
       </c>
       <c r="W250">
         <v>-17.1875</v>
@@ -32061,7 +32064,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AD250">
-        <v>-2.2939999999999999E-2</v>
+        <v>-2.2950000000000002E-2</v>
       </c>
       <c r="AE250">
         <v>-17.1875</v>
@@ -32189,7 +32192,7 @@
         <v>-15.625</v>
       </c>
       <c r="AD251">
-        <v>-2.0809999999999999E-2</v>
+        <v>-2.085E-2</v>
       </c>
       <c r="AE251">
         <v>-15.625</v>
@@ -32293,7 +32296,7 @@
         <v>-14.0625</v>
       </c>
       <c r="V252">
-        <v>-1.7989999999999999E-2</v>
+        <v>-1.7979999999999999E-2</v>
       </c>
       <c r="W252">
         <v>-14.0625</v>
@@ -32445,7 +32448,7 @@
         <v>-12.5</v>
       </c>
       <c r="AD253">
-        <v>-1.5469999999999999E-2</v>
+        <v>-1.5480000000000001E-2</v>
       </c>
       <c r="AE253">
         <v>-12.5</v>
@@ -32573,7 +32576,7 @@
         <v>-10.9375</v>
       </c>
       <c r="AD254" s="1">
-        <v>-1.069E-2</v>
+        <v>-1.0670000000000001E-2</v>
       </c>
       <c r="AE254">
         <v>-10.9375</v>
@@ -32701,7 +32704,7 @@
         <v>-9.375</v>
       </c>
       <c r="AD255">
-        <v>-4.5399999999999998E-3</v>
+        <v>-4.5199999999999997E-3</v>
       </c>
       <c r="AE255">
         <v>-9.375</v>
@@ -32829,7 +32832,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AD256" s="1">
-        <v>-1.80101E-4</v>
+        <v>-1.6257399999999999E-4</v>
       </c>
       <c r="AE256">
         <v>-7.8125</v>
@@ -32957,7 +32960,7 @@
         <v>-6.25</v>
       </c>
       <c r="AD257" s="1">
-        <v>1.28644E-5</v>
+        <v>2.4575699999999999E-5</v>
       </c>
       <c r="AE257">
         <v>-6.25</v>
@@ -33061,7 +33064,7 @@
         <v>-4.6875</v>
       </c>
       <c r="V258" s="1">
-        <v>1.9296500000000001E-5</v>
+        <v>0</v>
       </c>
       <c r="W258">
         <v>-4.6875</v>
@@ -33085,7 +33088,7 @@
         <v>-4.6875</v>
       </c>
       <c r="AD258" s="1">
-        <v>1.28644E-5</v>
+        <v>1.3854570000000001E-5</v>
       </c>
       <c r="AE258">
         <v>-4.6875</v>
@@ -33213,7 +33216,7 @@
         <v>-3.125</v>
       </c>
       <c r="AD259" s="1">
-        <v>1.9296500000000001E-5</v>
+        <v>1.8447499999999999E-5</v>
       </c>
       <c r="AE259">
         <v>-3.125</v>
@@ -33341,7 +33344,7 @@
         <v>-1.5625</v>
       </c>
       <c r="AD260" s="1">
-        <v>1.28644E-5</v>
+        <v>0</v>
       </c>
       <c r="AE260">
         <v>-1.5625</v>
